--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF9C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -120,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +147,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2352,9 +2361,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80 / 판매처 표기 ID70)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2364,13 +2373,13 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>스마트키 트림 별도(품번·칩 미확인)</t>
+          <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2378,19 +2387,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저(모듈 명칭 미확인)</t>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 C 2011.2 국내 출시)</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩은 순정 87510-21100 기준 확인 / 블레이드 명칭 판매처마다 상충(TOY48 vs KI-7), 스마트키 칩 미확인</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 C 2011.2 국내 출시), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
         </is>
       </c>
     </row>
@@ -2420,9 +2429,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80 / 판매처 표기 ID70)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2432,13 +2441,13 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>스마트키 트림 별도(품번·칩 미확인)</t>
+          <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2446,19 +2455,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저(모듈 명칭 미확인)</t>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩은 순정 87510-21100 기준 확인 / 블레이드 명칭 판매처마다 상충(TOY48 vs KI-7), 스마트키 칩 미확인</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
         </is>
       </c>
     </row>
@@ -2488,9 +2497,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80 / 판매처 표기 ID70)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2500,13 +2509,13 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>스마트키 트림 별도(품번·칩 미확인)</t>
+          <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2514,19 +2523,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저(모듈 명칭 미확인)</t>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
-        </is>
-      </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩은 순정 87510-21100 기준 확인 / 블레이드 명칭 판매처마다 상충(TOY48 vs KI-7), 스마트키 칩 미확인</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
         </is>
       </c>
     </row>
@@ -2556,9 +2565,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80 / 판매처 표기 ID70)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2568,13 +2577,13 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>스마트키 트림 별도(품번·칩 미확인)</t>
+          <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2582,19 +2591,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저(모듈 명칭 미확인)</t>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
-        </is>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩은 순정 87510-21100 기준 확인 / 블레이드 명칭 판매처마다 상충(TOY48 vs KI-7), 스마트키 칩 미확인</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
         </is>
       </c>
     </row>
@@ -2624,9 +2633,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80 / 판매처 표기 ID70)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2636,13 +2645,13 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>스마트키 트림 별도(품번·칩 미확인)</t>
+          <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2650,19 +2659,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저(모듈 명칭 미확인)</t>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
-        </is>
-      </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩은 순정 87510-21100 기준 확인 / 블레이드 명칭 판매처마다 상충(TOY48 vs KI-7), 스마트키 칩 미확인</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
         </is>
       </c>
     </row>
@@ -2692,9 +2701,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80 / 판매처 표기 ID70)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2704,13 +2713,13 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>스마트키 트림 별도(품번·칩 미확인)</t>
+          <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2718,19 +2727,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저(모듈 명칭 미확인)</t>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩은 순정 87510-21100 기준 확인 / 블레이드 명칭 판매처마다 상충(TOY48 vs KI-7), 스마트키 칩 미확인</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
         </is>
       </c>
     </row>
@@ -2760,9 +2769,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80 / 판매처 표기 ID70)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2772,13 +2781,13 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>스마트키 트림 별도(품번·칩 미확인)</t>
+          <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2786,19 +2795,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저(모듈 명칭 미확인)</t>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩은 순정 87510-21100 기준 확인 / 블레이드 명칭 판매처마다 상충(TOY48 vs KI-7), 스마트키 칩 미확인</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
         </is>
       </c>
     </row>
@@ -2828,9 +2837,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80 / 판매처 표기 ID70)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2840,13 +2849,13 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>스마트키 트림 별도(품번·칩 미확인)</t>
+          <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2854,19 +2863,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저(모듈 명칭 미확인)</t>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
-        </is>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩은 순정 87510-21100 기준 확인 / 블레이드 명칭 판매처마다 상충(TOY48 vs KI-7), 스마트키 칩 미확인</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
         </is>
       </c>
     </row>
@@ -2896,9 +2905,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80 / 판매처 표기 ID70)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2908,13 +2917,13 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>스마트키 트림 별도(품번·칩 미확인)</t>
+          <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2922,19 +2931,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저(모듈 명칭 미확인)</t>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩은 순정 87510-21100 기준 확인 / 블레이드 명칭 판매처마다 상충(TOY48 vs KI-7), 스마트키 칩 미확인 / 2019.2 C300 출시로 교체</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48) / 2019.2 C300 출시로 교체</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2975,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>DST80(ID70/4D70)</t>
+          <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -3026,7 +3035,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>DST80(ID70/4D70)</t>
+          <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -3086,7 +3095,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>DST80(ID70/4D70)</t>
+          <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -3146,7 +3155,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>DST80(ID70/4D70)</t>
+          <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -3206,7 +3215,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>DST80(ID70/4D70)</t>
+          <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -3266,7 +3275,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>DST80(ID70/4D70)</t>
+          <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -3326,7 +3335,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>DST80(ID70/4D70)</t>
+          <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -3386,7 +3395,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>DST80(ID70/4D70)</t>
+          <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -3556,9 +3565,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3568,13 +3577,13 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>8751035050 / 8751035060 (스마트키 트랜스미터, 칩 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3582,21 +3591,17 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L54" s="4" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), wikipedia(티볼리 2015.1 출시)</t>
-        </is>
-      </c>
-      <c r="N54" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충</t>
-        </is>
-      </c>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), wikipedia(티볼리 2015.1 출시), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3624,9 +3629,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3636,13 +3641,13 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>8751035050 / 8751035060 (스마트키 트랜스미터, 칩 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3650,21 +3655,17 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L55" s="4" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
-        </is>
-      </c>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충</t>
-        </is>
-      </c>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3692,9 +3693,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3704,13 +3705,13 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>8751035050 / 8751035060 (스마트키 트랜스미터, 칩 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3718,21 +3719,17 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L56" s="4" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
-        </is>
-      </c>
-      <c r="N56" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충</t>
-        </is>
-      </c>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3760,9 +3757,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3772,13 +3769,13 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>8751035050 / 8751035060 (스마트키 트랜스미터, 칩 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3786,21 +3783,17 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L57" s="4" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
-        </is>
-      </c>
-      <c r="N57" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충</t>
-        </is>
-      </c>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3828,9 +3821,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3840,13 +3833,13 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>8751035050 / 8751035060 (스마트키 트랜스미터, 칩 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3854,21 +3847,17 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L58" s="4" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
-        </is>
-      </c>
-      <c r="N58" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충</t>
-        </is>
-      </c>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3896,9 +3885,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3908,13 +3897,13 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>스마트키(품번·칩 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3922,19 +3911,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
-        </is>
-      </c>
-      <c r="N59" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>SmartKeyMV1 적용 2020.01 생산분까지</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3955,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+          <t>4D60x80(TI 80bit) 추정 — 2020.02 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3976,7 +3965,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3997,12 +3986,12 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4023,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+          <t>4D60x80(TI 80bit) 추정 — 2020.02 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -4044,7 +4033,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -4065,12 +4054,12 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4091,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+          <t>4D60x80(TI 80bit) 추정 — 2020.02 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -4112,7 +4101,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -4133,12 +4122,12 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충 / 3D Group 폴딩키 자료 2022년까지</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4159,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+          <t>4D60x80(TI 80bit) 추정 — 2020.02 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -4180,7 +4169,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -4201,12 +4190,12 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충 / 3D Group 폴딩키 자료 2022년까지</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4227,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+          <t>4D60x80(TI 80bit) 추정 — 2020.02 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -4248,7 +4237,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -4269,12 +4258,12 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충 / 3D Group 폴딩키 자료 2022년까지</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4295,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+          <t>4D60x80(TI 80bit) 추정 — 2020.02 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -4316,7 +4305,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4337,12 +4326,12 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module)</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>폴딩키 칩 확인(ID70 DST80), 스마트키 칩은 자료 없음 — 스마트키 차량은 실물 확인 / 블레이드 명칭 상충 / 3D Group 폴딩키 자료 2022년까지</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4372,9 +4361,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -4384,13 +4373,13 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>8751035050 / 8751035060 (티볼리 공용 추정)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4398,21 +4387,17 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해)</t>
-        </is>
-      </c>
-      <c r="N66" s="4" t="inlineStr">
-        <is>
-          <t>티볼리 롱바디 — 키는 티볼리와 동일 계열</t>
-        </is>
-      </c>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4440,9 +4425,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4452,13 +4437,13 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>8751035050 / 8751035060 (티볼리 공용 추정)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -4466,21 +4451,17 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L67" s="4" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해)</t>
-        </is>
-      </c>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>티볼리 롱바디 — 키는 티볼리와 동일 계열</t>
-        </is>
-      </c>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4508,9 +4489,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -4520,13 +4501,13 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>8751035050 / 8751035060 (티볼리 공용 추정)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4534,21 +4515,17 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해)</t>
-        </is>
-      </c>
-      <c r="N68" s="4" t="inlineStr">
-        <is>
-          <t>티볼리 롱바디 — 키는 티볼리와 동일 계열</t>
-        </is>
-      </c>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4576,9 +4553,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 스마트키·폴딩키 공통</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4588,13 +4565,13 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>8751035050 / 8751035060 (티볼리 공용 추정)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4602,19 +4579,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해), newdaily.co.kr(티볼리 에어 2019.9 단종)</t>
-        </is>
-      </c>
-      <c r="N69" s="4" t="inlineStr">
-        <is>
-          <t>티볼리 롱바디 — 키는 티볼리와 동일 계열 / 2019.9 단종 후 2020 재출시(재출시분은 원본 목록 범위 밖)</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해), newdaily.co.kr(티볼리 에어 2019.9 단종), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>2019.9 단종 후 2020 재출시</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5166,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -5249,7 +5226,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -5304,17 +5281,17 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(2007.3 이전 생산) / 이후 생산분 모듈 명칭 미확인</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000, 2007.3 이전 생산) / 이후 품번 변경 유닛</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인</t>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5321,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -5362,19 +5339,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N83" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5381,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -5422,19 +5399,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N84" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5441,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -5482,19 +5459,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N85" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5501,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -5542,19 +5519,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N86" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5586,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -5664,17 +5641,17 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(2007.3 이전 생산) / 이후 생산분 모듈 명칭 미확인</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000, 2007.3 이전 생산) / 이후 품번 변경 유닛</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인</t>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5681,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -5722,19 +5699,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N89" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5741,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -5782,19 +5759,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N90" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5801,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -5842,19 +5819,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N91" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5861,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -5902,19 +5879,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N92" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5921,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -5962,19 +5939,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N93" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6006,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -6089,7 +6066,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -6144,17 +6121,17 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(2007.3 이전 생산) / 이후 생산분 모듈 명칭 미확인</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000, 2007.3 이전 생산) / 이후 품번 변경 유닛</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인</t>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6161,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -6202,19 +6179,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N97" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6221,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -6262,19 +6239,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N98" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6281,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -6322,19 +6299,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N99" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6341,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
@@ -6382,19 +6359,19 @@
           <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
         </is>
       </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(2007.4 이후 별도 유닛 적용 종료 — 통합 모듈 명칭 미확인)</t>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3)</t>
-        </is>
-      </c>
-      <c r="N100" s="4" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 모듈 명칭 미확인</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6403,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+          <t>4D60x80(TI 80bit) 추정</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -6440,7 +6417,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
@@ -6453,12 +6434,12 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1)</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>액티언 스포츠 후속 — 3D Group 적용표의 "액티언 스포츠"에 해당하는지 직접 확인 안 됨</t>
+          <t>폴딩키 자료가 2014.01부터 — 2012·2013년식 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6471,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+          <t>4D60x80(TI 80bit) 추정</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -6504,7 +6485,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
@@ -6517,12 +6502,12 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1)</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>액티언 스포츠 후속 — 3D Group 적용표의 "액티언 스포츠"에 해당하는지 직접 확인 안 됨</t>
+          <t>폴딩키 자료가 2014.01부터 — 2012·2013년식 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
@@ -6552,9 +6537,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -6568,25 +6553,29 @@
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
+        </is>
+      </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L103" s="4" t="inlineStr">
+      <c r="L103" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1)</t>
-        </is>
-      </c>
-      <c r="N103" s="4" t="inlineStr">
-        <is>
-          <t>액티언 스포츠 후속 — 3D Group 적용표의 "액티언 스포츠"에 해당하는지 직접 확인 안 됨</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
         </is>
       </c>
     </row>
@@ -6616,9 +6605,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -6632,25 +6621,29 @@
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
+        </is>
+      </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L104" s="4" t="inlineStr">
+      <c r="L104" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1)</t>
-        </is>
-      </c>
-      <c r="N104" s="4" t="inlineStr">
-        <is>
-          <t>액티언 스포츠 후속 — 3D Group 적용표의 "액티언 스포츠"에 해당하는지 직접 확인 안 됨</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
         </is>
       </c>
     </row>
@@ -6680,9 +6673,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -6696,25 +6689,29 @@
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
+        </is>
+      </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L105" s="4" t="inlineStr">
+      <c r="L105" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1)</t>
-        </is>
-      </c>
-      <c r="N105" s="4" t="inlineStr">
-        <is>
-          <t>액티언 스포츠 후속 — 3D Group 적용표의 "액티언 스포츠"에 해당하는지 직접 확인 안 됨</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
         </is>
       </c>
     </row>
@@ -6744,9 +6741,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -6760,25 +6757,29 @@
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L106" s="4" t="inlineStr">
+      <c r="L106" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1)</t>
-        </is>
-      </c>
-      <c r="N106" s="4" t="inlineStr">
-        <is>
-          <t>액티언 스포츠 후속 — 3D Group 적용표의 "액티언 스포츠"에 해당하는지 직접 확인 안 됨</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
         </is>
       </c>
     </row>
@@ -6808,9 +6809,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit) — 폴딩키 기준</t>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -6824,25 +6825,29 @@
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L107" s="4" t="inlineStr">
+      <c r="L107" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1)</t>
-        </is>
-      </c>
-      <c r="N107" s="4" t="inlineStr">
-        <is>
-          <t>액티언 스포츠 후속 — 3D Group 적용표의 "액티언 스포츠"에 해당하는지 직접 확인 안 됨</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
         </is>
       </c>
     </row>
@@ -6857,12 +6862,24 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr"/>
-      <c r="D108" s="6" t="inlineStr"/>
-      <c r="E108" s="6" t="inlineStr"/>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
@@ -6870,23 +6887,23 @@
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>스마트키(품번 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2018.03~2021.12) / 8751036B00(무쏘 스포츠 2019-2021)</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="4" t="inlineStr">
+      <c r="L108" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경)</t>
-        </is>
-      </c>
-      <c r="N108" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 없음</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
         </is>
       </c>
     </row>
@@ -6901,12 +6918,24 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr"/>
-      <c r="D109" s="6" t="inlineStr"/>
-      <c r="E109" s="6" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
@@ -6914,23 +6943,23 @@
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>스마트키(품번 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2018.03~2021.12) / 8751036B00(무쏘 스포츠 2019-2021)</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="4" t="inlineStr">
+      <c r="L109" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경)</t>
-        </is>
-      </c>
-      <c r="N109" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 없음</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6974,24 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr"/>
-      <c r="D110" s="6" t="inlineStr"/>
-      <c r="E110" s="6" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
@@ -6958,23 +6999,23 @@
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>스마트키(품번 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2018.03~2021.12) / 8751036B00(무쏘 스포츠 2019-2021)</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="4" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경)</t>
-        </is>
-      </c>
-      <c r="N110" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 없음</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
         </is>
       </c>
     </row>
@@ -6989,12 +7030,24 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr"/>
-      <c r="D111" s="6" t="inlineStr"/>
-      <c r="E111" s="6" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
@@ -7002,23 +7055,23 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>스마트키(품번 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2018.03~2021.12) / 8751036B00(무쏘 스포츠 2019-2021)</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="4" t="inlineStr">
+      <c r="L111" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경)</t>
-        </is>
-      </c>
-      <c r="N111" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 없음</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7091,7 @@
       <c r="E112" s="6" t="inlineStr"/>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>확인 불가(2022 이후 스마트키 칩 자료 없음)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
@@ -7057,12 +7110,12 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경)</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>스마트키 칩 자료 없음</t>
+          <t>SmartKeyMV1은 2021.12 생산분까지 — 이후 키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7135,7 @@
       <c r="E113" s="6" t="inlineStr"/>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>확인 불가(2022 이후 스마트키 칩 자료 없음)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
@@ -7101,12 +7154,12 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경)</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
       <c r="N113" s="4" t="inlineStr">
         <is>
-          <t>스마트키 칩 자료 없음</t>
+          <t>SmartKeyMV1은 2021.12 생산분까지 — 이후 키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7179,7 @@
       <c r="E114" s="6" t="inlineStr"/>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>확인 불가(2022 이후 스마트키 칩 자료 없음)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
@@ -7145,12 +7198,12 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경)</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
-          <t>스마트키 칩 자료 없음 / 2025.2부터 무쏘 스포츠·무쏘 칸으로 차명 변경(같은 차)</t>
+          <t>SmartKeyMV1은 2021.12 생산분까지 — 이후 키 칩 자료 없음 / 2025.2부터 무쏘 스포츠·무쏘 칸으로 차명 변경</t>
         </is>
       </c>
     </row>
@@ -7165,12 +7218,24 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr"/>
-      <c r="D115" s="6" t="inlineStr"/>
-      <c r="E115" s="6" t="inlineStr"/>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
@@ -7182,19 +7247,19 @@
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시)</t>
-        </is>
-      </c>
-      <c r="N115" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+        </is>
+      </c>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>칩은 국내 열쇠기사 카페 자료(47칩) 기준 — 이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리(SKM) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7209,12 +7274,24 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr"/>
-      <c r="D116" s="6" t="inlineStr"/>
-      <c r="E116" s="6" t="inlineStr"/>
-      <c r="F116" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
@@ -7226,19 +7303,19 @@
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시)</t>
-        </is>
-      </c>
-      <c r="N116" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>칩은 국내 열쇠기사 카페 자료(47칩) 기준 — 이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리(SKM) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7253,12 +7330,24 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr"/>
-      <c r="D117" s="6" t="inlineStr"/>
-      <c r="E117" s="6" t="inlineStr"/>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
@@ -7270,19 +7359,19 @@
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시)</t>
-        </is>
-      </c>
-      <c r="N117" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>칩은 국내 열쇠기사 카페 자료(47칩) 기준 — 이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리(SKM) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7297,12 +7386,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr"/>
-      <c r="D118" s="6" t="inlineStr"/>
-      <c r="E118" s="6" t="inlineStr"/>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
@@ -7314,19 +7415,19 @@
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시)</t>
-        </is>
-      </c>
-      <c r="N118" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+        </is>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>칩은 국내 열쇠기사 카페 자료(47칩) 기준 — 이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리(SKM) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7341,12 +7442,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C119" s="6" t="inlineStr"/>
-      <c r="D119" s="6" t="inlineStr"/>
-      <c r="E119" s="6" t="inlineStr"/>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
@@ -7358,19 +7471,19 @@
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시)</t>
-        </is>
-      </c>
-      <c r="N119" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+        </is>
+      </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>2026.5 뉴 토레스 페이스리프트 — 신형 키 칩 직접 자료 없음, 기존 47칩 기준</t>
         </is>
       </c>
     </row>
@@ -7385,12 +7498,24 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr"/>
-      <c r="D120" s="6" t="inlineStr"/>
-      <c r="E120" s="6" t="inlineStr"/>
-      <c r="F120" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
@@ -7402,19 +7527,19 @@
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>SKM 추정</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터)</t>
-        </is>
-      </c>
-      <c r="N120" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>토레스 전기차 버전 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7554,24 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr"/>
-      <c r="D121" s="6" t="inlineStr"/>
-      <c r="E121" s="6" t="inlineStr"/>
-      <c r="F121" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
@@ -7446,19 +7583,19 @@
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>SKM 추정</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터)</t>
-        </is>
-      </c>
-      <c r="N121" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>토레스 전기차 버전 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7473,12 +7610,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr"/>
-      <c r="D122" s="6" t="inlineStr"/>
-      <c r="E122" s="6" t="inlineStr"/>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
@@ -7490,19 +7639,19 @@
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>SKM 추정</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터)</t>
-        </is>
-      </c>
-      <c r="N122" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>토레스 전기차 버전 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7517,12 +7666,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr"/>
-      <c r="D123" s="6" t="inlineStr"/>
-      <c r="E123" s="6" t="inlineStr"/>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
@@ -7534,19 +7695,19 @@
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>SKM 추정</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터)</t>
-        </is>
-      </c>
-      <c r="N123" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>토레스 전기차 버전 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7561,12 +7722,24 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr"/>
-      <c r="D124" s="6" t="inlineStr"/>
-      <c r="E124" s="6" t="inlineStr"/>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
@@ -7578,19 +7751,19 @@
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>SKM 추정</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유)</t>
-        </is>
-      </c>
-      <c r="N124" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>토레스와 플랫폼 공유(2024.8 출시) — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7605,12 +7778,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr"/>
-      <c r="D125" s="6" t="inlineStr"/>
-      <c r="E125" s="6" t="inlineStr"/>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
@@ -7622,19 +7807,19 @@
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>SKM 추정</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유)</t>
-        </is>
-      </c>
-      <c r="N125" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>토레스와 플랫폼 공유(2024.8 출시) — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7834,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr"/>
-      <c r="D126" s="6" t="inlineStr"/>
-      <c r="E126" s="6" t="inlineStr"/>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
@@ -7666,19 +7863,19 @@
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>SKM 추정</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유)</t>
-        </is>
-      </c>
-      <c r="N126" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>토레스와 플랫폼 공유(2024.8 출시) — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7890,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr"/>
-      <c r="D127" s="6" t="inlineStr"/>
-      <c r="E127" s="6" t="inlineStr"/>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr"/>
@@ -7710,19 +7919,19 @@
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>SKM 추정</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시)</t>
-        </is>
-      </c>
-      <c r="N127" s="7" t="inlineStr">
-        <is>
-          <t>원본 목록 2024~ — 실제 출시 2025.3 / 키 칩·이모빌라이저 자료 없음</t>
+          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>원본 목록 2024~ — 실제 출시 2025.3 / 토레스 EVX 기반 픽업 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7737,12 +7946,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr"/>
-      <c r="D128" s="6" t="inlineStr"/>
-      <c r="E128" s="6" t="inlineStr"/>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
@@ -7754,19 +7975,19 @@
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>SKM 추정</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시)</t>
-        </is>
-      </c>
-      <c r="N128" s="7" t="inlineStr">
-        <is>
-          <t>키 칩·이모빌라이저 자료 없음</t>
+          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>토레스 EVX 기반 픽업 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7796,9 +8017,9 @@
           <t>△</t>
         </is>
       </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>ID48(Megamos Crypto) 추정</t>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
@@ -7810,19 +8031,19 @@
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="4" t="inlineStr">
+      <c r="L129" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식)</t>
-        </is>
-      </c>
-      <c r="N129" s="4" t="inlineStr">
-        <is>
-          <t>2001.9 출시 — TMPro 자료가 2002년부터라 2001년식 직접 확인 안 됨</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>originalkey 순정 키 적용 범위가 2001년부터 — TMPro 이모박스 자료는 2002~</t>
         </is>
       </c>
     </row>
@@ -7873,7 +8094,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr"/>
@@ -7925,7 +8146,7 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr"/>
@@ -7977,7 +8198,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr"/>
@@ -8029,7 +8250,7 @@
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr"/>
@@ -8081,7 +8302,7 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -8141,7 +8362,7 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -8201,7 +8422,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr"/>
@@ -8257,7 +8478,7 @@
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr"/>
@@ -8313,7 +8534,7 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr"/>
@@ -8369,7 +8590,7 @@
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr"/>
@@ -8425,7 +8646,7 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr"/>
@@ -8481,7 +8702,7 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr"/>
@@ -8512,15 +8733,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>ID60(4D60, SSY3 키) / ID70·4D70(DST80, 폴딩키·스마트키)</t>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>SSY3 / TOY48·KI-7(폴딩키)</t>
+          <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -8531,22 +8752,22 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>87510-21100 (3버튼 폴딩키, 3D Group 적용표 "렉스턴")</t>
-        </is>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
+          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80)</t>
-        </is>
-      </c>
-      <c r="N142" s="4" t="inlineStr">
-        <is>
-          <t>키 종류(SSY3 리모컨키·폴딩키·스마트키)에 따라 칩 상이 — 차량 키로 확인 / ICU 부품 적용이 2017.04까지</t>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
         </is>
       </c>
     </row>
@@ -8576,15 +8797,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>ID60(4D60, SSY3 키) / ID70·4D70(DST80, 폴딩키·스마트키)</t>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>SSY3 / TOY48·KI-7(폴딩키)</t>
+          <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -8595,22 +8816,22 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>87510-21100 (3버튼 폴딩키, 3D Group 적용표 "렉스턴")</t>
-        </is>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
+          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80)</t>
-        </is>
-      </c>
-      <c r="N143" s="4" t="inlineStr">
-        <is>
-          <t>키 종류(SSY3 리모컨키·폴딩키·스마트키)에 따라 칩 상이 — 차량 키로 확인 / ICU 부품 적용이 2017.04까지</t>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
         </is>
       </c>
     </row>
@@ -8640,15 +8861,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>ID60(4D60, SSY3 키) / ID70·4D70(DST80, 폴딩키·스마트키)</t>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>SSY3 / TOY48·KI-7(폴딩키)</t>
+          <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -8659,22 +8880,22 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>87510-21100 (3버튼 폴딩키, 3D Group 적용표 "렉스턴")</t>
-        </is>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
+          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80)</t>
-        </is>
-      </c>
-      <c r="N144" s="4" t="inlineStr">
-        <is>
-          <t>키 종류(SSY3 리모컨키·폴딩키·스마트키)에 따라 칩 상이 — 차량 키로 확인 / ICU 부품 적용이 2017.04까지</t>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
         </is>
       </c>
     </row>
@@ -8704,15 +8925,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>ID60(4D60, SSY3 키) / ID70·4D70(DST80, 폴딩키·스마트키)</t>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>SSY3 / TOY48·KI-7(폴딩키)</t>
+          <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
@@ -8723,22 +8944,22 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>87510-21100 (3버튼 폴딩키, 3D Group 적용표 "렉스턴")</t>
-        </is>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
+          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80)</t>
-        </is>
-      </c>
-      <c r="N145" s="4" t="inlineStr">
-        <is>
-          <t>키 종류(SSY3 리모컨키·폴딩키·스마트키)에 따라 칩 상이 — 차량 키로 확인 / ICU 부품 적용이 2017.04까지</t>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
         </is>
       </c>
     </row>
@@ -8768,15 +8989,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>ID60(4D60, SSY3 키) / ID70·4D70(DST80, 폴딩키·스마트키)</t>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>SSY3 / TOY48·KI-7(폴딩키)</t>
+          <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -8787,22 +9008,22 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>87510-21100 (3버튼 폴딩키, 3D Group 적용표 "렉스턴")</t>
-        </is>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
+          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80)</t>
-        </is>
-      </c>
-      <c r="N146" s="4" t="inlineStr">
-        <is>
-          <t>키 종류(SSY3 리모컨키·폴딩키·스마트키)에 따라 칩 상이 — 차량 키로 확인 / ICU 부품 적용이 2017.04까지</t>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
         </is>
       </c>
     </row>
@@ -8832,15 +9053,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>ID60(4D60, SSY3 키) / ID70·4D70(DST80, 폴딩키·스마트키)</t>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>SSY3 / TOY48·KI-7(폴딩키)</t>
+          <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
@@ -8851,22 +9072,22 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>87510-21100 (3버튼 폴딩키, 3D Group 적용표 "렉스턴")</t>
-        </is>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
+          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80)</t>
-        </is>
-      </c>
-      <c r="N147" s="4" t="inlineStr">
-        <is>
-          <t>키 종류(SSY3 리모컨키·폴딩키·스마트키)에 따라 칩 상이 — 차량 키로 확인 / ICU 부품 적용이 2017.04까지</t>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
         </is>
       </c>
     </row>
@@ -8881,12 +9102,24 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr"/>
-      <c r="D148" s="6" t="inlineStr"/>
-      <c r="E148" s="6" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
@@ -8894,23 +9127,23 @@
       <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>스마트키(품번 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2017.07~2020.11, 87510-36050/36550/36560 대체)</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="4" t="inlineStr">
+      <c r="L148" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010)</t>
-        </is>
-      </c>
-      <c r="N148" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
         </is>
       </c>
     </row>
@@ -8925,12 +9158,24 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr"/>
-      <c r="D149" s="6" t="inlineStr"/>
-      <c r="E149" s="6" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr"/>
@@ -8938,23 +9183,23 @@
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>스마트키(품번 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2017.07~2020.11, 87510-36050/36550/36560 대체)</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="4" t="inlineStr">
+      <c r="L149" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010)</t>
-        </is>
-      </c>
-      <c r="N149" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
         </is>
       </c>
     </row>
@@ -8969,12 +9214,24 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="C150" s="6" t="inlineStr"/>
-      <c r="D150" s="6" t="inlineStr"/>
-      <c r="E150" s="6" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
@@ -8982,23 +9239,23 @@
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>스마트키(품번 미확인)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2017.07~2020.11, 87510-36050/36550/36560 대체)</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="4" t="inlineStr">
+      <c r="L150" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010)</t>
-        </is>
-      </c>
-      <c r="N150" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
         </is>
       </c>
     </row>
@@ -9013,12 +9270,24 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="C151" s="6" t="inlineStr"/>
-      <c r="D151" s="6" t="inlineStr"/>
-      <c r="E151" s="6" t="inlineStr"/>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>4D60x80(2020.11 이전 생산) / 신형 키 8751036C20(2020.11 이후, 칩 미확인)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
@@ -9026,7 +9295,7 @@
       <c r="I151" s="2" t="inlineStr"/>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>8751036C20 (5버튼, 433MHz, 2020.11~2022.04 생산)</t>
+          <t>R-C-2CG-SmartKeyMV1 (2017.07~2020.11, 87510-36050/36550/36560 대체) / 8751036C20(2020.11~)</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr"/>
@@ -9037,12 +9306,12 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04)</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>2020.11 페이스리프트 이후 스마트키 교체 — 신형 키(NXP 표기) 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9331,7 @@
       <c r="E152" s="6" t="inlineStr"/>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr"/>
@@ -9081,12 +9350,12 @@
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04)</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
       <c r="N152" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9375,7 @@
       <c r="E153" s="6" t="inlineStr"/>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr"/>
@@ -9125,12 +9394,12 @@
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04)</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
       <c r="N153" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9419,7 @@
       <c r="E154" s="6" t="inlineStr"/>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr"/>
@@ -9169,12 +9438,12 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010)</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
       <c r="N154" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9463,7 @@
       <c r="E155" s="6" t="inlineStr"/>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr"/>
@@ -9213,12 +9482,12 @@
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010)</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9507,7 @@
       <c r="E156" s="6" t="inlineStr"/>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr"/>
@@ -9257,12 +9526,12 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010)</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
       <c r="N156" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9282,7 +9551,7 @@
       <c r="E157" s="6" t="inlineStr"/>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(DST80 계열 추정)</t>
+          <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr"/>
@@ -9301,12 +9570,12 @@
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010)</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈(SKM) 확인, 스마트키 칩은 자료 없음 — 실물 확인 필요</t>
+          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9593,7 @@
       <c r="C158" s="6" t="inlineStr"/>
       <c r="D158" s="6" t="inlineStr"/>
       <c r="E158" s="6" t="inlineStr"/>
-      <c r="F158" s="7" t="inlineStr">
+      <c r="F158" s="8" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -9334,7 +9603,7 @@
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="7" t="inlineStr">
+      <c r="L158" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
@@ -9344,7 +9613,7 @@
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N158" s="7" t="inlineStr">
+      <c r="N158" s="8" t="inlineStr">
         <is>
           <t>이스타나 키 칩 자료 없음</t>
         </is>
@@ -9364,7 +9633,7 @@
       <c r="C159" s="6" t="inlineStr"/>
       <c r="D159" s="6" t="inlineStr"/>
       <c r="E159" s="6" t="inlineStr"/>
-      <c r="F159" s="7" t="inlineStr">
+      <c r="F159" s="8" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -9374,7 +9643,7 @@
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="7" t="inlineStr">
+      <c r="L159" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
@@ -9384,7 +9653,7 @@
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N159" s="7" t="inlineStr">
+      <c r="N159" s="8" t="inlineStr">
         <is>
           <t>이스타나 키 칩 자료 없음</t>
         </is>
@@ -9404,7 +9673,7 @@
       <c r="C160" s="6" t="inlineStr"/>
       <c r="D160" s="6" t="inlineStr"/>
       <c r="E160" s="6" t="inlineStr"/>
-      <c r="F160" s="7" t="inlineStr">
+      <c r="F160" s="8" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -9414,7 +9683,7 @@
       <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="7" t="inlineStr">
+      <c r="L160" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
@@ -9424,7 +9693,7 @@
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N160" s="7" t="inlineStr">
+      <c r="N160" s="8" t="inlineStr">
         <is>
           <t>이스타나 키 칩 자료 없음</t>
         </is>
@@ -9444,7 +9713,7 @@
       <c r="C161" s="6" t="inlineStr"/>
       <c r="D161" s="6" t="inlineStr"/>
       <c r="E161" s="6" t="inlineStr"/>
-      <c r="F161" s="7" t="inlineStr">
+      <c r="F161" s="8" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -9454,7 +9723,7 @@
       <c r="I161" s="2" t="inlineStr"/>
       <c r="J161" s="2" t="inlineStr"/>
       <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="7" t="inlineStr">
+      <c r="L161" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
@@ -9464,7 +9733,7 @@
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N161" s="7" t="inlineStr">
+      <c r="N161" s="8" t="inlineStr">
         <is>
           <t>이스타나 키 칩 자료 없음</t>
         </is>
@@ -9484,7 +9753,7 @@
       <c r="C162" s="6" t="inlineStr"/>
       <c r="D162" s="6" t="inlineStr"/>
       <c r="E162" s="6" t="inlineStr"/>
-      <c r="F162" s="7" t="inlineStr">
+      <c r="F162" s="8" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -9494,7 +9763,7 @@
       <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="7" t="inlineStr">
+      <c r="L162" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
@@ -9504,7 +9773,7 @@
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N162" s="7" t="inlineStr">
+      <c r="N162" s="8" t="inlineStr">
         <is>
           <t>이스타나 키 칩 자료 없음</t>
         </is>
@@ -9958,7 +10227,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>ID60(4D60, 1세대 키) / ID70(DST80, 로디우스 II 폴딩키 87510-21100)</t>
+          <t>ID60(4D60, 1세대 키) / 4D60x80(TI 80bit, 로디우스 II 폴딩키)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr"/>
@@ -9981,7 +10250,7 @@
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
+          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
       <c r="N171" s="4" t="inlineStr">
@@ -10018,7 +10287,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>ID60(4D60, 1세대 키) / ID70(DST80, 로디우스 II 폴딩키 87510-21100)</t>
+          <t>ID60(4D60, 1세대 키) / 4D60x80(TI 80bit, 로디우스 II 폴딩키)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
@@ -10041,7 +10310,7 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴)</t>
+          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
       <c r="N172" s="4" t="inlineStr">
@@ -10076,9 +10345,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -10088,7 +10357,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
@@ -10098,19 +10367,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L173" s="4" t="inlineStr">
+      <c r="L173" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2)</t>
-        </is>
-      </c>
-      <c r="N173" s="4" t="inlineStr">
-        <is>
-          <t>remkeys 적용표의 로디우스 II(2012-2019) 기준 — 블레이드 명칭 상충</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
         </is>
       </c>
     </row>
@@ -10140,9 +10409,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80)</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -10152,7 +10421,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
@@ -10162,19 +10431,19 @@
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L174" s="4" t="inlineStr">
+      <c r="L174" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2)</t>
-        </is>
-      </c>
-      <c r="N174" s="4" t="inlineStr">
-        <is>
-          <t>remkeys 적용표의 로디우스 II(2012-2019) 기준 — 블레이드 명칭 상충</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
         </is>
       </c>
     </row>
@@ -10204,9 +10473,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F175" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80)</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -10216,29 +10485,33 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>R-C-2CG-SmartKeyMV1 (로디우스/스타빅 II 2015.06~2019.03)</t>
+        </is>
+      </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L175" s="4" t="inlineStr">
+      <c r="L175" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2)</t>
-        </is>
-      </c>
-      <c r="N175" s="4" t="inlineStr">
-        <is>
-          <t>remkeys 적용표의 로디우스 II(2012-2019) 기준 — 블레이드 명칭 상충</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
         </is>
       </c>
     </row>
@@ -10268,9 +10541,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -10280,29 +10553,33 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>R-C-2CG-SmartKeyMV1 (로디우스/스타빅 II 2015.06~2019.03)</t>
+        </is>
+      </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L176" s="4" t="inlineStr">
+      <c r="L176" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2)</t>
-        </is>
-      </c>
-      <c r="N176" s="4" t="inlineStr">
-        <is>
-          <t>remkeys 적용표의 로디우스 II(2012-2019) 기준 — 블레이드 명칭 상충</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
         </is>
       </c>
     </row>
@@ -10332,9 +10609,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80)</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -10344,29 +10621,33 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>R-C-2CG-SmartKeyMV1 (로디우스/스타빅 II 2015.06~2019.03)</t>
+        </is>
+      </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L177" s="4" t="inlineStr">
+      <c r="L177" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2)</t>
-        </is>
-      </c>
-      <c r="N177" s="4" t="inlineStr">
-        <is>
-          <t>remkeys 적용표의 로디우스 II(2012-2019) 기준 — 블레이드 명칭 상충</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
         </is>
       </c>
     </row>
@@ -10396,9 +10677,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>ID70(DST80, 80bit)</t>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>4D60x80(TI 80bit, DST80)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -10408,29 +10689,33 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>TOY48 / KI-7 (자료 상충)</t>
+          <t>TOY48</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>R-C-2CG-SmartKeyMV1 (로디우스/스타빅 II 2015.06~2019.03)</t>
+        </is>
+      </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L178" s="4" t="inlineStr">
+      <c r="L178" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2)</t>
-        </is>
-      </c>
-      <c r="N178" s="4" t="inlineStr">
-        <is>
-          <t>remkeys 적용표의 로디우스 II(2012-2019) 기준 — 블레이드 명칭 상충</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
         </is>
       </c>
     </row>
@@ -10446,142 +10731,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr"/>
+      <c r="A2" s="9" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>- 칼리스타(1993-1997)·코란도 훼미리(1988-1996)는 2000년식 이전에 단종되어 행이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제와 다른 모델은 실제 기준으로 적고 비고에 적었습니다(체어맨 H ~2014, 체어맨 W ~2017, 코란도 e-모션 2022~2023, 무쏘 EV 2025~, 렉스턴 스포츠는 2025.2 무쏘 스포츠로 차명 변경).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 구형은 VDO 이모빌라이저 박스(이모박스), 액티언·카이런·렉스턴 계열은 이모빌라이저 컨트롤 유닛(ICU, 87110-08B00/09000), 신형 스마트키 차량은 SKM(스마트키 모듈)입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>- 폴딩키(리모컨 일체형) 품번은 '폴딩키(부품번호)', 스마트키 트랜스미터 품번은 '스마트키(부품번호)' 칸에 적었습니다. 쌍용은 카드키가 없어 카드키 칸은 비었습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID60(4D60)·ID70/DST80(4D70) → O/O/O, ID48(Megamos Crypto) → △/△/△, ID48·ID60 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr"/>
+      <c r="A11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>- 빨간색: 확인 불가 — 토레스·토레스 EVX·액티언(J120)·무쏘 EV·이스타나는 키 칩 자료를 찾지 못했습니다.</t>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>- 빨간색: 확인 불가 — 이스타나는 키 칩 자료를 찾지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나 연식 범위 밖인 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>- 무쏘·코란도·렉스턴(2002-2006): VDO 이모박스(MCU MC68HC05B16) + 메가모스 크립토(ID48) 트랜스폰더 — TMPro 모듈 85 자료. 코란도 2000-2006 블레이드 HYN10(JMA HY-5.P1).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>- 액티언·카이런·렉스턴 계열: 4D-60 칩 키, 블레이드 SSY3(JMA SSA-2P). 순정 키 87170-32030·32020·08D50은 80bit, 87170-08B21은 40bit — 연식 구분 자료가 없어 키 품번으로 확인해야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>- 이모빌라이저 컨트롤 유닛(87110-08B00/09000) 적용: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언 스포츠 2006.04~2007.03. 2007.4 이후 카이런·액티언 계열의 모듈 명칭은 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>- 순정 3버튼 폴딩키 87510-21100(코란도 C·로디우스 II/코란도 투리스모·티볼리 등): 80bit TI 칩(판매처 표기 ID70 DST80 / ID8E). 블레이드는 TOY48(remkeys)과 KI-7(3D Group, 블레이드 품번 7105121500)로 표기가 다릅니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>- [재조사] 토레스 스마트키 칩은 47칩(ID47, Hitag3) — 국내 열쇠기사 카페 자료. 토레스 EVX·액티언(J120)·무쏘 EV는 같은 플랫폼이라 동일 추정(주황).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>- [재조사] 코란도 C(러시아명 New Actyon) 순정 스마트키 4D60x80·비상키 TOY48, 스타빅·액티언·티볼리·렉스턴 순정 폴딩키(2013-2021) 4D60x80, 렉스턴 W 2버튼 키 4D60x80·TOY40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>- [재조사] 순정 스마트키 R-C-2CG-SmartKeyMV1(4D60x80, 433MHz): 티볼리 2015.03~2020.01, 렉스턴 스포츠 2018.03~2021.12, G4 렉스턴 2017.07~2020.11, 로디우스/스타빅 II 2015.06~2019.03. 이후 신형 키(G4 2020.11~ 8751036C20 등)는 칩 자료 없음(주황).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>- [재조사] 코란도 C(C200) 이모빌라이저는 SKM(키 슬롯)과 엔진 ECU(EMS)가 P-CAN으로 인증. 액티언 2008~2011도 별도 이모빌라이저 컨트롤 유닛 사용(품번 변경).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>- 코란도 C300 스마트키 DST80·HYN14R, 렉스턴 W 2013 스마트키 4D70 DST80(FCC DEO-MT FOBG02), G4 렉스턴 이모빌라이저 = SKM(87570-36010, 2017.07~).</t>
         </is>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KGM(쌍용) 트랜스폰더 DB'!$A$1:$N$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KGM(쌍용) 트랜스폰더 DB'!$A$1:$O$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N178"/>
+  <dimension ref="A1:O178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -529,14 +529,15 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -572,40 +573,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>키종류</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>키블레이드(부품번호)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>키블레이드(키웨이)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>카드키(부품번호)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>스마트키(부품번호)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>폴딩키(부품번호)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>이모빌라이저 시스템</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -642,24 +648,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -694,24 +705,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -746,24 +762,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -798,24 +819,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -850,24 +876,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -902,24 +933,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -954,24 +990,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1006,24 +1047,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1058,24 +1104,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>원본 목록 종료 2008 — 실제로는 체어맨 H(뉴 클래식 포함) 2014.12 단종까지 판매 / 체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1110,24 +1161,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1162,24 +1218,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼)</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1214,24 +1275,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼), carisyou.com(체어맨 H 2014.12.31 단종), danawa(체어맨 H 뉴 클래식 2011.5.27 출시)</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1266,24 +1332,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼), carisyou.com(체어맨 H 2014.12.31 단종)</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1318,24 +1389,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼), carisyou.com(체어맨 H 2014.12.31 단종)</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1370,24 +1446,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 트랜스폰더키: 쌍용 체어맨·액티언·카이런·렉스턴), wikipedia(체어맨 1997-2017, W124 플랫폼), carisyou.com(체어맨 H 2014.12.31 단종)</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>2014.12.31 단종 / 체어맨 연식별 칩 자료 없음 — 쌍용 공용 4D60 키 판매처 목록 기준 추정</t>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>체어맨 칩 직접 자료 없음 — 쌍용 공용 4D60 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1422,24 +1503,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1474,24 +1560,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1526,24 +1617,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1674,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1630,24 +1731,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1682,24 +1788,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1734,24 +1845,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1786,24 +1902,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1838,24 +1959,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1890,24 +2016,29 @@
           <t>ID60(4D60) 추정</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>확인 불가(모듈 명칭)</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>myremotekey.com(4D60 칩 쌍용 체어맨 포함), carisyou.com/namu.wiki(체어맨 W 2017.12 생산 종료)</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>원본 목록 종료 2024 — 실제 2017.12 단종 / 체어맨 W 스마트키 칩 자료 없음 — 추정값, 실물 확인 필요</t>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>스마트키 칩 자료 없음 — 추정값</t>
         </is>
       </c>
     </row>
@@ -1942,28 +2073,33 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>HYN10 (JMA HY-5.P1)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), reidsremotes.com.au(코란도 2000-2006 트랜스폰더키 HYN10/HY-5.P1)</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>TMPro 이모박스 자료가 2002년부터 — 2000·2001년식 이모박스 적용 여부 직접 확인 안 됨</t>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>이모박스 자료가 2002년부터 — 2000·2001년식 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
@@ -1998,28 +2134,33 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>HYN10 (JMA HY-5.P1)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), reidsremotes.com.au(코란도 2000-2006 트랜스폰더키 HYN10/HY-5.P1)</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>TMPro 이모박스 자료가 2002년부터 — 2000·2001년식 이모박스 적용 여부 직접 확인 안 됨</t>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>이모박스 자료가 2002년부터 — 2000·2001년식 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
@@ -2054,26 +2195,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>HYN10 (JMA HY-5.P1)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), reidsremotes.com.au(코란도 2000-2006 트랜스폰더키 HYN10/HY-5.P1)</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2106,26 +2252,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>HYN10 (JMA HY-5.P1)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), reidsremotes.com.au(코란도 2000-2006 트랜스폰더키 HYN10/HY-5.P1)</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2158,26 +2309,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>HYN10 (JMA HY-5.P1)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), reidsremotes.com.au(코란도 2000-2006 트랜스폰더키 HYN10/HY-5.P1)</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2210,26 +2366,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>HYN10 (JMA HY-5.P1)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), reidsremotes.com.au(코란도 2000-2006 트랜스폰더키 HYN10/HY-5.P1)</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2262,26 +2423,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>HYN10 (JMA HY-5.P1)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), reidsremotes.com.au(코란도 2000-2006 HYN10)</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2314,26 +2480,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>HYN10 (JMA HY-5.P1)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), reidsremotes.com.au(코란도 2000-2006 HYN10)</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2368,40 +2539,41 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 C 2011.2 국내 출시), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
-        </is>
-      </c>
+      <c r="O35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2436,40 +2608,41 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
-        </is>
-      </c>
+      <c r="O36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2504,40 +2677,41 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
-        </is>
-      </c>
+      <c r="O37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2572,40 +2746,41 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
-        </is>
-      </c>
+      <c r="O38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2640,40 +2815,41 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
-        </is>
-      </c>
+      <c r="O39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2708,40 +2884,41 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
-        </is>
-      </c>
+      <c r="O40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2776,40 +2953,41 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
-        </is>
-      </c>
+      <c r="O41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2844,40 +3022,41 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48)</t>
-        </is>
-      </c>
+      <c r="O42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2912,40 +3091,41 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>순정 스마트키 4버튼 433.92MHz(4D60x80, 비상키 TOY48)</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈·키 슬롯) — EMS(ECU)와 P-CAN 인증</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 스마트키 "Actyon"(러시아명 = 코란도 C) 2010-2020 4D60x80 433.92MHz 4버튼, 비상키 TOY48), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), manualslib(코란도 C200 정비지침서: 키 트랜스폰더가 SKM(이모빌라이저 슬롯)·EMS와 P-CAN 통신으로 인증)</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon = 코란도 C / 3D Group만 블레이드를 KI-7로 표기(나머지 TOY48) / 2019.2 C300 출시로 교체</t>
-        </is>
-      </c>
+      <c r="O43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2978,32 +3158,37 @@
           <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>HYN14R</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드는 carkeyhelper 요약 기준 / 이모빌라이저 모듈 명칭은 같은 세대 티볼리·G4 렉스턴(SKM) 기준 추정</t>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3038,32 +3223,37 @@
           <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>HYN14R</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드는 carkeyhelper 요약 기준 / 이모빌라이저 모듈 명칭은 같은 세대 티볼리·G4 렉스턴(SKM) 기준 추정</t>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3098,32 +3288,37 @@
           <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>HYN14R</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드는 carkeyhelper 요약 기준 / 이모빌라이저 모듈 명칭은 같은 세대 티볼리·G4 렉스턴(SKM) 기준 추정</t>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3158,32 +3353,37 @@
           <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>HYN14R</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드는 carkeyhelper 요약 기준 / 이모빌라이저 모듈 명칭은 같은 세대 티볼리·G4 렉스턴(SKM) 기준 추정</t>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3218,32 +3418,37 @@
           <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>HYN14R</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드는 carkeyhelper 요약 기준 / 이모빌라이저 모듈 명칭은 같은 세대 티볼리·G4 렉스턴(SKM) 기준 추정</t>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3278,32 +3483,37 @@
           <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>HYN14R</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드는 carkeyhelper 요약 기준 / 이모빌라이저 모듈 명칭은 같은 세대 티볼리·G4 렉스턴(SKM) 기준 추정</t>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3338,32 +3548,37 @@
           <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>HYN14R</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드는 carkeyhelper 요약 기준 / 이모빌라이저 모듈 명칭은 같은 세대 티볼리·G4 렉스턴(SKM) 기준 추정 / 2026년식 자료 없음</t>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3398,32 +3613,37 @@
           <t>DST80(TI 80bit, 4D60x80 계열)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>HYN14R</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="4" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드는 carkeyhelper 요약 기준 / 이모빌라이저 모듈 명칭은 같은 세대 티볼리·G4 렉스턴(SKM) 기준 추정 / 2026년식 자료 없음</t>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3458,28 +3678,33 @@
           <t>DST80(ID70/4D70) 추정(C300 기준)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>HYN14R 추정</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="4" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>newdaily.co.kr(코란도 이모션 2022.2 출시), sisajournal-e.com(2023 판매 중단), carkeyhelper.com(코란도 C300 스마트키 DST80)</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr">
-        <is>
-          <t>원본 목록 2019~ — 실제 국내 출시 2022.2 / C300 기반 전기차 — 키 칩 직접 자료 없음</t>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 코란도 C300 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3514,28 +3739,33 @@
           <t>DST80(ID70/4D70) 추정(C300 기준)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>HYN14R 추정</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="4" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>newdaily.co.kr(코란도 이모션 2022.2 출시), sisajournal-e.com(2023 판매 중단), carkeyhelper.com(코란도 C300 스마트키 DST80)</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr">
-        <is>
-          <t>2023.7 판매 종료 / C300 기반 전기차 — 키 칩 직접 자료 없음</t>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 코란도 C300 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3572,36 +3802,41 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), wikipedia(티볼리 2015.1 출시), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3636,36 +3871,41 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3700,36 +3940,41 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3764,36 +4009,41 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3828,36 +4078,41 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3892,40 +4147,41 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1 적용 2020.01 생산분까지</t>
-        </is>
-      </c>
+      <c r="O59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3960,38 +4216,43 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번·칩 미확인)</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="M60" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N60" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인</t>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>2020.02 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4028,38 +4289,43 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번·칩 미확인)</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N61" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>2020.02 이후 스마트키 칩 자료 없음 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4096,38 +4362,43 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번·칩 미확인)</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>2020.02 이후 스마트키 칩 자료 없음 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4164,38 +4435,43 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번·칩 미확인)</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L63" s="4" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>2020.02 이후 스마트키 칩 자료 없음 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4232,38 +4508,43 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번·칩 미확인)</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N64" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>2020.02 이후 스마트키 칩 자료 없음 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4300,38 +4581,43 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번·칩 미확인)</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L65" s="4" t="inlineStr">
+      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), kogoos.com/kpartsmall.com(티볼리 순정 스마트키 8751035060/8751035050), scandoc.online(티볼리 뉴 X150 SMART Key Module), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N65" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.01 생산분까지 — 이후 스마트키 칩 직접 자료 없음, 폴딩키는 2021년까지 4D60x80 확인 (2022~ 폴딩키도 미확인)</t>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>2020.02 이후 스마트키 칩 자료 없음 (2022~ 폴딩키도 미확인)</t>
         </is>
       </c>
     </row>
@@ -4368,36 +4654,41 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4432,36 +4723,41 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4496,36 +4792,41 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4560,40 +4861,41 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2015.03~2020.01, 87510-35050/35060 대체)</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), stockddalbae.com(티볼리 에어 키 분해), newdaily.co.kr(티볼리 에어 2019.9 단종), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz)</t>
         </is>
       </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>2019.9 단종 후 2020 재출시</t>
-        </is>
-      </c>
+      <c r="O69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4626,24 +4928,29 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>TMPro 자료가 2002년부터 — 2000·2001년식 직접 확인 안 됨 / 무쏘 키 블레이드 자료 없음</t>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>이모박스 자료가 2002년부터 — 2000·2001년식 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
@@ -4678,24 +4985,29 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
-        <is>
-          <t>TMPro 자료가 2002년부터 — 2000·2001년식 직접 확인 안 됨 / 무쏘 키 블레이드 자료 없음</t>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>이모박스 자료가 2002년부터 — 2000·2001년식 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
@@ -4730,26 +5042,27 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>무쏘 키 블레이드 자료 없음</t>
-        </is>
-      </c>
+      <c r="O72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4782,26 +5095,27 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
         </is>
       </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>무쏘 키 블레이드 자료 없음</t>
-        </is>
-      </c>
+      <c r="O73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4834,26 +5148,27 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
         </is>
       </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>무쏘 키 블레이드 자료 없음</t>
-        </is>
-      </c>
+      <c r="O74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4886,26 +5201,27 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
         </is>
       </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>무쏘 키 블레이드 자료 없음 / 실제 생산은 2006.4까지(namu.wiki)</t>
-        </is>
-      </c>
+      <c r="O75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4938,24 +5254,29 @@
           <t>ID48(Megamos Crypto) 추정(무쏘 기준)</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="4" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="4" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스 추정</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시)</t>
         </is>
       </c>
-      <c r="N76" s="4" t="inlineStr">
-        <is>
-          <t>무쏘 스포츠 직접 자료 없음 — 무쏘(이모박스 적용) 기준 추정</t>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>직접 자료 없음 — 무쏘 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4990,24 +5311,29 @@
           <t>ID48(Megamos Crypto) 추정(무쏘 기준)</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="4" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스 추정</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시)</t>
         </is>
       </c>
-      <c r="N77" s="4" t="inlineStr">
-        <is>
-          <t>무쏘 스포츠 직접 자료 없음 — 무쏘(이모박스 적용) 기준 추정</t>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>직접 자료 없음 — 무쏘 기준 추정</t>
         </is>
       </c>
     </row>
@@ -5042,24 +5368,29 @@
           <t>ID48(Megamos Crypto) 추정(무쏘 기준)</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="4" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스 추정</t>
         </is>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시)</t>
         </is>
       </c>
-      <c r="N78" s="4" t="inlineStr">
-        <is>
-          <t>무쏘 스포츠 직접 자료 없음 — 무쏘(이모박스 적용) 기준 추정</t>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>직접 자료 없음 — 무쏘 기준 추정</t>
         </is>
       </c>
     </row>
@@ -5094,24 +5425,29 @@
           <t>ID48(Megamos Crypto) 추정(무쏘 기준)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="4" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스 추정</t>
         </is>
       </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시)</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr">
-        <is>
-          <t>무쏘 스포츠 직접 자료 없음 — 무쏘(이모박스 적용) 기준 추정</t>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>직접 자료 없음 — 무쏘 기준 추정</t>
         </is>
       </c>
     </row>
@@ -5146,34 +5482,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000)</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>2005.10 출시 / 40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인</t>
-        </is>
-      </c>
+      <c r="O80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5206,34 +5543,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000)</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인</t>
-        </is>
-      </c>
+      <c r="O81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5266,34 +5604,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000, 2007.3 이전 생산) / 이후 품번 변경 유닛</t>
         </is>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5326,34 +5665,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5386,34 +5726,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5446,34 +5787,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5506,34 +5848,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5566,34 +5909,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000)</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>2006.3 출시 / 40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인</t>
-        </is>
-      </c>
+      <c r="O87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5626,34 +5970,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000, 2007.3 이전 생산) / 이후 품번 변경 유닛</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N88" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5686,34 +6031,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N89" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5746,34 +6092,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N90" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5806,34 +6153,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5866,34 +6214,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5926,34 +6275,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="N93" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N93" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5986,34 +6336,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000)</t>
         </is>
       </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N94" s="2" t="inlineStr">
-        <is>
-          <t>2005.6 출시 / 40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인</t>
-        </is>
-      </c>
+      <c r="O94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6046,34 +6397,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000)</t>
         </is>
       </c>
-      <c r="M95" s="2" t="inlineStr">
+      <c r="N95" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N95" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인</t>
-        </is>
-      </c>
+      <c r="O95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6106,34 +6458,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00/09000, 2007.3 이전 생산) / 이후 품번 변경 유닛</t>
         </is>
       </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="N96" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N96" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6166,34 +6519,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6226,34 +6580,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6286,34 +6641,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6346,34 +6702,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
+          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>87170-32030 / 87170-32020(80bit), 87170-08B21(40bit) — 2버튼 리모컨키</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(2007.4 이후 변경 품번)</t>
         </is>
       </c>
-      <c r="M100" s="2" t="inlineStr">
+      <c r="N100" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>40bit(08B21)·80bit(32030/32020) 키 연식 구분 자료 없음 — 키 품번으로 확인 / 2007.4 이후 이모빌라이저 유닛 품번 변경(87110-08B00/09000 적용 종료)</t>
-        </is>
-      </c>
+      <c r="O100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6408,36 +6765,41 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>TOY48 / KI-7 (자료 상충)</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L101" s="4" t="inlineStr">
+      <c r="M101" s="4" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M101" s="2" t="inlineStr">
+      <c r="N101" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr">
+      <c r="O101" s="4" t="inlineStr">
         <is>
           <t>폴딩키 자료가 2014.01부터 — 2012·2013년식 직접 확인 안 됨</t>
         </is>
@@ -6476,36 +6838,41 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>TOY48 / KI-7 (자료 상충)</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
         <is>
           <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="L102" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L102" s="4" t="inlineStr">
+      <c r="M102" s="4" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M102" s="2" t="inlineStr">
+      <c r="N102" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
-      <c r="N102" s="4" t="inlineStr">
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>폴딩키 자료가 2014.01부터 — 2012·2013년식 직접 확인 안 됨</t>
         </is>
@@ -6544,40 +6911,41 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t>TOY48 / KI-7 (자료 상충)</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="L103" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L103" s="2" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
-        </is>
-      </c>
+      <c r="O103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6612,40 +6980,41 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>TOY48 / KI-7 (자료 상충)</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
+      <c r="L104" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr">
+      <c r="M104" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M104" s="2" t="inlineStr">
+      <c r="N104" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
-        </is>
-      </c>
+      <c r="O104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6680,40 +7049,41 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>TOY48 / KI-7 (자료 상충)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="L105" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr">
+      <c r="M105" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M105" s="2" t="inlineStr">
+      <c r="N105" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
-        </is>
-      </c>
+      <c r="O105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6748,40 +7118,41 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>TOY48 / KI-7 (자료 상충)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
         <is>
           <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="L106" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L106" s="2" t="inlineStr">
+      <c r="M106" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M106" s="2" t="inlineStr">
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
-      <c r="N106" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
-        </is>
-      </c>
+      <c r="O106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6816,40 +7187,41 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>TOY48 / KI-7 (자료 상충)</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>8751008010 (2012-2018) / 8751032021 (15년형~) — 스마트리모컨</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="L107" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L107" s="2" t="inlineStr">
+      <c r="M107" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr">
+      <c r="N107" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
-      <c r="N107" s="2" t="inlineStr">
-        <is>
-          <t>러시아 판매명 New Actyon Sports = 코란도 스포츠 / 이모빌라이저 모듈 명칭은 미확인</t>
-        </is>
-      </c>
+      <c r="O107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6882,30 +7254,31 @@
           <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2018.03~2021.12) / 8751036B00(무쏘 스포츠 2019-2021)</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
-        </is>
-      </c>
+      <c r="O108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6938,30 +7311,31 @@
           <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2018.03~2021.12) / 8751036B00(무쏘 스포츠 2019-2021)</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
-        </is>
-      </c>
+      <c r="O109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6994,30 +7368,31 @@
           <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2018.03~2021.12) / 8751036B00(무쏘 스포츠 2019-2021)</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="N110" s="2" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
-        </is>
-      </c>
+      <c r="O110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7050,30 +7425,31 @@
           <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2018.03~2021.12) / 8751036B00(무쏘 스포츠 2019-2021)</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M111" s="2" t="inlineStr">
+      <c r="N111" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="N111" s="2" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
-        </is>
-      </c>
+      <c r="O111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7094,28 +7470,33 @@
           <t>확인 불가(2022 이후 스마트키 칩 자료 없음)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="4" t="inlineStr">
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M112" s="2" t="inlineStr">
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="N112" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1은 2021.12 생산분까지 — 이후 키 칩 자료 없음</t>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t>2022 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -7138,28 +7519,33 @@
           <t>확인 불가(2022 이후 스마트키 칩 자료 없음)</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="4" t="inlineStr">
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr">
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="N113" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1은 2021.12 생산분까지 — 이후 키 칩 자료 없음</t>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t>2022 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -7182,28 +7568,33 @@
           <t>확인 불가(2022 이후 스마트키 칩 자료 없음)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="4" t="inlineStr">
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈)</t>
         </is>
       </c>
-      <c r="M114" s="2" t="inlineStr">
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="N114" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1은 2021.12 생산분까지 — 이후 키 칩 자료 없음 / 2025.2부터 무쏘 스포츠·무쏘 칸으로 차명 변경</t>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>2022 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -7238,28 +7629,33 @@
           <t>ID47(Hitag3)</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="4" t="inlineStr">
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M115" s="2" t="inlineStr">
+      <c r="N115" s="2" t="inlineStr">
         <is>
           <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
         </is>
       </c>
-      <c r="N115" s="4" t="inlineStr">
-        <is>
-          <t>칩은 국내 열쇠기사 카페 자료(47칩) 기준 — 이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리(SKM) 기준 추정</t>
+      <c r="O115" s="4" t="inlineStr">
+        <is>
+          <t>이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7294,28 +7690,33 @@
           <t>ID47(Hitag3)</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="4" t="inlineStr">
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
         </is>
       </c>
-      <c r="N116" s="4" t="inlineStr">
-        <is>
-          <t>칩은 국내 열쇠기사 카페 자료(47칩) 기준 — 이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리(SKM) 기준 추정</t>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7350,28 +7751,33 @@
           <t>ID47(Hitag3)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="4" t="inlineStr">
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M117" s="2" t="inlineStr">
+      <c r="N117" s="2" t="inlineStr">
         <is>
           <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
         </is>
       </c>
-      <c r="N117" s="4" t="inlineStr">
-        <is>
-          <t>칩은 국내 열쇠기사 카페 자료(47칩) 기준 — 이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리(SKM) 기준 추정</t>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7406,28 +7812,33 @@
           <t>ID47(Hitag3)</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="4" t="inlineStr">
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
         </is>
       </c>
-      <c r="N118" s="4" t="inlineStr">
-        <is>
-          <t>칩은 국내 열쇠기사 카페 자료(47칩) 기준 — 이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리(SKM) 기준 추정</t>
+      <c r="O118" s="4" t="inlineStr">
+        <is>
+          <t>이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7462,28 +7873,33 @@
           <t>ID47(Hitag3)</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="4" t="inlineStr">
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈) 추정</t>
         </is>
       </c>
-      <c r="M119" s="2" t="inlineStr">
+      <c r="N119" s="2" t="inlineStr">
         <is>
           <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
         </is>
       </c>
-      <c r="N119" s="4" t="inlineStr">
-        <is>
-          <t>2026.5 뉴 토레스 페이스리프트 — 신형 키 칩 직접 자료 없음, 기존 47칩 기준</t>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>페이스리프트 신형 키 칩 자료 없음 — 기존 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7518,28 +7934,33 @@
           <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr">
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr">
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
-      <c r="N120" s="4" t="inlineStr">
-        <is>
-          <t>토레스 전기차 버전 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7574,28 +7995,33 @@
           <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="4" t="inlineStr">
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M121" s="2" t="inlineStr">
+      <c r="N121" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
-      <c r="N121" s="4" t="inlineStr">
-        <is>
-          <t>토레스 전기차 버전 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7630,28 +8056,33 @@
           <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="4" t="inlineStr">
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="N122" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
-      <c r="N122" s="4" t="inlineStr">
-        <is>
-          <t>토레스 전기차 버전 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7686,28 +8117,33 @@
           <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr">
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="4" t="inlineStr">
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M123" s="2" t="inlineStr">
+      <c r="N123" s="2" t="inlineStr">
         <is>
           <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
-      <c r="N123" s="4" t="inlineStr">
-        <is>
-          <t>토레스 전기차 버전 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7742,28 +8178,33 @@
           <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="4" t="inlineStr">
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M124" s="2" t="inlineStr">
+      <c r="N124" s="2" t="inlineStr">
         <is>
           <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
-      <c r="N124" s="4" t="inlineStr">
-        <is>
-          <t>토레스와 플랫폼 공유(2024.8 출시) — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7798,28 +8239,33 @@
           <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="4" t="inlineStr">
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M125" s="2" t="inlineStr">
+      <c r="N125" s="2" t="inlineStr">
         <is>
           <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
-      <c r="N125" s="4" t="inlineStr">
-        <is>
-          <t>토레스와 플랫폼 공유(2024.8 출시) — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7854,28 +8300,33 @@
           <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="4" t="inlineStr">
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M126" s="2" t="inlineStr">
+      <c r="N126" s="2" t="inlineStr">
         <is>
           <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
-      <c r="N126" s="4" t="inlineStr">
-        <is>
-          <t>토레스와 플랫폼 공유(2024.8 출시) — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7910,28 +8361,33 @@
           <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="4" t="inlineStr">
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
-      <c r="N127" s="4" t="inlineStr">
-        <is>
-          <t>원본 목록 2024~ — 실제 출시 2025.3 / 토레스 EVX 기반 픽업 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7966,28 +8422,33 @@
           <t>ID47(Hitag3) 추정(토레스 기준)</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr">
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="4" t="inlineStr">
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="4" t="inlineStr">
         <is>
           <t>SKM 추정</t>
         </is>
       </c>
-      <c r="M128" s="2" t="inlineStr">
+      <c r="N128" s="2" t="inlineStr">
         <is>
           <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
-      <c r="N128" s="4" t="inlineStr">
-        <is>
-          <t>토레스 EVX 기반 픽업 — 이 차종 키 칩 직접 자료 없음, 토레스 47칩 기준 추정</t>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8022,30 +8483,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
         <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="inlineStr">
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M129" s="2" t="inlineStr">
+      <c r="N129" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
-      <c r="N129" s="2" t="inlineStr">
-        <is>
-          <t>originalkey 순정 키 적용 범위가 2001년부터 — TMPro 이모박스 자료는 2002~</t>
-        </is>
-      </c>
+      <c r="O129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8078,26 +8540,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
         <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="inlineStr">
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M130" s="2" t="inlineStr">
+      <c r="N130" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
-      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8130,26 +8597,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
         <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="inlineStr">
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M131" s="2" t="inlineStr">
+      <c r="N131" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
-      <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8182,26 +8654,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr">
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M132" s="2" t="inlineStr">
+      <c r="N132" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
-      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8234,26 +8711,31 @@
           <t>ID48(Megamos Crypto)</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="inlineStr">
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr">
         <is>
           <t>VDO 이모빌라이저 박스(이모박스)</t>
         </is>
       </c>
-      <c r="M133" s="2" t="inlineStr">
+      <c r="N133" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
-      <c r="N133" s="2" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8286,30 +8768,31 @@
           <t>ID48(Megamos, 2006.1 이전 생산) / ID60(4D60, 2006.2 이후 생산)</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr">
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr">
         <is>
           <t>VDO 이모박스(2006.1 이전 생산) / 이모빌라이저 컨트롤 유닛 87110-08B00(2006.2 이후 생산)</t>
         </is>
       </c>
-      <c r="M134" s="2" t="inlineStr">
+      <c r="N134" s="2" t="inlineStr">
         <is>
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
-      <c r="N134" s="2" t="inlineStr">
-        <is>
-          <t>ICU 적용 2006.02~ — 이모박스(ID48)에서 ICU(4D60)로 전환</t>
-        </is>
-      </c>
+      <c r="O134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8342,34 +8825,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
+          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit) — 리모컨 일체형 막대키</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr"/>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit)</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
-      <c r="M135" s="2" t="inlineStr">
+      <c r="N135" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N135" s="2" t="inlineStr">
-        <is>
-          <t>2006.6 출시</t>
-        </is>
-      </c>
+      <c r="O135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8402,30 +8886,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
+          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit) — 리모컨 일체형 막대키</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit)</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr">
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
-      <c r="M136" s="2" t="inlineStr">
+      <c r="N136" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8458,30 +8947,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
+          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit) — 리모컨 일체형 막대키</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr"/>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit)</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
-      <c r="M137" s="2" t="inlineStr">
+      <c r="N137" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N137" s="2" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8514,30 +9008,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
+          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit) — 리모컨 일체형 막대키</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr"/>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit)</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
-      <c r="M138" s="2" t="inlineStr">
+      <c r="N138" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8570,30 +9069,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
+          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit) — 리모컨 일체형 막대키</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr"/>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit)</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
-      <c r="M139" s="2" t="inlineStr">
+      <c r="N139" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8626,30 +9130,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
+          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit) — 리모컨 일체형 막대키</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit)</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="inlineStr">
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
-      <c r="M140" s="2" t="inlineStr">
+      <c r="N140" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8682,30 +9191,35 @@
           <t>ID60(4D60, 40bit/80bit 키 병존)</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
+          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit) — 리모컨 일체형 막대키</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
           <t>SSY3 (JMA SSA-2P)</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr"/>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>87170-08B21(40bit, 액티언·렉스턴 2007-2013) / 87170-08D50(80bit)</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="inlineStr">
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
-      <c r="M141" s="2" t="inlineStr">
+      <c r="N141" s="2" t="inlineStr">
         <is>
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8738,38 +9252,43 @@
           <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
+          <t>2버튼 리모컨키(4D60x80, TOY40)</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
           <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
         <is>
           <t>스마트키 FCC DEO-MT FOBG02(4D70 DST80, 2013 사례)</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
-        </is>
-      </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
+          <t>3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
-      <c r="M142" s="2" t="inlineStr">
+      <c r="N142" s="2" t="inlineStr">
         <is>
           <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N142" s="2" t="inlineStr">
-        <is>
-          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
-        </is>
-      </c>
+      <c r="O142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8802,38 +9321,43 @@
           <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
+          <t>2버튼 리모컨키(4D60x80, TOY40)</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
           <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr">
         <is>
           <t>스마트키 FCC DEO-MT FOBG02(4D70 DST80, 2013 사례)</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
-        </is>
-      </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
+          <t>3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
-      <c r="M143" s="2" t="inlineStr">
+      <c r="N143" s="2" t="inlineStr">
         <is>
           <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N143" s="2" t="inlineStr">
-        <is>
-          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
-        </is>
-      </c>
+      <c r="O143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8866,38 +9390,43 @@
           <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
+          <t>2버튼 리모컨키(4D60x80, TOY40)</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
           <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr">
         <is>
           <t>스마트키 FCC DEO-MT FOBG02(4D70 DST80, 2013 사례)</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
-        </is>
-      </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
+          <t>3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
-      <c r="M144" s="2" t="inlineStr">
+      <c r="N144" s="2" t="inlineStr">
         <is>
           <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N144" s="2" t="inlineStr">
-        <is>
-          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
-        </is>
-      </c>
+      <c r="O144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8930,38 +9459,43 @@
           <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
+          <t>2버튼 리모컨키(4D60x80, TOY40)</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
           <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr">
         <is>
           <t>스마트키 FCC DEO-MT FOBG02(4D70 DST80, 2013 사례)</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
-        </is>
-      </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
+          <t>3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
-      <c r="M145" s="2" t="inlineStr">
+      <c r="N145" s="2" t="inlineStr">
         <is>
           <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N145" s="2" t="inlineStr">
-        <is>
-          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
-        </is>
-      </c>
+      <c r="O145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8994,38 +9528,43 @@
           <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
+          <t>2버튼 리모컨키(4D60x80, TOY40)</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
           <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr">
         <is>
           <t>스마트키 FCC DEO-MT FOBG02(4D70 DST80, 2013 사례)</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
-        </is>
-      </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
+          <t>3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
-      <c r="M146" s="2" t="inlineStr">
+      <c r="N146" s="2" t="inlineStr">
         <is>
           <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N146" s="2" t="inlineStr">
-        <is>
-          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
-        </is>
-      </c>
+      <c r="O146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9058,38 +9597,43 @@
           <t>4D60x80(TI 80bit) — 2버튼 리모컨키·폴딩키 / 스마트키 4D70 DST80</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
+          <t>2버튼 리모컨키(4D60x80, TOY40)</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
           <t>TOY40 (2버튼 리모컨키)</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr">
         <is>
           <t>스마트키 FCC DEO-MT FOBG02(4D70 DST80, 2013 사례)</t>
         </is>
       </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>2버튼 리모컨키(4D60x80, TOY40) / 3버튼 폴딩키(4D60x80, 2013~)</t>
-        </is>
-      </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
+          <t>3버튼 폴딩키(4D60x80, 2013~)</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
           <t>이모빌라이저 컨트롤 유닛(87110-08B00, ~2017.04)</t>
         </is>
       </c>
-      <c r="M147" s="2" t="inlineStr">
+      <c r="N147" s="2" t="inlineStr">
         <is>
           <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N147" s="2" t="inlineStr">
-        <is>
-          <t>키 종류가 여러 가지지만 모두 TI 80bit 계열 — 블레이드는 키 형태별로 확인</t>
-        </is>
-      </c>
+      <c r="O147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9122,30 +9666,31 @@
           <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2017.07~2020.11, 87510-36050/36550/36560 대체)</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="inlineStr">
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M148" s="2" t="inlineStr">
+      <c r="N148" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N148" s="2" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
-        </is>
-      </c>
+      <c r="O148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9178,30 +9723,31 @@
           <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2017.07~2020.11, 87510-36050/36550/36560 대체)</t>
         </is>
       </c>
-      <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="2" t="inlineStr">
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M149" s="2" t="inlineStr">
+      <c r="N149" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N149" s="2" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
-        </is>
-      </c>
+      <c r="O149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9234,30 +9780,31 @@
           <t>4D60x80(TI 80bit)</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2017.07~2020.11, 87510-36050/36550/36560 대체)</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="inlineStr">
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M150" s="2" t="inlineStr">
+      <c r="N150" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N150" s="2" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1 스마트키(티볼리와 동일 품목) 기준</t>
-        </is>
-      </c>
+      <c r="O150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9290,28 +9837,33 @@
           <t>4D60x80(2020.11 이전 생산) / 신형 키 8751036C20(2020.11 이후, 칩 미확인)</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (2017.07~2020.11, 87510-36050/36550/36560 대체) / 8751036C20(2020.11~)</t>
         </is>
       </c>
-      <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="4" t="inlineStr">
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M151" s="2" t="inlineStr">
+      <c r="N151" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N151" s="4" t="inlineStr">
-        <is>
-          <t>2020.11 페이스리프트 이후 스마트키 교체 — 신형 키(NXP 표기) 칩 자료 없음</t>
+      <c r="O151" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9334,28 +9886,33 @@
           <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr">
         <is>
           <t>8751036C20 (5버튼, 433MHz, 2020.11~2022.04 생산)</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="4" t="inlineStr">
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M152" s="2" t="inlineStr">
+      <c r="N152" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N152" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9378,28 +9935,33 @@
           <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr">
         <is>
           <t>8751036C20 (5버튼, 433MHz, 2020.11~2022.04 생산)</t>
         </is>
       </c>
-      <c r="K153" s="2" t="inlineStr"/>
-      <c r="L153" s="4" t="inlineStr">
+      <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M153" s="2" t="inlineStr">
+      <c r="N153" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N153" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
+      <c r="O153" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9422,28 +9984,33 @@
           <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="4" t="inlineStr">
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M154" s="2" t="inlineStr">
+      <c r="N154" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N154" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9466,28 +10033,33 @@
           <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="4" t="inlineStr">
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M155" s="2" t="inlineStr">
+      <c r="N155" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N155" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
+      <c r="O155" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9510,28 +10082,33 @@
           <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H156" s="2" t="inlineStr"/>
       <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="4" t="inlineStr">
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M156" s="2" t="inlineStr">
+      <c r="N156" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N156" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9554,28 +10131,33 @@
           <t>확인 불가(2020.11 이후 신형 스마트키, NXP 표기)</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr">
         <is>
           <t>스마트키(품번 미확인)</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="4" t="inlineStr">
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="4" t="inlineStr">
         <is>
           <t>SKM(스마트키 모듈 87570-36010, 2017.07~)</t>
         </is>
       </c>
-      <c r="M157" s="2" t="inlineStr">
+      <c r="N157" s="2" t="inlineStr">
         <is>
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="N157" s="4" t="inlineStr">
-        <is>
-          <t>SmartKeyMV1(4D60x80)은 2020.11까지 — 이후 신형 키 칩 자료 없음</t>
+      <c r="O157" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9598,24 +10180,29 @@
           <t>확인 불가</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="8" t="inlineStr">
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
       </c>
-      <c r="M158" s="2" t="inlineStr">
+      <c r="N158" s="2" t="inlineStr">
         <is>
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N158" s="8" t="inlineStr">
-        <is>
-          <t>이스타나 키 칩 자료 없음</t>
+      <c r="O158" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9638,24 +10225,29 @@
           <t>확인 불가</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="8" t="inlineStr">
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
       </c>
-      <c r="M159" s="2" t="inlineStr">
+      <c r="N159" s="2" t="inlineStr">
         <is>
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N159" s="8" t="inlineStr">
-        <is>
-          <t>이스타나 키 칩 자료 없음</t>
+      <c r="O159" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9678,24 +10270,29 @@
           <t>확인 불가</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="inlineStr"/>
       <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="8" t="inlineStr">
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
       </c>
-      <c r="M160" s="2" t="inlineStr">
+      <c r="N160" s="2" t="inlineStr">
         <is>
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N160" s="8" t="inlineStr">
-        <is>
-          <t>이스타나 키 칩 자료 없음</t>
+      <c r="O160" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9718,24 +10315,29 @@
           <t>확인 불가</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr"/>
       <c r="J161" s="2" t="inlineStr"/>
       <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="8" t="inlineStr">
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
       </c>
-      <c r="M161" s="2" t="inlineStr">
+      <c r="N161" s="2" t="inlineStr">
         <is>
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N161" s="8" t="inlineStr">
-        <is>
-          <t>이스타나 키 칩 자료 없음</t>
+      <c r="O161" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9758,24 +10360,29 @@
           <t>확인 불가</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="8" t="inlineStr">
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 확인 불가)</t>
         </is>
       </c>
-      <c r="M162" s="2" t="inlineStr">
+      <c r="N162" s="2" t="inlineStr">
         <is>
           <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
         </is>
       </c>
-      <c r="N162" s="8" t="inlineStr">
-        <is>
-          <t>이스타나 키 칩 자료 없음</t>
+      <c r="O162" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -9810,30 +10417,31 @@
           <t>ID60(4D60)</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>SSY3</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="2" t="inlineStr"/>
       <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="2" t="inlineStr">
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M163" s="2" t="inlineStr">
+      <c r="N163" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
-      <c r="N163" s="2" t="inlineStr">
-        <is>
-          <t>2004.9 출시</t>
-        </is>
-      </c>
+      <c r="O163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -9866,26 +10474,31 @@
           <t>ID60(4D60)</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>SSY3</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="inlineStr">
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M164" s="2" t="inlineStr">
+      <c r="N164" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
-      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -9918,26 +10531,31 @@
           <t>ID60(4D60)</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>SSY3</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="2" t="inlineStr"/>
       <c r="K165" s="2" t="inlineStr"/>
-      <c r="L165" s="2" t="inlineStr">
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M165" s="2" t="inlineStr">
+      <c r="N165" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
-      <c r="N165" s="2" t="inlineStr"/>
+      <c r="O165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9970,26 +10588,31 @@
           <t>ID60(4D60)</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>SSY3</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="inlineStr">
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M166" s="2" t="inlineStr">
+      <c r="N166" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
-      <c r="N166" s="2" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -10022,26 +10645,31 @@
           <t>ID60(4D60)</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>SSY3</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="2" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="2" t="inlineStr">
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M167" s="2" t="inlineStr">
+      <c r="N167" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
-      <c r="N167" s="2" t="inlineStr"/>
+      <c r="O167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -10074,26 +10702,31 @@
           <t>ID60(4D60)</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>SSY3</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="2" t="inlineStr">
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M168" s="2" t="inlineStr">
+      <c r="N168" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
-      <c r="N168" s="2" t="inlineStr"/>
+      <c r="O168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -10126,26 +10759,31 @@
           <t>ID60(4D60)</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>SSY3</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
       <c r="J169" s="2" t="inlineStr"/>
       <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="2" t="inlineStr">
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
-      <c r="N169" s="2" t="inlineStr"/>
+      <c r="O169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -10178,26 +10816,31 @@
           <t>ID60(4D60)</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>SSY3</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
       <c r="J170" s="2" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="inlineStr">
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M170" s="2" t="inlineStr">
+      <c r="N170" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
-      <c r="N170" s="2" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -10230,32 +10873,37 @@
           <t>ID60(4D60, 1세대 키) / 4D60x80(TI 80bit, 로디우스 II 폴딩키)</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>막대키,폴딩키</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>SSY3 / TOY48·KI-7</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr"/>
       <c r="J171" s="2" t="inlineStr"/>
-      <c r="K171" s="2" t="inlineStr">
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (로디우스 II, 3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L171" s="4" t="inlineStr">
+      <c r="M171" s="4" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M171" s="2" t="inlineStr">
+      <c r="N171" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N171" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 로디우스 II(2012~) 폴딩키는 ID70 — 1세대 키와 구분</t>
+      <c r="O171" s="4" t="inlineStr">
+        <is>
+          <t>1세대 키(4D60)와 로디우스 II 폴딩키(4D60x80) 병존 — 키로 구분 필요</t>
         </is>
       </c>
     </row>
@@ -10290,32 +10938,37 @@
           <t>ID60(4D60, 1세대 키) / 4D60x80(TI 80bit, 로디우스 II 폴딩키)</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>막대키,폴딩키</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>SSY3 / TOY48·KI-7</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr"/>
-      <c r="K172" s="2" t="inlineStr">
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (로디우스 II, 3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L172" s="4" t="inlineStr">
+      <c r="M172" s="4" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M172" s="2" t="inlineStr">
+      <c r="N172" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N172" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 로디우스 II(2012~) 폴딩키는 ID70 — 1세대 키와 구분</t>
+      <c r="O172" s="4" t="inlineStr">
+        <is>
+          <t>1세대 키(4D60)와 로디우스 II 폴딩키(4D60x80) 병존 — 키로 구분 필요</t>
         </is>
       </c>
     </row>
@@ -10352,36 +11005,37 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="2" t="inlineStr"/>
-      <c r="K173" s="2" t="inlineStr">
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L173" s="2" t="inlineStr">
+      <c r="M173" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M173" s="2" t="inlineStr">
+      <c r="N173" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
-        </is>
-      </c>
+      <c r="O173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -10416,36 +11070,37 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="2" t="inlineStr">
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L174" s="2" t="inlineStr">
+      <c r="M174" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M174" s="2" t="inlineStr">
+      <c r="N174" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N174" s="2" t="inlineStr">
-        <is>
-          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
-        </is>
-      </c>
+      <c r="O174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -10480,40 +11135,41 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (로디우스/스타빅 II 2015.06~2019.03)</t>
         </is>
       </c>
-      <c r="K175" s="2" t="inlineStr">
+      <c r="L175" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L175" s="2" t="inlineStr">
+      <c r="M175" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="N175" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
-        </is>
-      </c>
+      <c r="O175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10548,40 +11204,41 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (로디우스/스타빅 II 2015.06~2019.03)</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr">
+      <c r="L176" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L176" s="2" t="inlineStr">
+      <c r="M176" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M176" s="2" t="inlineStr">
+      <c r="N176" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N176" s="2" t="inlineStr">
-        <is>
-          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
-        </is>
-      </c>
+      <c r="O176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -10616,40 +11273,41 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (로디우스/스타빅 II 2015.06~2019.03)</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr">
+      <c r="L177" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L177" s="2" t="inlineStr">
+      <c r="M177" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M177" s="2" t="inlineStr">
+      <c r="N177" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N177" s="2" t="inlineStr">
-        <is>
-          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
-        </is>
-      </c>
+      <c r="O177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10684,43 +11342,44 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr">
         <is>
           <t>R-C-2CG-SmartKeyMV1 (로디우스/스타빅 II 2015.06~2019.03)</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr">
+      <c r="L178" s="2" t="inlineStr">
         <is>
           <t>87510-21100 (3버튼 폴딩키)</t>
         </is>
       </c>
-      <c r="L178" s="2" t="inlineStr">
+      <c r="M178" s="2" t="inlineStr">
         <is>
           <t>이모빌라이저(모듈 명칭 미확인)</t>
         </is>
       </c>
-      <c r="M178" s="2" t="inlineStr">
+      <c r="N178" s="2" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="N178" s="2" t="inlineStr">
-        <is>
-          <t>로디우스 II(=코란도 투리스모) — 폴딩키 칩 확인, 스마트키는 SmartKeyMV1</t>
-        </is>
-      </c>
+      <c r="O178" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N178"/>
+  <autoFilter ref="A1:O178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10731,7 +11390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -10757,144 +11416,165 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
+          <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>- 칼리스타(1993-1997)·코란도 훼미리(1988-1996)는 2000년식 이전에 단종되어 행이 없습니다.</t>
+          <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>- 원본 목록 연식이 실제와 다른 모델은 실제 기준으로 적고 비고에 적었습니다(체어맨 H ~2014, 체어맨 W ~2017, 코란도 e-모션 2022~2023, 무쏘 EV 2025~, 렉스턴 스포츠는 2025.2 무쏘 스포츠로 차명 변경).</t>
+          <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>- '이모빌라이저 시스템': 구형은 VDO 이모빌라이저 박스(이모박스), 액티언·카이런·렉스턴 계열은 이모빌라이저 컨트롤 유닛(ICU, 87110-08B00/09000), 신형 스마트키 차량은 SKM(스마트키 모듈)입니다.</t>
+          <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>- 폴딩키(리모컨 일체형) 품번은 '폴딩키(부품번호)', 스마트키 트랜스미터 품번은 '스마트키(부품번호)' 칸에 적었습니다. 쌍용은 카드키가 없어 카드키 칸은 비었습니다.</t>
+          <t>- 칼리스타(1993-1997)·코란도 훼미리(1988-1996)는 2000년식 이전에 단종되어 행이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID60(4D60)·ID70/DST80(4D70) → O/O/O, ID48(Megamos Crypto) → △/△/△, ID48·ID60 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
+          <t>- 원본 목록 연식이 실제와 다른 모델은 실제 기준으로 적었습니다(체어맨 H ~2014, 체어맨 W ~2017, 코란도 e-모션 2022~2023, 무쏘 EV 2025~, 렉스턴 스포츠는 2025.2 무쏘 스포츠로 차명 변경).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
+          <t>- '이모빌라이저 시스템': 구형은 VDO 이모빌라이저 박스(이모박스), 액티언·카이런·렉스턴 계열은 이모빌라이저 컨트롤 유닛(ICU, 87110-08B00/09000), 신형 스마트키 차량은 SKM(스마트키 모듈)입니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>- 폴딩키(리모컨 일체형) 품번은 '폴딩키(부품번호)', 스마트키 트랜스미터 품번은 '스마트키(부품번호)' 칸에 적었습니다. 쌍용은 카드키가 없어 카드키 칸은 비었습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>※ 색상</t>
+          <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID60(4D60)·ID70/DST80(4D70) → O/O/O, ID48(Megamos Crypto) → △/△/△, ID48·ID60 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>- 빨간색: 확인 불가 — 이스타나는 키 칩 자료를 찾지 못했습니다.</t>
+          <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>- 주황색: 추정이거나 자료가 서로 다르거나 연식 범위 밖인 값 — 실물 키/VIN으로 재확인.</t>
-        </is>
-      </c>
+      <c r="A14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>※ 색상</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>※ 조사하며 확인된 주요 사항</t>
+          <t>- 빨간색: 확인 불가 — 이스타나는 키 칩 자료를 찾지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>- 무쏘·코란도·렉스턴(2002-2006): VDO 이모박스(MCU MC68HC05B16) + 메가모스 크립토(ID48) 트랜스폰더 — TMPro 모듈 85 자료. 코란도 2000-2006 블레이드 HYN10(JMA HY-5.P1).</t>
+          <t>- 주황색: 추정이거나 자료가 서로 다르거나 연식 범위 밖인 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>- 액티언·카이런·렉스턴 계열: 4D-60 칩 키, 블레이드 SSY3(JMA SSA-2P). 순정 키 87170-32030·32020·08D50은 80bit, 87170-08B21은 40bit — 연식 구분 자료가 없어 키 품번으로 확인해야 합니다.</t>
-        </is>
-      </c>
+      <c r="A18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>- 이모빌라이저 컨트롤 유닛(87110-08B00/09000) 적용: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언 스포츠 2006.04~2007.03. 2007.4 이후 카이런·액티언 계열의 모듈 명칭은 확인하지 못했습니다.</t>
+          <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>- 순정 3버튼 폴딩키 87510-21100(코란도 C·로디우스 II/코란도 투리스모·티볼리 등): 80bit TI 칩(판매처 표기 ID70 DST80 / ID8E). 블레이드는 TOY48(remkeys)과 KI-7(3D Group, 블레이드 품번 7105121500)로 표기가 다릅니다.</t>
+          <t>- 무쏘·코란도·렉스턴(2002-2006): VDO 이모박스(MCU MC68HC05B16) + 메가모스 크립토(ID48) 트랜스폰더 — TMPro 모듈 85 자료. 코란도 2000-2006 블레이드 HYN10(JMA HY-5.P1).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>- [재조사] 토레스 스마트키 칩은 47칩(ID47, Hitag3) — 국내 열쇠기사 카페 자료. 토레스 EVX·액티언(J120)·무쏘 EV는 같은 플랫폼이라 동일 추정(주황).</t>
+          <t>- 액티언·카이런·렉스턴 계열: 4D-60 칩 키, 블레이드 SSY3(JMA SSA-2P). 순정 키 87170-32030·32020·08D50은 80bit, 87170-08B21은 40bit — 연식 구분 자료가 없어 키 품번으로 확인해야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>- [재조사] 코란도 C(러시아명 New Actyon) 순정 스마트키 4D60x80·비상키 TOY48, 스타빅·액티언·티볼리·렉스턴 순정 폴딩키(2013-2021) 4D60x80, 렉스턴 W 2버튼 키 4D60x80·TOY40.</t>
+          <t>- 이모빌라이저 컨트롤 유닛(87110-08B00/09000) 적용: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언 스포츠 2006.04~2007.03. 2007.4 이후 카이런·액티언 계열의 모듈 명칭은 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>- [재조사] 순정 스마트키 R-C-2CG-SmartKeyMV1(4D60x80, 433MHz): 티볼리 2015.03~2020.01, 렉스턴 스포츠 2018.03~2021.12, G4 렉스턴 2017.07~2020.11, 로디우스/스타빅 II 2015.06~2019.03. 이후 신형 키(G4 2020.11~ 8751036C20 등)는 칩 자료 없음(주황).</t>
+          <t>- 순정 3버튼 폴딩키 87510-21100(코란도 C·로디우스 II/코란도 투리스모·티볼리 등): 80bit TI 칩(판매처 표기 ID70 DST80 / ID8E). 블레이드는 TOY48(remkeys)과 KI-7(3D Group, 블레이드 품번 7105121500)로 표기가 다릅니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>- [재조사] 코란도 C(C200) 이모빌라이저는 SKM(키 슬롯)과 엔진 ECU(EMS)가 P-CAN으로 인증. 액티언 2008~2011도 별도 이모빌라이저 컨트롤 유닛 사용(품번 변경).</t>
+          <t>- [재조사] 토레스 스마트키 칩은 47칩(ID47, Hitag3) — 국내 열쇠기사 카페 자료. 토레스 EVX·액티언(J120)·무쏘 EV는 같은 플랫폼이라 동일 추정(주황).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>- [재조사] 코란도 C(러시아명 New Actyon) 순정 스마트키 4D60x80·비상키 TOY48, 스타빅·액티언·티볼리·렉스턴 순정 폴딩키(2013-2021) 4D60x80, 렉스턴 W 2버튼 키 4D60x80·TOY40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>- [재조사] 순정 스마트키 R-C-2CG-SmartKeyMV1(4D60x80, 433MHz): 티볼리 2015.03~2020.01, 렉스턴 스포츠 2018.03~2021.12, G4 렉스턴 2017.07~2020.11, 로디우스/스타빅 II 2015.06~2019.03. 이후 신형 키(G4 2020.11~ 8751036C20 등)는 칩 자료 없음(주황).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>- [재조사] 코란도 C(C200) 이모빌라이저는 SKM(키 슬롯)과 엔진 ECU(EMS)가 P-CAN으로 인증. 액티언 2008~2011도 별도 이모빌라이저 컨트롤 유닛 사용(품번 변경).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>- 코란도 C300 스마트키 DST80·HYN14R, 렉스턴 W 2013 스마트키 4D70 DST80(FCC DEO-MT FOBG02), G4 렉스턴 이모빌라이저 = SKM(87570-36010, 2017.07~).</t>
         </is>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -129,16 +129,16 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -150,10 +150,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,7 +540,7 @@
     <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>모델명</t>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -166,6 +166,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3350,7 +3353,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>4D60x80</t>
         </is>
@@ -3369,9 +3372,9 @@
       <c r="K44" s="11" t="inlineStr"/>
       <c r="L44" s="11" t="n"/>
       <c r="M44" s="11" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>SKM[추정]</t>
+      <c r="N44" s="14" t="inlineStr">
+        <is>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O44" s="11" t="inlineStr">
@@ -3379,11 +3382,7 @@
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="P44" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
-        </is>
-      </c>
+      <c r="P44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -3416,7 +3415,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>4D60x80</t>
         </is>
@@ -3435,9 +3434,9 @@
       <c r="K45" s="11" t="inlineStr"/>
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="11" t="inlineStr"/>
-      <c r="N45" s="4" t="inlineStr">
-        <is>
-          <t>SKM[추정]</t>
+      <c r="N45" s="14" t="inlineStr">
+        <is>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr">
@@ -3445,11 +3444,7 @@
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="P45" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
-        </is>
-      </c>
+      <c r="P45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -3482,7 +3477,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>4D60x80</t>
         </is>
@@ -3501,9 +3496,9 @@
       <c r="K46" s="11" t="inlineStr"/>
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="11" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>SKM[추정]</t>
+      <c r="N46" s="14" t="inlineStr">
+        <is>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O46" s="11" t="inlineStr">
@@ -3511,11 +3506,7 @@
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="P46" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
-        </is>
-      </c>
+      <c r="P46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -3548,7 +3539,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>4D60x80</t>
         </is>
@@ -3567,9 +3558,9 @@
       <c r="K47" s="11" t="inlineStr"/>
       <c r="L47" s="11" t="n"/>
       <c r="M47" s="11" t="inlineStr"/>
-      <c r="N47" s="4" t="inlineStr">
-        <is>
-          <t>SKM[추정]</t>
+      <c r="N47" s="14" t="inlineStr">
+        <is>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
@@ -3577,11 +3568,7 @@
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="P47" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
-        </is>
-      </c>
+      <c r="P47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -3614,7 +3601,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>4D60x80</t>
         </is>
@@ -3633,9 +3620,9 @@
       <c r="K48" s="11" t="inlineStr"/>
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="11" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr">
-        <is>
-          <t>SKM[추정]</t>
+      <c r="N48" s="14" t="inlineStr">
+        <is>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O48" s="11" t="inlineStr">
@@ -3643,11 +3630,7 @@
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="P48" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
-        </is>
-      </c>
+      <c r="P48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -3680,7 +3663,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>4D60x80</t>
         </is>
@@ -3699,9 +3682,9 @@
       <c r="K49" s="11" t="inlineStr"/>
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="11" t="inlineStr"/>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>SKM[추정]</t>
+      <c r="N49" s="14" t="inlineStr">
+        <is>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
@@ -3709,11 +3692,7 @@
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="P49" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
-        </is>
-      </c>
+      <c r="P49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -3746,7 +3725,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>4D60x80</t>
         </is>
@@ -3765,9 +3744,9 @@
       <c r="K50" s="11" t="inlineStr"/>
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="11" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>SKM[추정]</t>
+      <c r="N50" s="14" t="inlineStr">
+        <is>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O50" s="11" t="inlineStr">
@@ -3775,11 +3754,7 @@
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="P50" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
-        </is>
-      </c>
+      <c r="P50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -3812,7 +3787,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="14" t="inlineStr">
         <is>
           <t>4D60x80</t>
         </is>
@@ -3831,9 +3806,9 @@
       <c r="K51" s="11" t="inlineStr"/>
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="11" t="inlineStr"/>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>SKM[추정]</t>
+      <c r="N51" s="14" t="inlineStr">
+        <is>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
@@ -3841,11 +3816,7 @@
           <t>carkeyhelper.com(코란도 Mk4 C300 2019- 스마트키 DST80, HYN14R), ebay(2020-2022 코란도 스마트키 트랜스미터 / 2023-2024 KGM 코란도 스마트키)</t>
         </is>
       </c>
-      <c r="P51" s="4" t="inlineStr">
-        <is>
-          <t>칩·블레이드 해외 판매처 1곳 기준, 이모빌라이저 명칭은 티볼리·G4 렉스턴 기준 추정</t>
-        </is>
-      </c>
+      <c r="P51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -8135,7 +8106,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리 기준 추정</t>
+          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8168,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리 기준 추정</t>
+          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8230,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리 기준 추정</t>
+          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8292,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈 명칭은 G4 렉스턴·티볼리 기준 추정</t>
+          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8354,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>페이스리프트 신형 키 칩 자료 없음 — 기존 47칩 기준 추정</t>
+          <t>토레스 하이브리드부터 스마트키 변경 — 신형 키 칩 자료 없음(기존 47칩 기준 추정)</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10394,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
+          <t>2020.11 이후 생산분 신형 스마트키(NXP 부품 표기) 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10477,7 +10448,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10502,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10581,7 +10552,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10602,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10652,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10702,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2020.11 이후 신형 스마트키 칩 자료 없음</t>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -12076,191 +12047,191 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr"/>
+      <c r="A2" s="13" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>- 칼리스타(1993-1997)·코란도 훼미리(1988-1996)는 2000년식 이전에 단종되어 행이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제와 다른 모델은 실제 기준으로 적었습니다(체어맨 H ~2014, 체어맨 W ~2017, 코란도 e-모션 2022~2023, 무쏘 EV 2025~, 렉스턴 스포츠는 2025.2 무쏘 스포츠로 차명 변경).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 구형은 VDO 이모빌라이저 박스(이모박스), 액티언·카이런·렉스턴 계열은 이모빌라이저 컨트롤 유닛(ICU, 87110-08B00/09000), 신형 스마트키 차량은 SKM(스마트키 모듈)입니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>- 폴딩키(리모컨 일체형) 품번은 '폴딩키(부품번호)', 스마트키 트랜스미터 품번은 '스마트키(부품번호)' 칸에 적었습니다. 쌍용은 카드키가 없어 카드키 칸은 비었습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID60(4D60)·ID70/DST80(4D70) → O/O/O, ID48(Megamos Crypto) → △/△/△, ID48·ID60 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — 이스타나는 키 칩 자료를 찾지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나 연식 범위 밖인 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>- 무쏘·코란도·렉스턴(2002-2006): VDO 이모박스(MCU MC68HC05B16) + 메가모스 크립토(ID48) 트랜스폰더 — TMPro 모듈 85 자료. 코란도 2000-2006 블레이드 HYN10(JMA HY-5.P1).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>- 액티언·카이런·렉스턴 계열: 4D-60 칩 키, 블레이드 SSY3(JMA SSA-2P). 순정 키 87170-32030·32020·08D50은 80bit, 87170-08B21은 40bit — 연식 구분 자료가 없어 키 품번으로 확인해야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>- 이모빌라이저 컨트롤 유닛(87110-08B00/09000) 적용: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언 스포츠 2006.04~2007.03. 2007.4 이후 카이런·액티언 계열의 모듈 명칭은 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>- 순정 3버튼 폴딩키 87510-21100(코란도 C·로디우스 II/코란도 투리스모·티볼리 등): 80bit TI 칩(판매처 표기 ID70 DST80 / ID8E). 블레이드는 TOY48(remkeys)과 KI-7(3D Group, 블레이드 품번 7105121500)로 표기가 다릅니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>- [재조사] 토레스 스마트키 칩은 47칩(ID47, Hitag3) — 국내 열쇠기사 카페 자료. 토레스 EVX·액티언(J120)·무쏘 EV는 같은 플랫폼이라 동일 추정(주황).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>- [재조사] 코란도 C(러시아명 New Actyon) 순정 스마트키 4D60x80·비상키 TOY48, 스타빅·액티언·티볼리·렉스턴 순정 폴딩키(2013-2021) 4D60x80, 렉스턴 W 2버튼 키 4D60x80·TOY40.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>- [재조사] 순정 스마트키 R-C-2CG-SmartKeyMV1(4D60x80, 433MHz): 티볼리 2015.03~2020.01, 렉스턴 스포츠 2018.03~2021.12, G4 렉스턴 2017.07~2020.11, 로디우스/스타빅 II 2015.06~2019.03. 이후 신형 키(G4 2020.11~ 8751036C20 등)는 칩 자료 없음(주황).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>- [재조사] 코란도 C(C200) 이모빌라이저는 SKM(키 슬롯)과 엔진 ECU(EMS)가 P-CAN으로 인증. 액티언 2008~2011도 별도 이모빌라이저 컨트롤 유닛 사용(품번 변경).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>- 코란도 C300 스마트키 DST80·HYN14R, 렉스턴 W 2013 스마트키 4D70 DST80(FCC DEO-MT FOBG02), G4 렉스턴 이모빌라이저 = SKM(87570-36010, 2017.07~).</t>
         </is>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -169,6 +169,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P178"/>
+  <dimension ref="A1:P183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5921,12 +5927,12 @@
           <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
-      <c r="K82" s="11" t="inlineStr"/>
-      <c r="L82" s="11" t="inlineStr"/>
-      <c r="M82" s="11" t="inlineStr"/>
+      <c r="K82" s="11" t="n"/>
+      <c r="L82" s="11" t="n"/>
+      <c r="M82" s="11" t="n"/>
       <c r="N82" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[2007.3 이전 생산], 이모빌라이저 컨트롤 유닛(87110-09000)[2007.3 이전 생산], 이모빌라이저 컨트롤 유닛[2007.4 이후 생산, 변경 품번]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[2007.3 이전 생산], 이모빌라이저 컨트롤 유닛(87110-09000)[2007.3 이전 생산]</t>
         </is>
       </c>
       <c r="O82" s="11" t="inlineStr">
@@ -5934,7 +5940,7 @@
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="P82" s="11" t="inlineStr"/>
+      <c r="P82" s="11" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
@@ -5949,7 +5955,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -5987,12 +5993,12 @@
           <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
-      <c r="K83" s="11" t="inlineStr"/>
-      <c r="L83" s="11" t="inlineStr"/>
-      <c r="M83" s="11" t="inlineStr"/>
+      <c r="K83" s="11" t="n"/>
+      <c r="L83" s="11" t="n"/>
+      <c r="M83" s="11" t="n"/>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
+          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 생산, 변경 품번]</t>
         </is>
       </c>
       <c r="O83" s="11" t="inlineStr">
@@ -6000,7 +6006,7 @@
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="P83" s="11" t="inlineStr"/>
+      <c r="P83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
@@ -6015,7 +6021,7 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -6081,7 +6087,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -6147,7 +6153,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>2011(단종)</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -6208,12 +6214,12 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>액티언 스포츠 (픽업)</t>
+          <t>액티언 (1세대)</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2011(단종)</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -6256,12 +6262,12 @@
       <c r="M87" s="11" t="inlineStr"/>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00), 이모빌라이저 컨트롤 유닛(87110-09000)</t>
+          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
         </is>
       </c>
       <c r="O87" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
       <c r="P87" s="11" t="inlineStr"/>
@@ -6279,7 +6285,7 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -6322,12 +6328,12 @@
       <c r="M88" s="11" t="inlineStr"/>
       <c r="N88" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[2007.3 이전 생산], 이모빌라이저 컨트롤 유닛(87110-09000)[2007.3 이전 생산], 이모빌라이저 컨트롤 유닛[2007.4 이후 생산, 변경 품번]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00), 이모빌라이저 컨트롤 유닛(87110-09000)</t>
         </is>
       </c>
       <c r="O88" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="P88" s="11" t="inlineStr"/>
@@ -6345,7 +6351,7 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -6383,12 +6389,12 @@
           <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
-      <c r="K89" s="11" t="inlineStr"/>
-      <c r="L89" s="11" t="inlineStr"/>
-      <c r="M89" s="11" t="inlineStr"/>
+      <c r="K89" s="11" t="n"/>
+      <c r="L89" s="11" t="n"/>
+      <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[2007.3 이전 생산], 이모빌라이저 컨트롤 유닛(87110-09000)[2007.3 이전 생산]</t>
         </is>
       </c>
       <c r="O89" s="11" t="inlineStr">
@@ -6396,7 +6402,7 @@
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="P89" s="11" t="inlineStr"/>
+      <c r="P89" s="11" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
@@ -6411,7 +6417,7 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -6449,12 +6455,12 @@
           <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
-      <c r="K90" s="11" t="inlineStr"/>
-      <c r="L90" s="11" t="inlineStr"/>
-      <c r="M90" s="11" t="inlineStr"/>
+      <c r="K90" s="11" t="n"/>
+      <c r="L90" s="11" t="n"/>
+      <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
+          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 생산, 변경 품번]</t>
         </is>
       </c>
       <c r="O90" s="11" t="inlineStr">
@@ -6462,7 +6468,7 @@
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="P90" s="11" t="inlineStr"/>
+      <c r="P90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
@@ -6477,7 +6483,7 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -6543,7 +6549,7 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -6609,7 +6615,7 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>2012(단종)</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -6670,12 +6676,12 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>카이런</t>
+          <t>액티언 스포츠 (픽업)</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -6718,12 +6724,12 @@
       <c r="M94" s="11" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00), 이모빌라이저 컨트롤 유닛(87110-09000)</t>
+          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
         </is>
       </c>
       <c r="O94" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
       <c r="P94" s="11" t="inlineStr"/>
@@ -6736,12 +6742,12 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>카이런</t>
+          <t>액티언 스포츠 (픽업)</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2012(단종)</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -6784,12 +6790,12 @@
       <c r="M95" s="11" t="inlineStr"/>
       <c r="N95" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00), 이모빌라이저 컨트롤 유닛(87110-09000)</t>
+          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
         </is>
       </c>
       <c r="O95" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
       <c r="P95" s="11" t="inlineStr"/>
@@ -6807,7 +6813,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -6850,12 +6856,12 @@
       <c r="M96" s="11" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[2007.3 이전 생산], 이모빌라이저 컨트롤 유닛(87110-09000)[2007.3 이전 생산], 이모빌라이저 컨트롤 유닛[2007.4 이후 생산, 변경 품번]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00), 이모빌라이저 컨트롤 유닛(87110-09000)</t>
         </is>
       </c>
       <c r="O96" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="P96" s="11" t="inlineStr"/>
@@ -6873,7 +6879,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -6916,12 +6922,12 @@
       <c r="M97" s="11" t="inlineStr"/>
       <c r="N97" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00), 이모빌라이저 컨트롤 유닛(87110-09000)</t>
         </is>
       </c>
       <c r="O97" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="P97" s="11" t="inlineStr"/>
@@ -6939,7 +6945,7 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -6977,12 +6983,12 @@
           <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
-      <c r="K98" s="11" t="inlineStr"/>
-      <c r="L98" s="11" t="inlineStr"/>
-      <c r="M98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="11" t="n"/>
       <c r="N98" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[2007.3 이전 생산], 이모빌라이저 컨트롤 유닛(87110-09000)[2007.3 이전 생산]</t>
         </is>
       </c>
       <c r="O98" s="11" t="inlineStr">
@@ -6990,7 +6996,7 @@
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="P98" s="11" t="inlineStr"/>
+      <c r="P98" s="11" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
@@ -7005,7 +7011,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -7043,12 +7049,12 @@
           <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
-      <c r="K99" s="11" t="inlineStr"/>
-      <c r="L99" s="11" t="inlineStr"/>
-      <c r="M99" s="11" t="inlineStr"/>
+      <c r="K99" s="11" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="11" t="n"/>
       <c r="N99" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
+          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 생산, 변경 품번]</t>
         </is>
       </c>
       <c r="O99" s="11" t="inlineStr">
@@ -7056,7 +7062,7 @@
           <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
-      <c r="P99" s="11" t="inlineStr"/>
+      <c r="P99" s="11" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
@@ -7071,7 +7077,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>2011(단종)</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -7132,12 +7138,12 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>코란도 스포츠 (픽업)</t>
+          <t>카이런</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -7155,52 +7161,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>4D60x80[추정]</t>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>7105121500</t>
+          <t>87170-32030[80bit], 87170-32020[80bit], 87170-08B21[40bit]</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>TOY48[자료 상충], KI-7[자료 상충]</t>
+          <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr"/>
-      <c r="L101" s="11" t="inlineStr">
-        <is>
-          <t>8751008010[2012~2018], 8751032021[15년형~]</t>
-        </is>
-      </c>
-      <c r="M101" s="11" t="inlineStr">
-        <is>
-          <t>87510-21100[3버튼]</t>
-        </is>
-      </c>
-      <c r="N101" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저</t>
+      <c r="L101" s="11" t="inlineStr"/>
+      <c r="M101" s="11" t="inlineStr"/>
+      <c r="N101" s="11" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
         </is>
       </c>
       <c r="O101" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
-        </is>
-      </c>
-      <c r="P101" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 자료가 2014.01부터 — 2012·2013년식 직접 확인 안 됨</t>
-        </is>
-      </c>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="P101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
@@ -7210,12 +7204,12 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>코란도 스포츠 (픽업)</t>
+          <t>카이런</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -7233,52 +7227,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>4D60x80[추정]</t>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>7105121500</t>
+          <t>87170-32030[80bit], 87170-32020[80bit], 87170-08B21[40bit]</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
         <is>
-          <t>TOY48[자료 상충], KI-7[자료 상충]</t>
+          <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr"/>
-      <c r="L102" s="11" t="inlineStr">
-        <is>
-          <t>8751008010[2012~2018], 8751032021[15년형~]</t>
-        </is>
-      </c>
-      <c r="M102" s="11" t="inlineStr">
-        <is>
-          <t>87510-21100[3버튼]</t>
-        </is>
-      </c>
-      <c r="N102" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저</t>
+      <c r="L102" s="11" t="inlineStr"/>
+      <c r="M102" s="11" t="inlineStr"/>
+      <c r="N102" s="11" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
         </is>
       </c>
       <c r="O102" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
-        </is>
-      </c>
-      <c r="P102" s="4" t="inlineStr">
-        <is>
-          <t>폴딩키 자료가 2014.01부터 — 2012·2013년식 직접 확인 안 됨</t>
-        </is>
-      </c>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
+        </is>
+      </c>
+      <c r="P102" s="11" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
@@ -7288,12 +7270,12 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>코란도 스포츠 (픽업)</t>
+          <t>카이런</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2011(단종)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -7313,43 +7295,35 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>4D60x80</t>
+          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>7105121500</t>
+          <t>87170-32030[80bit], 87170-32020[80bit], 87170-08B21[40bit]</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>TOY48[자료 상충], KI-7[자료 상충]</t>
+          <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr"/>
-      <c r="L103" s="11" t="inlineStr">
-        <is>
-          <t>8751008010[2012~2018], 8751032021[15년형~]</t>
-        </is>
-      </c>
-      <c r="M103" s="11" t="inlineStr">
-        <is>
-          <t>87510-21100[3버튼]</t>
-        </is>
-      </c>
+      <c r="L103" s="11" t="inlineStr"/>
+      <c r="M103" s="11" t="inlineStr"/>
       <c r="N103" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저</t>
+          <t>이모빌라이저 컨트롤 유닛[2007.4 이후 변경 품번]</t>
         </is>
       </c>
       <c r="O103" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅 트랜스폰더키 SSY3), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키), [재조사] ebay(쌍용 액티언 2008-2011 순정 이모빌라이저 컨트롤 유닛), manualslib(2008 액티언 정비지침서: 키 박스의 이모빌라이저 유닛이 트랜스폰더 확인 후 ECU에 승인 전달)</t>
         </is>
       </c>
       <c r="P103" s="11" t="inlineStr"/>
@@ -7367,7 +7341,7 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -7385,9 +7359,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
-        <is>
-          <t>4D60x80</t>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>4D60x80[추정]</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
@@ -7416,7 +7390,7 @@
           <t>87510-21100[3버튼]</t>
         </is>
       </c>
-      <c r="N104" s="11" t="inlineStr">
+      <c r="N104" s="4" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
@@ -7426,7 +7400,11 @@
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
-      <c r="P104" s="11" t="inlineStr"/>
+      <c r="P104" s="4" t="inlineStr">
+        <is>
+          <t>폴딩키 자료가 2014.01부터 — 2012·2013년식 직접 확인 안 됨</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
@@ -7441,7 +7419,7 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -7459,9 +7437,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
-        <is>
-          <t>4D60x80</t>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>4D60x80[추정]</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -7490,7 +7468,7 @@
           <t>87510-21100[3버튼]</t>
         </is>
       </c>
-      <c r="N105" s="11" t="inlineStr">
+      <c r="N105" s="4" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
@@ -7500,7 +7478,11 @@
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
-      <c r="P105" s="11" t="inlineStr"/>
+      <c r="P105" s="4" t="inlineStr">
+        <is>
+          <t>폴딩키 자료가 2014.01부터 — 2012·2013년식 직접 확인 안 됨</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
@@ -7515,7 +7497,7 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -7589,7 +7571,7 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -7658,12 +7640,12 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 스포츠 &amp; 칸 (픽업)</t>
+          <t>코란도 스포츠 (픽업)</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -7688,26 +7670,38 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I108" s="11" t="inlineStr"/>
-      <c r="J108" s="11" t="inlineStr"/>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>7105121500</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[자료 상충], KI-7[자료 상충]</t>
+        </is>
+      </c>
       <c r="K108" s="11" t="inlineStr"/>
       <c r="L108" s="11" t="inlineStr">
         <is>
-          <t>KC R-C-2CG-SmartKeyMV1[2018.03~2021.12], 8751036B00[무쏘 스포츠, 2019~2021]</t>
-        </is>
-      </c>
-      <c r="M108" s="11" t="inlineStr"/>
+          <t>8751008010[2012~2018], 8751032021[15년형~]</t>
+        </is>
+      </c>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>87510-21100[3버튼]</t>
+        </is>
+      </c>
       <c r="N108" s="11" t="inlineStr">
         <is>
-          <t>SKM</t>
+          <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O108" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
       <c r="P108" s="11" t="inlineStr"/>
@@ -7720,12 +7714,12 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 스포츠 &amp; 칸 (픽업)</t>
+          <t>코란도 스포츠 (픽업)</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -7750,26 +7744,38 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I109" s="11" t="inlineStr"/>
-      <c r="J109" s="11" t="inlineStr"/>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>7105121500</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[자료 상충], KI-7[자료 상충]</t>
+        </is>
+      </c>
       <c r="K109" s="11" t="inlineStr"/>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>KC R-C-2CG-SmartKeyMV1[2018.03~2021.12], 8751036B00[무쏘 스포츠, 2019~2021]</t>
-        </is>
-      </c>
-      <c r="M109" s="11" t="inlineStr"/>
+          <t>8751008010[2012~2018], 8751032021[15년형~]</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>87510-21100[3버튼]</t>
+        </is>
+      </c>
       <c r="N109" s="11" t="inlineStr">
         <is>
-          <t>SKM</t>
+          <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O109" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
       <c r="P109" s="11" t="inlineStr"/>
@@ -7782,12 +7788,12 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 스포츠 &amp; 칸 (픽업)</t>
+          <t>코란도 스포츠 (픽업)</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018(단종)</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -7812,26 +7818,38 @@
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I110" s="11" t="inlineStr"/>
-      <c r="J110" s="11" t="inlineStr"/>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>7105121500</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[자료 상충], KI-7[자료 상충]</t>
+        </is>
+      </c>
       <c r="K110" s="11" t="inlineStr"/>
       <c r="L110" s="11" t="inlineStr">
         <is>
-          <t>KC R-C-2CG-SmartKeyMV1[2018.03~2021.12], 8751036B00[무쏘 스포츠, 2019~2021]</t>
-        </is>
-      </c>
-      <c r="M110" s="11" t="inlineStr"/>
+          <t>8751008010[2012~2018], 8751032021[15년형~]</t>
+        </is>
+      </c>
+      <c r="M110" s="11" t="inlineStr">
+        <is>
+          <t>87510-21100[3버튼]</t>
+        </is>
+      </c>
       <c r="N110" s="11" t="inlineStr">
         <is>
-          <t>SKM</t>
+          <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O110" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), blog.daum.net(코란도스포츠 차키 이모빌라이저 기본 내장), namu.wiki(코란도 스포츠 2012.1-2018.1), [재조사] pechanara.com(코란도스포츠 트랜스미터·스마트키 8751008010 Q150/Q160 2012-2018, 스마트리모컨 8751032021 15년형~), [재조사] originalkey.ru·autokeymaster.ru(뉴 액티언 스포츠(=코란도 스포츠) 2014.01~ 순정 폴딩키 4D60x80 433MHz, 순정 칩 액티언·렉스턴 2013-2022 4D60x80)</t>
         </is>
       </c>
       <c r="P110" s="11" t="inlineStr"/>
@@ -7849,7 +7867,7 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -7911,15 +7929,27 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr"/>
-      <c r="E112" s="6" t="inlineStr"/>
-      <c r="F112" s="6" t="inlineStr"/>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
@@ -7930,9 +7960,13 @@
       <c r="I112" s="11" t="inlineStr"/>
       <c r="J112" s="11" t="inlineStr"/>
       <c r="K112" s="11" t="inlineStr"/>
-      <c r="L112" s="11" t="n"/>
+      <c r="L112" s="11" t="inlineStr">
+        <is>
+          <t>KC R-C-2CG-SmartKeyMV1[2018.03~2021.12], 8751036B00[무쏘 스포츠, 2019~2021]</t>
+        </is>
+      </c>
       <c r="M112" s="11" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="N112" s="11" t="inlineStr">
         <is>
           <t>SKM</t>
         </is>
@@ -7942,11 +7976,7 @@
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="P112" s="4" t="inlineStr">
-        <is>
-          <t>2022 이후 스마트키 칩 자료 없음</t>
-        </is>
-      </c>
+      <c r="P112" s="11" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
@@ -7961,15 +7991,27 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr"/>
-      <c r="E113" s="6" t="inlineStr"/>
-      <c r="F113" s="6" t="inlineStr"/>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -7980,9 +8022,13 @@
       <c r="I113" s="11" t="inlineStr"/>
       <c r="J113" s="11" t="inlineStr"/>
       <c r="K113" s="11" t="inlineStr"/>
-      <c r="L113" s="11" t="n"/>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>KC R-C-2CG-SmartKeyMV1[2018.03~2021.12], 8751036B00[무쏘 스포츠, 2019~2021]</t>
+        </is>
+      </c>
       <c r="M113" s="11" t="inlineStr"/>
-      <c r="N113" s="4" t="inlineStr">
+      <c r="N113" s="11" t="inlineStr">
         <is>
           <t>SKM</t>
         </is>
@@ -7992,11 +8038,7 @@
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="P113" s="4" t="inlineStr">
-        <is>
-          <t>2022 이후 스마트키 칩 자료 없음</t>
-        </is>
-      </c>
+      <c r="P113" s="11" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
@@ -8011,15 +8053,27 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>2024(단종)</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr"/>
-      <c r="E114" s="6" t="inlineStr"/>
-      <c r="F114" s="6" t="inlineStr"/>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
@@ -8030,9 +8084,13 @@
       <c r="I114" s="11" t="inlineStr"/>
       <c r="J114" s="11" t="inlineStr"/>
       <c r="K114" s="11" t="inlineStr"/>
-      <c r="L114" s="11" t="n"/>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>KC R-C-2CG-SmartKeyMV1[2018.03~2021.12], 8751036B00[무쏘 스포츠, 2019~2021]</t>
+        </is>
+      </c>
       <c r="M114" s="11" t="inlineStr"/>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="N114" s="11" t="inlineStr">
         <is>
           <t>SKM</t>
         </is>
@@ -8042,11 +8100,7 @@
           <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
-      <c r="P114" s="4" t="inlineStr">
-        <is>
-          <t>2022 이후 스마트키 칩 자료 없음</t>
-        </is>
-      </c>
+      <c r="P114" s="11" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
@@ -8056,7 +8110,7 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>토레스</t>
+          <t>렉스턴 스포츠 &amp; 칸 (픽업)</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8064,24 +8118,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="D115" s="6" t="inlineStr"/>
+      <c r="E115" s="6" t="inlineStr"/>
+      <c r="F115" s="6" t="inlineStr"/>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>ID47</t>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
@@ -8096,17 +8138,17 @@
       <c r="M115" s="11" t="inlineStr"/>
       <c r="N115" s="4" t="inlineStr">
         <is>
-          <t>SKM[추정]</t>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O115" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
+          <t>2022 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8160,7 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>토레스</t>
+          <t>렉스턴 스포츠 &amp; 칸 (픽업)</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
@@ -8126,24 +8168,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="D116" s="6" t="inlineStr"/>
+      <c r="E116" s="6" t="inlineStr"/>
+      <c r="F116" s="6" t="inlineStr"/>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>ID47</t>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr">
@@ -8158,17 +8188,17 @@
       <c r="M116" s="11" t="inlineStr"/>
       <c r="N116" s="4" t="inlineStr">
         <is>
-          <t>SKM[추정]</t>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O116" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
+          <t>2022 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -8180,32 +8210,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>토레스</t>
+          <t>렉스턴 스포츠 &amp; 칸 (픽업)</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>2024(단종)</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr"/>
+      <c r="E117" s="6" t="inlineStr"/>
+      <c r="F117" s="6" t="inlineStr"/>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>ID47</t>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
@@ -8220,17 +8238,17 @@
       <c r="M117" s="11" t="inlineStr"/>
       <c r="N117" s="4" t="inlineStr">
         <is>
-          <t>SKM[추정]</t>
+          <t>SKM</t>
         </is>
       </c>
       <c r="O117" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
+          <t>2022 이후 스마트키 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8265,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
@@ -8309,7 +8327,7 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
@@ -8354,7 +8372,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>토레스 하이브리드부터 스마트키 변경 — 신형 키 칩 자료 없음(기존 47칩 기준 추정)</t>
+          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8384,12 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>토레스 EVX (전기차)</t>
+          <t>토레스</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
@@ -8391,7 +8409,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>ID47[추정]</t>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
@@ -8411,12 +8429,12 @@
       </c>
       <c r="O120" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
+          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8428,12 +8446,12 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>토레스 EVX (전기차)</t>
+          <t>토레스</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
@@ -8453,7 +8471,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>ID47[추정]</t>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
@@ -8473,12 +8491,12 @@
       </c>
       <c r="O121" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
+          <t>칩(47) 확인 — 이모빌라이저 모듈 명칭만 G4 렉스턴·티볼리 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8508,12 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>토레스 EVX (전기차)</t>
+          <t>토레스</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
@@ -8515,7 +8533,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>ID47[추정]</t>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
@@ -8535,12 +8553,12 @@
       </c>
       <c r="O122" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
         </is>
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
+          <t>토레스 하이브리드부터 스마트키 변경 — 신형 키 칩 자료 없음(기존 47칩 기준 추정)</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8575,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -8614,7 +8632,7 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>액티언 (2세대, J120)</t>
+          <t>토레스 EVX (전기차)</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
@@ -8659,7 +8677,7 @@
       </c>
       <c r="O124" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
@@ -8676,7 +8694,7 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>액티언 (2세대, J120)</t>
+          <t>토레스 EVX (전기차)</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -8721,7 +8739,7 @@
       </c>
       <c r="O125" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -8738,7 +8756,7 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>액티언 (2세대, J120)</t>
+          <t>토레스 EVX (전기차)</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
@@ -8783,7 +8801,7 @@
       </c>
       <c r="O126" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -8800,12 +8818,12 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>무쏘 EV (픽업, 전기차)</t>
+          <t>액티언 (2세대, J120)</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
@@ -8845,7 +8863,7 @@
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
@@ -8862,12 +8880,12 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>무쏘 EV (픽업, 전기차)</t>
+          <t>액티언 (2세대, J120)</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -8907,7 +8925,7 @@
       </c>
       <c r="O128" s="11" t="inlineStr">
         <is>
-          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -8924,59 +8942,59 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 (1세대)</t>
+          <t>액티언 (2세대, J120)</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G129" s="11" t="inlineStr">
-        <is>
-          <t>ID48</t>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>ID47[추정]</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr"/>
-      <c r="J129" s="11" t="inlineStr">
-        <is>
-          <t>SSY3, JMA SSA-2P</t>
-        </is>
-      </c>
+      <c r="J129" s="11" t="inlineStr"/>
       <c r="K129" s="11" t="inlineStr"/>
-      <c r="L129" s="11" t="inlineStr"/>
+      <c r="L129" s="11" t="n"/>
       <c r="M129" s="11" t="inlineStr"/>
-      <c r="N129" s="11" t="inlineStr">
-        <is>
-          <t>VDO 이모박스</t>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>SKM[추정]</t>
         </is>
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
-        </is>
-      </c>
-      <c r="P129" s="11" t="inlineStr"/>
+          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="P129" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
@@ -8986,59 +9004,59 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 (1세대)</t>
+          <t>무쏘 EV (픽업, 전기차)</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G130" s="11" t="inlineStr">
-        <is>
-          <t>ID48</t>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>ID47[추정]</t>
         </is>
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr"/>
-      <c r="J130" s="11" t="inlineStr">
-        <is>
-          <t>SSY3, JMA SSA-2P</t>
-        </is>
-      </c>
+      <c r="J130" s="11" t="inlineStr"/>
       <c r="K130" s="11" t="inlineStr"/>
-      <c r="L130" s="11" t="inlineStr"/>
+      <c r="L130" s="11" t="n"/>
       <c r="M130" s="11" t="inlineStr"/>
-      <c r="N130" s="11" t="inlineStr">
-        <is>
-          <t>VDO 이모박스</t>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>SKM[추정]</t>
         </is>
       </c>
       <c r="O130" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
-        </is>
-      </c>
-      <c r="P130" s="11" t="inlineStr"/>
+          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="P130" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
@@ -9048,59 +9066,59 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 (1세대)</t>
+          <t>무쏘 EV (픽업, 전기차)</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G131" s="11" t="inlineStr">
-        <is>
-          <t>ID48</t>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>ID47[추정]</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr"/>
-      <c r="J131" s="11" t="inlineStr">
-        <is>
-          <t>SSY3, JMA SSA-2P</t>
-        </is>
-      </c>
+      <c r="J131" s="11" t="inlineStr"/>
       <c r="K131" s="11" t="inlineStr"/>
-      <c r="L131" s="11" t="inlineStr"/>
+      <c r="L131" s="11" t="n"/>
       <c r="M131" s="11" t="inlineStr"/>
-      <c r="N131" s="11" t="inlineStr">
-        <is>
-          <t>VDO 이모박스</t>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>SKM[추정]</t>
         </is>
       </c>
       <c r="O131" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
-        </is>
-      </c>
-      <c r="P131" s="11" t="inlineStr"/>
+          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+        </is>
+      </c>
+      <c r="P131" s="4" t="inlineStr">
+        <is>
+          <t>키 칩 직접 자료 없음 — 토레스 47칩 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
@@ -9115,7 +9133,7 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -9177,7 +9195,7 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -9239,7 +9257,7 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>2006(단종)</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
@@ -9252,14 +9270,14 @@
           <t>△</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr">
         <is>
-          <t>ID48[2006.1 이전 생산], ID60(4D60)[2006.2 이후 생산]</t>
+          <t>ID48</t>
         </is>
       </c>
       <c r="H134" s="11" t="inlineStr">
@@ -9278,12 +9296,12 @@
       <c r="M134" s="11" t="inlineStr"/>
       <c r="N134" s="11" t="inlineStr">
         <is>
-          <t>VDO 이모박스[2006.1 이전 생산], 이모빌라이저 컨트롤 유닛(87110-08B00)[2006.2 이후 생산]</t>
+          <t>VDO 이모박스</t>
         </is>
       </c>
       <c r="O134" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
       <c r="P134" s="11" t="inlineStr"/>
@@ -9296,32 +9314,32 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>뉴 렉스턴</t>
+          <t>렉스턴 (1세대)</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
+          <t>ID48</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
@@ -9329,11 +9347,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I135" s="11" t="inlineStr">
-        <is>
-          <t>87170-08B21[40bit], 87170-08D50[80bit]</t>
-        </is>
-      </c>
+      <c r="I135" s="11" t="inlineStr"/>
       <c r="J135" s="11" t="inlineStr">
         <is>
           <t>SSY3, JMA SSA-2P</t>
@@ -9344,12 +9358,12 @@
       <c r="M135" s="11" t="inlineStr"/>
       <c r="N135" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
+          <t>VDO 이모박스</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
       <c r="P135" s="11" t="inlineStr"/>
@@ -9362,32 +9376,32 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>뉴 렉스턴</t>
+          <t>렉스턴 (1세대)</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr">
         <is>
-          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
+          <t>ID48</t>
         </is>
       </c>
       <c r="H136" s="11" t="inlineStr">
@@ -9395,11 +9409,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I136" s="11" t="inlineStr">
-        <is>
-          <t>87170-08B21[40bit], 87170-08D50[80bit]</t>
-        </is>
-      </c>
+      <c r="I136" s="11" t="inlineStr"/>
       <c r="J136" s="11" t="inlineStr">
         <is>
           <t>SSY3, JMA SSA-2P</t>
@@ -9410,12 +9420,12 @@
       <c r="M136" s="11" t="inlineStr"/>
       <c r="N136" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
+          <t>VDO 이모박스</t>
         </is>
       </c>
       <c r="O136" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
         </is>
       </c>
       <c r="P136" s="11" t="inlineStr"/>
@@ -9428,32 +9438,32 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>뉴 렉스턴</t>
+          <t>렉스턴 (1세대)</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2006(단종)</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
+          <t>ID48[2006.1 이전 생산]</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
@@ -9461,30 +9471,26 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I137" s="11" t="inlineStr">
-        <is>
-          <t>87170-08B21[40bit], 87170-08D50[80bit]</t>
-        </is>
-      </c>
+      <c r="I137" s="11" t="n"/>
       <c r="J137" s="11" t="inlineStr">
         <is>
           <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
-      <c r="K137" s="11" t="inlineStr"/>
-      <c r="L137" s="11" t="inlineStr"/>
-      <c r="M137" s="11" t="inlineStr"/>
+      <c r="K137" s="11" t="n"/>
+      <c r="L137" s="11" t="n"/>
+      <c r="M137" s="11" t="n"/>
       <c r="N137" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
+          <t>VDO 이모박스[2006.1 이전 생산]</t>
         </is>
       </c>
       <c r="O137" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
-        </is>
-      </c>
-      <c r="P137" s="11" t="inlineStr"/>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
+        </is>
+      </c>
+      <c r="P137" s="11" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
@@ -9494,12 +9500,12 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>뉴 렉스턴</t>
+          <t>렉스턴 (1세대)</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2006(단종)</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -9519,7 +9525,7 @@
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
-          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
+          <t>ID60(4D60)[2006.2 이후 생산]</t>
         </is>
       </c>
       <c r="H138" s="11" t="inlineStr">
@@ -9527,30 +9533,26 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I138" s="11" t="inlineStr">
-        <is>
-          <t>87170-08B21[40bit], 87170-08D50[80bit]</t>
-        </is>
-      </c>
+      <c r="I138" s="11" t="n"/>
       <c r="J138" s="11" t="inlineStr">
         <is>
           <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
-      <c r="K138" s="11" t="inlineStr"/>
-      <c r="L138" s="11" t="inlineStr"/>
-      <c r="M138" s="11" t="inlineStr"/>
+      <c r="K138" s="11" t="n"/>
+      <c r="L138" s="11" t="n"/>
+      <c r="M138" s="11" t="n"/>
       <c r="N138" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[2006.2 이후 생산]</t>
         </is>
       </c>
       <c r="O138" s="11" t="inlineStr">
         <is>
-          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
-        </is>
-      </c>
-      <c r="P138" s="11" t="inlineStr"/>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), abkeys.com(액티언·렉스턴 2000+ SSY3 리모컨키 헤드), manualslib(2004 렉스턴 2.7 XDi: 트랜스폰더 코드 ECU 확인 방식), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), [재조사] originalkey.ru(렉스턴 2001-2006 순정 키: 트랜스폰더 8E(메가모스 계열 표기), 조명 버튼), savekey.ru(2버튼 리모컨키: 액티언 2005-2012·액티언스포츠 2006-2012·카이런 2005-2012·렉스턴 2001-2012)</t>
+        </is>
+      </c>
+      <c r="P138" s="11" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
@@ -9565,7 +9567,7 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -9631,7 +9633,7 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -9697,7 +9699,7 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>2012(단종)</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -9758,12 +9760,12 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 W / 렉스턴 II</t>
+          <t>뉴 렉스턴</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -9783,35 +9785,35 @@
       </c>
       <c r="G142" s="11" t="inlineStr">
         <is>
-          <t>4D60x80[리모컨키, 폴딩키], ID70(4D70)[스마트키]</t>
+          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
         </is>
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>막대키,폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I142" s="11" t="n"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>87170-08B21[40bit], 87170-08D50[80bit]</t>
+        </is>
+      </c>
       <c r="J142" s="11" t="inlineStr">
         <is>
-          <t>TOY40[리모컨키]</t>
+          <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
       <c r="K142" s="11" t="inlineStr"/>
-      <c r="L142" s="11" t="inlineStr">
-        <is>
-          <t>FCC DEO-MT FOBG02</t>
-        </is>
-      </c>
-      <c r="M142" s="11" t="n"/>
+      <c r="L142" s="11" t="inlineStr"/>
+      <c r="M142" s="11" t="inlineStr"/>
       <c r="N142" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[~2017.04]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
       <c r="O142" s="11" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="P142" s="11" t="inlineStr"/>
@@ -9824,12 +9826,12 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 W / 렉스턴 II</t>
+          <t>뉴 렉스턴</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -9849,35 +9851,35 @@
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>4D60x80[리모컨키, 폴딩키], ID70(4D70)[스마트키]</t>
+          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>막대키,폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I143" s="11" t="n"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>87170-08B21[40bit], 87170-08D50[80bit]</t>
+        </is>
+      </c>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>TOY40[리모컨키]</t>
+          <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
       <c r="K143" s="11" t="inlineStr"/>
-      <c r="L143" s="11" t="inlineStr">
-        <is>
-          <t>FCC DEO-MT FOBG02</t>
-        </is>
-      </c>
-      <c r="M143" s="11" t="n"/>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
       <c r="N143" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[~2017.04]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
       <c r="O143" s="11" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="P143" s="11" t="inlineStr"/>
@@ -9890,12 +9892,12 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 W / 렉스턴 II</t>
+          <t>뉴 렉스턴</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -9915,35 +9917,35 @@
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
-          <t>4D60x80[리모컨키, 폴딩키], ID70(4D70)[스마트키]</t>
+          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
         </is>
       </c>
       <c r="H144" s="11" t="inlineStr">
         <is>
-          <t>막대키,폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I144" s="11" t="n"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>87170-08B21[40bit], 87170-08D50[80bit]</t>
+        </is>
+      </c>
       <c r="J144" s="11" t="inlineStr">
         <is>
-          <t>TOY40[리모컨키]</t>
+          <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
       <c r="K144" s="11" t="inlineStr"/>
-      <c r="L144" s="11" t="inlineStr">
-        <is>
-          <t>FCC DEO-MT FOBG02</t>
-        </is>
-      </c>
-      <c r="M144" s="11" t="n"/>
+      <c r="L144" s="11" t="inlineStr"/>
+      <c r="M144" s="11" t="inlineStr"/>
       <c r="N144" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[~2017.04]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
       <c r="O144" s="11" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="P144" s="11" t="inlineStr"/>
@@ -9956,12 +9958,12 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>렉스턴 W / 렉스턴 II</t>
+          <t>뉴 렉스턴</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2012(단종)</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -9981,35 +9983,35 @@
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>4D60x80[리모컨키, 폴딩키], ID70(4D70)[스마트키]</t>
+          <t>ID60(4D60)[40bit 키], 4D60x80[80bit 키]</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>막대키,폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I145" s="11" t="n"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>87170-08B21[40bit], 87170-08D50[80bit]</t>
+        </is>
+      </c>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>TOY40[리모컨키]</t>
+          <t>SSY3, JMA SSA-2P</t>
         </is>
       </c>
       <c r="K145" s="11" t="inlineStr"/>
-      <c r="L145" s="11" t="inlineStr">
-        <is>
-          <t>FCC DEO-MT FOBG02</t>
-        </is>
-      </c>
-      <c r="M145" s="11" t="n"/>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
       <c r="N145" s="11" t="inlineStr">
         <is>
-          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[~2017.04]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)</t>
         </is>
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+          <t>auto-keys.eu(쌍용 순정 키 87170-32030·32020·08D50 TMS37145 4D-60 80bit / 87170-08B21 4D-60 40bit, 블레이드 SSA2P), kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), tlslocks.com.au(렉스턴 2006+ 4D60), [재조사] absolutkey.ru(액티언·카이런·렉스턴 키 ID60 SSY3), savekey.ru(액티언 2005-2012·카이런 2005-2012·렉스턴 2001-2012 2버튼 리모컨키)</t>
         </is>
       </c>
       <c r="P145" s="11" t="inlineStr"/>
@@ -10027,7 +10029,7 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -10093,7 +10095,7 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>2017(단종)</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -10154,12 +10156,12 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>G4 렉스턴 (2세대)</t>
+          <t>렉스턴 W / 렉스턴 II</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -10179,31 +10181,35 @@
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
-          <t>4D60x80</t>
+          <t>4D60x80[리모컨키, 폴딩키], ID70(4D70)[스마트키]</t>
         </is>
       </c>
       <c r="H148" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I148" s="11" t="inlineStr"/>
-      <c r="J148" s="11" t="inlineStr"/>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="n"/>
+      <c r="J148" s="11" t="inlineStr">
+        <is>
+          <t>TOY40[리모컨키]</t>
+        </is>
+      </c>
       <c r="K148" s="11" t="inlineStr"/>
       <c r="L148" s="11" t="inlineStr">
         <is>
-          <t>87510-36050[2017.07~2020.11], 87510-36550[2017.07~2020.11], 87510-36560[2017.07~2020.11], KC R-C-2CG-SmartKeyMV1[2017.07~2020.11]</t>
-        </is>
-      </c>
-      <c r="M148" s="11" t="inlineStr"/>
+          <t>FCC DEO-MT FOBG02</t>
+        </is>
+      </c>
+      <c r="M148" s="11" t="n"/>
       <c r="N148" s="11" t="inlineStr">
         <is>
-          <t>SKM(87570-36010)[2017.07~]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[~2017.04]</t>
         </is>
       </c>
       <c r="O148" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
       <c r="P148" s="11" t="inlineStr"/>
@@ -10216,12 +10222,12 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>G4 렉스턴 (2세대)</t>
+          <t>렉스턴 W / 렉스턴 II</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -10241,31 +10247,35 @@
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>4D60x80</t>
+          <t>4D60x80[리모컨키, 폴딩키], ID70(4D70)[스마트키]</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I149" s="11" t="inlineStr"/>
-      <c r="J149" s="11" t="inlineStr"/>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="n"/>
+      <c r="J149" s="11" t="inlineStr">
+        <is>
+          <t>TOY40[리모컨키]</t>
+        </is>
+      </c>
       <c r="K149" s="11" t="inlineStr"/>
       <c r="L149" s="11" t="inlineStr">
         <is>
-          <t>87510-36050[2017.07~2020.11], 87510-36550[2017.07~2020.11], 87510-36560[2017.07~2020.11], KC R-C-2CG-SmartKeyMV1[2017.07~2020.11]</t>
-        </is>
-      </c>
-      <c r="M149" s="11" t="inlineStr"/>
+          <t>FCC DEO-MT FOBG02</t>
+        </is>
+      </c>
+      <c r="M149" s="11" t="n"/>
       <c r="N149" s="11" t="inlineStr">
         <is>
-          <t>SKM(87570-36010)[2017.07~]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[~2017.04]</t>
         </is>
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
       <c r="P149" s="11" t="inlineStr"/>
@@ -10278,12 +10288,12 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>G4 렉스턴 (2세대)</t>
+          <t>렉스턴 W / 렉스턴 II</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -10303,31 +10313,35 @@
       </c>
       <c r="G150" s="11" t="inlineStr">
         <is>
-          <t>4D60x80</t>
+          <t>4D60x80[리모컨키, 폴딩키], ID70(4D70)[스마트키]</t>
         </is>
       </c>
       <c r="H150" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I150" s="11" t="inlineStr"/>
-      <c r="J150" s="11" t="inlineStr"/>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="n"/>
+      <c r="J150" s="11" t="inlineStr">
+        <is>
+          <t>TOY40[리모컨키]</t>
+        </is>
+      </c>
       <c r="K150" s="11" t="inlineStr"/>
       <c r="L150" s="11" t="inlineStr">
         <is>
-          <t>87510-36050[2017.07~2020.11], 87510-36550[2017.07~2020.11], 87510-36560[2017.07~2020.11], KC R-C-2CG-SmartKeyMV1[2017.07~2020.11]</t>
-        </is>
-      </c>
-      <c r="M150" s="11" t="inlineStr"/>
+          <t>FCC DEO-MT FOBG02</t>
+        </is>
+      </c>
+      <c r="M150" s="11" t="n"/>
       <c r="N150" s="11" t="inlineStr">
         <is>
-          <t>SKM(87570-36010)[2017.07~]</t>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[~2017.04]</t>
         </is>
       </c>
       <c r="O150" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
       <c r="P150" s="11" t="inlineStr"/>
@@ -10340,12 +10354,12 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>G4 렉스턴 (2세대)</t>
+          <t>렉스턴 W / 렉스턴 II</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017(단종)</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -10363,40 +10377,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G151" s="4" t="inlineStr">
-        <is>
-          <t>4D60x80[2020.11 이전 생산], 확인 불가[2020.11 이후 생산]</t>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80[리모컨키, 폴딩키], ID70(4D70)[스마트키]</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I151" s="11" t="inlineStr"/>
-      <c r="J151" s="11" t="inlineStr"/>
+          <t>막대키,폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="n"/>
+      <c r="J151" s="11" t="inlineStr">
+        <is>
+          <t>TOY40[리모컨키]</t>
+        </is>
+      </c>
       <c r="K151" s="11" t="inlineStr"/>
       <c r="L151" s="11" t="inlineStr">
         <is>
-          <t>87510-36050[2017.07~2020.11], 87510-36550[2017.07~2020.11], 87510-36560[2017.07~2020.11], KC R-C-2CG-SmartKeyMV1[2017.07~2020.11], 8751036C20[2020.11~]</t>
-        </is>
-      </c>
-      <c r="M151" s="11" t="inlineStr"/>
-      <c r="N151" s="4" t="inlineStr">
-        <is>
-          <t>SKM(87570-36010)[2017.07~]</t>
+          <t>FCC DEO-MT FOBG02</t>
+        </is>
+      </c>
+      <c r="M151" s="11" t="n"/>
+      <c r="N151" s="11" t="inlineStr">
+        <is>
+          <t>이모빌라이저 컨트롤 유닛(87110-08B00)[~2017.04]</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
-        </is>
-      </c>
-      <c r="P151" s="4" t="inlineStr">
-        <is>
-          <t>2020.11 이후 생산분 신형 스마트키(NXP 부품 표기) 칩 ID 자료 없음</t>
-        </is>
-      </c>
+          <t>kpartsmall.com·autoecupart.net(이모빌라이저 컨트롤 유닛 87110-08B00/09000: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언스포츠 2006.04~2007.03), abkeys.com(렉스턴 2011-2013 SSY3 2버튼 리모컨키), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), digital-kaos.co.uk(2013 렉스턴 스마트키 DEO-MT FOBG02 4D70 DST80), [재조사] autokeymaster.ru(순정 렉스턴 2012.06-2017 2버튼 키 4D60x80 TOY40 433.92MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="P151" s="11" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
@@ -10411,15 +10425,27 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr"/>
-      <c r="E152" s="6" t="inlineStr"/>
-      <c r="F152" s="6" t="inlineStr"/>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G152" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
         </is>
       </c>
       <c r="H152" s="11" t="inlineStr">
@@ -10432,25 +10458,21 @@
       <c r="K152" s="11" t="inlineStr"/>
       <c r="L152" s="11" t="inlineStr">
         <is>
-          <t>8751036C20[5버튼, 2020.11~2022.04 생산]</t>
+          <t>87510-36050[2017.07~2020.11], 87510-36550[2017.07~2020.11], 87510-36560[2017.07~2020.11], KC R-C-2CG-SmartKeyMV1[2017.07~2020.11]</t>
         </is>
       </c>
       <c r="M152" s="11" t="inlineStr"/>
-      <c r="N152" s="4" t="inlineStr">
+      <c r="N152" s="11" t="inlineStr">
         <is>
           <t>SKM(87570-36010)[2017.07~]</t>
         </is>
       </c>
       <c r="O152" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
-        </is>
-      </c>
-      <c r="P152" s="4" t="inlineStr">
-        <is>
-          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
-        </is>
-      </c>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="P152" s="11" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
@@ -10465,15 +10487,27 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr"/>
-      <c r="E153" s="6" t="inlineStr"/>
-      <c r="F153" s="6" t="inlineStr"/>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
@@ -10486,25 +10520,21 @@
       <c r="K153" s="11" t="inlineStr"/>
       <c r="L153" s="11" t="inlineStr">
         <is>
-          <t>8751036C20[5버튼, 2020.11~2022.04 생산]</t>
+          <t>87510-36050[2017.07~2020.11], 87510-36550[2017.07~2020.11], 87510-36560[2017.07~2020.11], KC R-C-2CG-SmartKeyMV1[2017.07~2020.11]</t>
         </is>
       </c>
       <c r="M153" s="11" t="inlineStr"/>
-      <c r="N153" s="4" t="inlineStr">
+      <c r="N153" s="11" t="inlineStr">
         <is>
           <t>SKM(87570-36010)[2017.07~]</t>
         </is>
       </c>
       <c r="O153" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
-        </is>
-      </c>
-      <c r="P153" s="4" t="inlineStr">
-        <is>
-          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
-        </is>
-      </c>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="P153" s="11" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
@@ -10519,15 +10549,27 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr"/>
-      <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="6" t="inlineStr"/>
-      <c r="G154" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G154" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
@@ -10538,9 +10580,13 @@
       <c r="I154" s="11" t="inlineStr"/>
       <c r="J154" s="11" t="inlineStr"/>
       <c r="K154" s="11" t="inlineStr"/>
-      <c r="L154" s="11" t="n"/>
+      <c r="L154" s="11" t="inlineStr">
+        <is>
+          <t>87510-36050[2017.07~2020.11], 87510-36550[2017.07~2020.11], 87510-36560[2017.07~2020.11], KC R-C-2CG-SmartKeyMV1[2017.07~2020.11]</t>
+        </is>
+      </c>
       <c r="M154" s="11" t="inlineStr"/>
-      <c r="N154" s="4" t="inlineStr">
+      <c r="N154" s="11" t="inlineStr">
         <is>
           <t>SKM(87570-36010)[2017.07~]</t>
         </is>
@@ -10550,11 +10596,7 @@
           <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
-      <c r="P154" s="4" t="inlineStr">
-        <is>
-          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
-        </is>
-      </c>
+      <c r="P154" s="11" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
@@ -10569,15 +10611,27 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D155" s="6" t="inlineStr"/>
-      <c r="E155" s="6" t="inlineStr"/>
-      <c r="F155" s="6" t="inlineStr"/>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G155" s="14" t="inlineStr">
+        <is>
+          <t>4D60x80[2020.11 이전 생산]</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
@@ -10585,26 +10639,26 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I155" s="11" t="inlineStr"/>
-      <c r="J155" s="11" t="inlineStr"/>
-      <c r="K155" s="11" t="inlineStr"/>
-      <c r="L155" s="11" t="n"/>
-      <c r="M155" s="11" t="inlineStr"/>
-      <c r="N155" s="4" t="inlineStr">
+      <c r="I155" s="11" t="n"/>
+      <c r="J155" s="11" t="n"/>
+      <c r="K155" s="11" t="n"/>
+      <c r="L155" s="11" t="inlineStr">
+        <is>
+          <t>87510-36050[2017.07~2020.11], 87510-36550[2017.07~2020.11], 87510-36560[2017.07~2020.11], KC R-C-2CG-SmartKeyMV1[2017.07~2020.11]</t>
+        </is>
+      </c>
+      <c r="M155" s="11" t="n"/>
+      <c r="N155" s="14" t="inlineStr">
         <is>
           <t>SKM(87570-36010)[2017.07~]</t>
         </is>
       </c>
       <c r="O155" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
-        </is>
-      </c>
-      <c r="P155" s="4" t="inlineStr">
-        <is>
-          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
-        </is>
-      </c>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="P155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
@@ -10619,15 +10673,15 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr"/>
-      <c r="E156" s="6" t="inlineStr"/>
-      <c r="F156" s="6" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D156" s="15" t="n"/>
+      <c r="E156" s="15" t="n"/>
+      <c r="F156" s="15" t="n"/>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>확인 불가[2020.11 이후 생산]</t>
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr">
@@ -10635,11 +10689,15 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I156" s="11" t="inlineStr"/>
-      <c r="J156" s="11" t="inlineStr"/>
-      <c r="K156" s="11" t="inlineStr"/>
-      <c r="L156" s="11" t="n"/>
-      <c r="M156" s="11" t="inlineStr"/>
+      <c r="I156" s="11" t="n"/>
+      <c r="J156" s="11" t="n"/>
+      <c r="K156" s="11" t="n"/>
+      <c r="L156" s="11" t="inlineStr">
+        <is>
+          <t>8751036C20[2020.11~]</t>
+        </is>
+      </c>
+      <c r="M156" s="11" t="n"/>
       <c r="N156" s="4" t="inlineStr">
         <is>
           <t>SKM(87570-36010)[2017.07~]</t>
@@ -10647,12 +10705,12 @@
       </c>
       <c r="O156" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
+          <t>2020.11 이후 생산분 신형 스마트키(NXP 부품 표기) 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10727,7 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr"/>
@@ -10688,7 +10746,11 @@
       <c r="I157" s="11" t="inlineStr"/>
       <c r="J157" s="11" t="inlineStr"/>
       <c r="K157" s="11" t="inlineStr"/>
-      <c r="L157" s="11" t="n"/>
+      <c r="L157" s="11" t="inlineStr">
+        <is>
+          <t>8751036C20[5버튼, 2020.11~2022.04 생산]</t>
+        </is>
+      </c>
       <c r="M157" s="11" t="inlineStr"/>
       <c r="N157" s="4" t="inlineStr">
         <is>
@@ -10697,7 +10759,7 @@
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
@@ -10714,45 +10776,49 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>이스타나 (밴)</t>
+          <t>G4 렉스턴 (2세대)</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr"/>
       <c r="E158" s="6" t="inlineStr"/>
       <c r="F158" s="6" t="inlineStr"/>
-      <c r="G158" s="8" t="inlineStr">
+      <c r="G158" s="4" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="H158" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I158" s="11" t="inlineStr"/>
       <c r="J158" s="11" t="inlineStr"/>
       <c r="K158" s="11" t="inlineStr"/>
-      <c r="L158" s="11" t="inlineStr"/>
+      <c r="L158" s="11" t="inlineStr">
+        <is>
+          <t>8751036C20[5버튼, 2020.11~2022.04 생산]</t>
+        </is>
+      </c>
       <c r="M158" s="11" t="inlineStr"/>
-      <c r="N158" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저</t>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>SKM(87570-36010)[2017.07~]</t>
         </is>
       </c>
       <c r="O158" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
-        </is>
-      </c>
-      <c r="P158" s="8" t="inlineStr">
-        <is>
-          <t>키 칩 자료 없음</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="P158" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10764,45 +10830,45 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>이스타나 (밴)</t>
+          <t>G4 렉스턴 (2세대)</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr"/>
       <c r="E159" s="6" t="inlineStr"/>
       <c r="F159" s="6" t="inlineStr"/>
-      <c r="G159" s="8" t="inlineStr">
+      <c r="G159" s="4" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I159" s="11" t="inlineStr"/>
       <c r="J159" s="11" t="inlineStr"/>
       <c r="K159" s="11" t="inlineStr"/>
-      <c r="L159" s="11" t="inlineStr"/>
+      <c r="L159" s="11" t="n"/>
       <c r="M159" s="11" t="inlineStr"/>
-      <c r="N159" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저</t>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>SKM(87570-36010)[2017.07~]</t>
         </is>
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
-        </is>
-      </c>
-      <c r="P159" s="8" t="inlineStr">
-        <is>
-          <t>키 칩 자료 없음</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="P159" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10814,45 +10880,45 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>이스타나 (밴)</t>
+          <t>G4 렉스턴 (2세대)</t>
         </is>
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr"/>
       <c r="E160" s="6" t="inlineStr"/>
       <c r="F160" s="6" t="inlineStr"/>
-      <c r="G160" s="8" t="inlineStr">
+      <c r="G160" s="4" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="H160" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I160" s="11" t="inlineStr"/>
       <c r="J160" s="11" t="inlineStr"/>
       <c r="K160" s="11" t="inlineStr"/>
-      <c r="L160" s="11" t="inlineStr"/>
+      <c r="L160" s="11" t="n"/>
       <c r="M160" s="11" t="inlineStr"/>
-      <c r="N160" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저</t>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>SKM(87570-36010)[2017.07~]</t>
         </is>
       </c>
       <c r="O160" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
-        </is>
-      </c>
-      <c r="P160" s="8" t="inlineStr">
-        <is>
-          <t>키 칩 자료 없음</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="P160" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10864,45 +10930,45 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>이스타나 (밴)</t>
+          <t>G4 렉스턴 (2세대)</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr"/>
       <c r="E161" s="6" t="inlineStr"/>
       <c r="F161" s="6" t="inlineStr"/>
-      <c r="G161" s="8" t="inlineStr">
+      <c r="G161" s="4" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I161" s="11" t="inlineStr"/>
       <c r="J161" s="11" t="inlineStr"/>
       <c r="K161" s="11" t="inlineStr"/>
-      <c r="L161" s="11" t="inlineStr"/>
+      <c r="L161" s="11" t="n"/>
       <c r="M161" s="11" t="inlineStr"/>
-      <c r="N161" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저</t>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>SKM(87570-36010)[2017.07~]</t>
         </is>
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
-        </is>
-      </c>
-      <c r="P161" s="8" t="inlineStr">
-        <is>
-          <t>키 칩 자료 없음</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="P161" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10914,45 +10980,45 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>이스타나 (밴)</t>
+          <t>G4 렉스턴 (2세대)</t>
         </is>
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>2004(단종)</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr"/>
       <c r="E162" s="6" t="inlineStr"/>
       <c r="F162" s="6" t="inlineStr"/>
-      <c r="G162" s="8" t="inlineStr">
+      <c r="G162" s="4" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
       </c>
       <c r="H162" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I162" s="11" t="inlineStr"/>
       <c r="J162" s="11" t="inlineStr"/>
       <c r="K162" s="11" t="inlineStr"/>
-      <c r="L162" s="11" t="inlineStr"/>
+      <c r="L162" s="11" t="n"/>
       <c r="M162" s="11" t="inlineStr"/>
-      <c r="N162" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저</t>
+      <c r="N162" s="4" t="inlineStr">
+        <is>
+          <t>SKM(87570-36010)[2017.07~]</t>
         </is>
       </c>
       <c r="O162" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
-        </is>
-      </c>
-      <c r="P162" s="8" t="inlineStr">
-        <is>
-          <t>키 칩 자료 없음</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+        </is>
+      </c>
+      <c r="P162" s="4" t="inlineStr">
+        <is>
+          <t>2020.11 이후 신형 스마트키(8751036C20 등)는 NXP 부품 표기 — 칩 ID 자료 없음</t>
         </is>
       </c>
     </row>
@@ -10964,32 +11030,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>로디우스</t>
+          <t>이스타나 (밴)</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G163" s="11" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr"/>
+      <c r="E163" s="6" t="inlineStr"/>
+      <c r="F163" s="6" t="inlineStr"/>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
@@ -10998,25 +11052,25 @@
         </is>
       </c>
       <c r="I163" s="11" t="inlineStr"/>
-      <c r="J163" s="11" t="inlineStr">
-        <is>
-          <t>SSY3</t>
-        </is>
-      </c>
+      <c r="J163" s="11" t="inlineStr"/>
       <c r="K163" s="11" t="inlineStr"/>
       <c r="L163" s="11" t="inlineStr"/>
       <c r="M163" s="11" t="inlineStr"/>
-      <c r="N163" s="11" t="inlineStr">
+      <c r="N163" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
-        </is>
-      </c>
-      <c r="P163" s="11" t="inlineStr"/>
+          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
+        </is>
+      </c>
+      <c r="P163" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
@@ -11026,32 +11080,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>로디우스</t>
+          <t>이스타나 (밴)</t>
         </is>
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G164" s="11" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr"/>
+      <c r="E164" s="6" t="inlineStr"/>
+      <c r="F164" s="6" t="inlineStr"/>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="H164" s="11" t="inlineStr">
@@ -11060,25 +11102,25 @@
         </is>
       </c>
       <c r="I164" s="11" t="inlineStr"/>
-      <c r="J164" s="11" t="inlineStr">
-        <is>
-          <t>SSY3</t>
-        </is>
-      </c>
+      <c r="J164" s="11" t="inlineStr"/>
       <c r="K164" s="11" t="inlineStr"/>
       <c r="L164" s="11" t="inlineStr"/>
       <c r="M164" s="11" t="inlineStr"/>
-      <c r="N164" s="11" t="inlineStr">
+      <c r="N164" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O164" s="11" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
-        </is>
-      </c>
-      <c r="P164" s="11" t="inlineStr"/>
+          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
+        </is>
+      </c>
+      <c r="P164" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
@@ -11088,32 +11130,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>로디우스</t>
+          <t>이스타나 (밴)</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G165" s="11" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr"/>
+      <c r="E165" s="6" t="inlineStr"/>
+      <c r="F165" s="6" t="inlineStr"/>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
@@ -11122,25 +11152,25 @@
         </is>
       </c>
       <c r="I165" s="11" t="inlineStr"/>
-      <c r="J165" s="11" t="inlineStr">
-        <is>
-          <t>SSY3</t>
-        </is>
-      </c>
+      <c r="J165" s="11" t="inlineStr"/>
       <c r="K165" s="11" t="inlineStr"/>
       <c r="L165" s="11" t="inlineStr"/>
       <c r="M165" s="11" t="inlineStr"/>
-      <c r="N165" s="11" t="inlineStr">
+      <c r="N165" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
-        </is>
-      </c>
-      <c r="P165" s="11" t="inlineStr"/>
+          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
+        </is>
+      </c>
+      <c r="P165" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
@@ -11150,32 +11180,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>로디우스</t>
+          <t>이스타나 (밴)</t>
         </is>
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G166" s="11" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr"/>
+      <c r="E166" s="6" t="inlineStr"/>
+      <c r="F166" s="6" t="inlineStr"/>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="H166" s="11" t="inlineStr">
@@ -11184,25 +11202,25 @@
         </is>
       </c>
       <c r="I166" s="11" t="inlineStr"/>
-      <c r="J166" s="11" t="inlineStr">
-        <is>
-          <t>SSY3</t>
-        </is>
-      </c>
+      <c r="J166" s="11" t="inlineStr"/>
       <c r="K166" s="11" t="inlineStr"/>
       <c r="L166" s="11" t="inlineStr"/>
       <c r="M166" s="11" t="inlineStr"/>
-      <c r="N166" s="11" t="inlineStr">
+      <c r="N166" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O166" s="11" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
-        </is>
-      </c>
-      <c r="P166" s="11" t="inlineStr"/>
+          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
+        </is>
+      </c>
+      <c r="P166" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
@@ -11212,32 +11230,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>로디우스</t>
+          <t>이스타나 (밴)</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G167" s="11" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
+          <t>2004(단종)</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr"/>
+      <c r="E167" s="6" t="inlineStr"/>
+      <c r="F167" s="6" t="inlineStr"/>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
@@ -11246,25 +11252,25 @@
         </is>
       </c>
       <c r="I167" s="11" t="inlineStr"/>
-      <c r="J167" s="11" t="inlineStr">
-        <is>
-          <t>SSY3</t>
-        </is>
-      </c>
+      <c r="J167" s="11" t="inlineStr"/>
       <c r="K167" s="11" t="inlineStr"/>
       <c r="L167" s="11" t="inlineStr"/>
       <c r="M167" s="11" t="inlineStr"/>
-      <c r="N167" s="11" t="inlineStr">
+      <c r="N167" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O167" s="11" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
-        </is>
-      </c>
-      <c r="P167" s="11" t="inlineStr"/>
+          <t>wikipedia(이스타나 = 벤츠 MB100 기반 15인승 밴), alibaba(쌍용 키: 이모빌라이저가 연료분사 ECU 차단)</t>
+        </is>
+      </c>
+      <c r="P167" s="8" t="inlineStr">
+        <is>
+          <t>키 칩 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
@@ -11279,7 +11285,7 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -11341,7 +11347,7 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -11403,7 +11409,7 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11465,7 +11471,7 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -11483,44 +11489,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G171" s="4" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[1세대 키], 4D60x80[로디우스 II 폴딩키]</t>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>막대키,폴딩키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I171" s="11" t="inlineStr"/>
       <c r="J171" s="11" t="inlineStr">
         <is>
-          <t>SSY3, TOY48, KI-7</t>
+          <t>SSY3</t>
         </is>
       </c>
       <c r="K171" s="11" t="inlineStr"/>
       <c r="L171" s="11" t="inlineStr"/>
-      <c r="M171" s="11" t="inlineStr">
-        <is>
-          <t>87510-21100[로디우스 II, 3버튼]</t>
-        </is>
-      </c>
-      <c r="N171" s="4" t="inlineStr">
+      <c r="M171" s="11" t="inlineStr"/>
+      <c r="N171" s="11" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
-        </is>
-      </c>
-      <c r="P171" s="4" t="inlineStr">
-        <is>
-          <t>1세대 키(4D60)와 로디우스 II 폴딩키(4D60x80) 병존 — 키로 구분 필요</t>
-        </is>
-      </c>
+          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
+        </is>
+      </c>
+      <c r="P171" s="11" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
@@ -11535,7 +11533,7 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>2013(단종)</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -11553,44 +11551,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[1세대 키], 4D60x80[로디우스 II 폴딩키]</t>
+      <c r="G172" s="11" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H172" s="11" t="inlineStr">
         <is>
-          <t>막대키,폴딩키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I172" s="11" t="inlineStr"/>
       <c r="J172" s="11" t="inlineStr">
         <is>
-          <t>SSY3, TOY48, KI-7</t>
+          <t>SSY3</t>
         </is>
       </c>
       <c r="K172" s="11" t="inlineStr"/>
       <c r="L172" s="11" t="inlineStr"/>
-      <c r="M172" s="11" t="inlineStr">
-        <is>
-          <t>87510-21100[로디우스 II, 3버튼]</t>
-        </is>
-      </c>
-      <c r="N172" s="4" t="inlineStr">
+      <c r="M172" s="11" t="inlineStr"/>
+      <c r="N172" s="11" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O172" s="11" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
-        </is>
-      </c>
-      <c r="P172" s="4" t="inlineStr">
-        <is>
-          <t>1세대 키(4D60)와 로디우스 II 폴딩키(4D60x80) 병존 — 키로 구분 필요</t>
-        </is>
-      </c>
+          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
+        </is>
+      </c>
+      <c r="P172" s="11" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
@@ -11600,12 +11590,12 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>코란도 투리스모</t>
+          <t>로디우스</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -11625,31 +11615,23 @@
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>4D60x80</t>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
-        </is>
-      </c>
-      <c r="I173" s="11" t="inlineStr">
-        <is>
-          <t>7105121500</t>
-        </is>
-      </c>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I173" s="11" t="inlineStr"/>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>SSY3</t>
         </is>
       </c>
       <c r="K173" s="11" t="inlineStr"/>
       <c r="L173" s="11" t="inlineStr"/>
-      <c r="M173" s="11" t="inlineStr">
-        <is>
-          <t>87510-21100[3버튼]</t>
-        </is>
-      </c>
+      <c r="M173" s="11" t="inlineStr"/>
       <c r="N173" s="11" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
@@ -11657,7 +11639,7 @@
       </c>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
       <c r="P173" s="11" t="inlineStr"/>
@@ -11670,12 +11652,12 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>코란도 투리스모</t>
+          <t>로디우스</t>
         </is>
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -11695,31 +11677,23 @@
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
-          <t>4D60x80</t>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H174" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
-        </is>
-      </c>
-      <c r="I174" s="11" t="inlineStr">
-        <is>
-          <t>7105121500</t>
-        </is>
-      </c>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I174" s="11" t="inlineStr"/>
       <c r="J174" s="11" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>SSY3</t>
         </is>
       </c>
       <c r="K174" s="11" t="inlineStr"/>
       <c r="L174" s="11" t="inlineStr"/>
-      <c r="M174" s="11" t="inlineStr">
-        <is>
-          <t>87510-21100[3버튼]</t>
-        </is>
-      </c>
+      <c r="M174" s="11" t="inlineStr"/>
       <c r="N174" s="11" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
@@ -11727,7 +11701,7 @@
       </c>
       <c r="O174" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
       <c r="P174" s="11" t="inlineStr"/>
@@ -11740,12 +11714,12 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>코란도 투리스모</t>
+          <t>로디우스</t>
         </is>
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -11765,35 +11739,23 @@
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>4D60x80</t>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I175" s="11" t="inlineStr">
-        <is>
-          <t>7105121500</t>
-        </is>
-      </c>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I175" s="11" t="inlineStr"/>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>SSY3</t>
         </is>
       </c>
       <c r="K175" s="11" t="inlineStr"/>
-      <c r="L175" s="11" t="inlineStr">
-        <is>
-          <t>KC R-C-2CG-SmartKeyMV1[2015.06~2019.03]</t>
-        </is>
-      </c>
-      <c r="M175" s="11" t="inlineStr">
-        <is>
-          <t>87510-21100[3버튼]</t>
-        </is>
-      </c>
+      <c r="L175" s="11" t="inlineStr"/>
+      <c r="M175" s="11" t="inlineStr"/>
       <c r="N175" s="11" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
@@ -11801,7 +11763,7 @@
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60)</t>
         </is>
       </c>
       <c r="P175" s="11" t="inlineStr"/>
@@ -11814,12 +11776,12 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>코란도 투리스모</t>
+          <t>로디우스</t>
         </is>
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -11837,48 +11799,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G176" s="11" t="inlineStr">
-        <is>
-          <t>4D60x80</t>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[1세대 키], 4D60x80[로디우스 II 폴딩키]</t>
         </is>
       </c>
       <c r="H176" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I176" s="11" t="inlineStr">
-        <is>
-          <t>7105121500</t>
-        </is>
-      </c>
+          <t>막대키,폴딩키</t>
+        </is>
+      </c>
+      <c r="I176" s="11" t="inlineStr"/>
       <c r="J176" s="11" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>SSY3, TOY48, KI-7</t>
         </is>
       </c>
       <c r="K176" s="11" t="inlineStr"/>
-      <c r="L176" s="11" t="inlineStr">
-        <is>
-          <t>KC R-C-2CG-SmartKeyMV1[2015.06~2019.03]</t>
-        </is>
-      </c>
+      <c r="L176" s="11" t="inlineStr"/>
       <c r="M176" s="11" t="inlineStr">
         <is>
-          <t>87510-21100[3버튼]</t>
-        </is>
-      </c>
-      <c r="N176" s="11" t="inlineStr">
+          <t>87510-21100[로디우스 II, 3버튼]</t>
+        </is>
+      </c>
+      <c r="N176" s="4" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O176" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
-        </is>
-      </c>
-      <c r="P176" s="11" t="inlineStr"/>
+          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="P176" s="4" t="inlineStr">
+        <is>
+          <t>1세대 키(4D60)와 로디우스 II 폴딩키(4D60x80) 병존 — 키로 구분 필요</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
@@ -11888,12 +11846,12 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>코란도 투리스모</t>
+          <t>로디우스</t>
         </is>
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2013(단종)</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -11911,48 +11869,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G177" s="11" t="inlineStr">
-        <is>
-          <t>4D60x80</t>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[1세대 키], 4D60x80[로디우스 II 폴딩키]</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I177" s="11" t="inlineStr">
-        <is>
-          <t>7105121500</t>
-        </is>
-      </c>
+          <t>막대키,폴딩키</t>
+        </is>
+      </c>
+      <c r="I177" s="11" t="inlineStr"/>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>TOY48</t>
+          <t>SSY3, TOY48, KI-7</t>
         </is>
       </c>
       <c r="K177" s="11" t="inlineStr"/>
-      <c r="L177" s="11" t="inlineStr">
-        <is>
-          <t>KC R-C-2CG-SmartKeyMV1[2015.06~2019.03]</t>
-        </is>
-      </c>
+      <c r="L177" s="11" t="inlineStr"/>
       <c r="M177" s="11" t="inlineStr">
         <is>
-          <t>87510-21100[3버튼]</t>
-        </is>
-      </c>
-      <c r="N177" s="11" t="inlineStr">
+          <t>87510-21100[로디우스 II, 3버튼]</t>
+        </is>
+      </c>
+      <c r="N177" s="4" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
-        </is>
-      </c>
-      <c r="P177" s="11" t="inlineStr"/>
+          <t>reidsremotes.com.au(액티언스포츠·카이런·렉스턴·스타빅(=로디우스) 트랜스폰더키 SSY3), myremotekey.com(4D60), remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), [재조사] autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="P177" s="4" t="inlineStr">
+        <is>
+          <t>1세대 키(4D60)와 로디우스 II 폴딩키(4D60x80) 병존 — 키로 구분 필요</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
@@ -11967,66 +11921,428 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G178" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
+        </is>
+      </c>
+      <c r="H178" s="11" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="I178" s="11" t="inlineStr">
+        <is>
+          <t>7105121500</t>
+        </is>
+      </c>
+      <c r="J178" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
+      <c r="K178" s="11" t="inlineStr"/>
+      <c r="L178" s="11" t="inlineStr"/>
+      <c r="M178" s="11" t="inlineStr">
+        <is>
+          <t>87510-21100[3버튼]</t>
+        </is>
+      </c>
+      <c r="N178" s="11" t="inlineStr">
+        <is>
+          <t>이모빌라이저</t>
+        </is>
+      </c>
+      <c r="O178" s="11" t="inlineStr">
+        <is>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="P178" s="11" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>KG모빌리티(쌍용)</t>
+        </is>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>코란도 투리스모</t>
+        </is>
+      </c>
+      <c r="C179" s="11" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G179" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
+        </is>
+      </c>
+      <c r="H179" s="11" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="I179" s="11" t="inlineStr">
+        <is>
+          <t>7105121500</t>
+        </is>
+      </c>
+      <c r="J179" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
+      <c r="K179" s="11" t="inlineStr"/>
+      <c r="L179" s="11" t="inlineStr"/>
+      <c r="M179" s="11" t="inlineStr">
+        <is>
+          <t>87510-21100[3버튼]</t>
+        </is>
+      </c>
+      <c r="N179" s="11" t="inlineStr">
+        <is>
+          <t>이모빌라이저</t>
+        </is>
+      </c>
+      <c r="O179" s="11" t="inlineStr">
+        <is>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="P179" s="11" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>KG모빌리티(쌍용)</t>
+        </is>
+      </c>
+      <c r="B180" s="11" t="inlineStr">
+        <is>
+          <t>코란도 투리스모</t>
+        </is>
+      </c>
+      <c r="C180" s="11" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G180" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
+        </is>
+      </c>
+      <c r="H180" s="11" t="inlineStr">
+        <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I180" s="11" t="inlineStr">
+        <is>
+          <t>7105121500</t>
+        </is>
+      </c>
+      <c r="J180" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
+      <c r="K180" s="11" t="inlineStr"/>
+      <c r="L180" s="11" t="inlineStr">
+        <is>
+          <t>KC R-C-2CG-SmartKeyMV1[2015.06~2019.03]</t>
+        </is>
+      </c>
+      <c r="M180" s="11" t="inlineStr">
+        <is>
+          <t>87510-21100[3버튼]</t>
+        </is>
+      </c>
+      <c r="N180" s="11" t="inlineStr">
+        <is>
+          <t>이모빌라이저</t>
+        </is>
+      </c>
+      <c r="O180" s="11" t="inlineStr">
+        <is>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="P180" s="11" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>KG모빌리티(쌍용)</t>
+        </is>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>코란도 투리스모</t>
+        </is>
+      </c>
+      <c r="C181" s="11" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G181" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
+        </is>
+      </c>
+      <c r="H181" s="11" t="inlineStr">
+        <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I181" s="11" t="inlineStr">
+        <is>
+          <t>7105121500</t>
+        </is>
+      </c>
+      <c r="J181" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
+      <c r="K181" s="11" t="inlineStr"/>
+      <c r="L181" s="11" t="inlineStr">
+        <is>
+          <t>KC R-C-2CG-SmartKeyMV1[2015.06~2019.03]</t>
+        </is>
+      </c>
+      <c r="M181" s="11" t="inlineStr">
+        <is>
+          <t>87510-21100[3버튼]</t>
+        </is>
+      </c>
+      <c r="N181" s="11" t="inlineStr">
+        <is>
+          <t>이모빌라이저</t>
+        </is>
+      </c>
+      <c r="O181" s="11" t="inlineStr">
+        <is>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="P181" s="11" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>KG모빌리티(쌍용)</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="inlineStr">
+        <is>
+          <t>코란도 투리스모</t>
+        </is>
+      </c>
+      <c r="C182" s="11" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G182" s="11" t="inlineStr">
+        <is>
+          <t>4D60x80</t>
+        </is>
+      </c>
+      <c r="H182" s="11" t="inlineStr">
+        <is>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I182" s="11" t="inlineStr">
+        <is>
+          <t>7105121500</t>
+        </is>
+      </c>
+      <c r="J182" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
+      <c r="K182" s="11" t="inlineStr"/>
+      <c r="L182" s="11" t="inlineStr">
+        <is>
+          <t>KC R-C-2CG-SmartKeyMV1[2015.06~2019.03]</t>
+        </is>
+      </c>
+      <c r="M182" s="11" t="inlineStr">
+        <is>
+          <t>87510-21100[3버튼]</t>
+        </is>
+      </c>
+      <c r="N182" s="11" t="inlineStr">
+        <is>
+          <t>이모빌라이저</t>
+        </is>
+      </c>
+      <c r="O182" s="11" t="inlineStr">
+        <is>
+          <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
+        </is>
+      </c>
+      <c r="P182" s="11" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>KG모빌리티(쌍용)</t>
+        </is>
+      </c>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>코란도 투리스모</t>
+        </is>
+      </c>
+      <c r="C183" s="11" t="inlineStr">
+        <is>
           <t>2018(단종)</t>
         </is>
       </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G178" s="11" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G183" s="11" t="inlineStr">
         <is>
           <t>4D60x80</t>
         </is>
       </c>
-      <c r="H178" s="11" t="inlineStr">
+      <c r="H183" s="11" t="inlineStr">
         <is>
           <t>폴딩키,스마트키</t>
         </is>
       </c>
-      <c r="I178" s="11" t="inlineStr">
+      <c r="I183" s="11" t="inlineStr">
         <is>
           <t>7105121500</t>
         </is>
       </c>
-      <c r="J178" s="11" t="inlineStr">
+      <c r="J183" s="11" t="inlineStr">
         <is>
           <t>TOY48</t>
         </is>
       </c>
-      <c r="K178" s="11" t="inlineStr"/>
-      <c r="L178" s="11" t="inlineStr">
+      <c r="K183" s="11" t="inlineStr"/>
+      <c r="L183" s="11" t="inlineStr">
         <is>
           <t>KC R-C-2CG-SmartKeyMV1[2015.06~2019.03]</t>
         </is>
       </c>
-      <c r="M178" s="11" t="inlineStr">
+      <c r="M183" s="11" t="inlineStr">
         <is>
           <t>87510-21100[3버튼]</t>
         </is>
       </c>
-      <c r="N178" s="11" t="inlineStr">
+      <c r="N183" s="11" t="inlineStr">
         <is>
           <t>이모빌라이저</t>
         </is>
       </c>
-      <c r="O178" s="11" t="inlineStr">
+      <c r="O183" s="11" t="inlineStr">
         <is>
           <t>remkeys.com(순정 3버튼 폴딩키 87510-21100 ID70 DST80 433MHz, 블레이드 TOY48 — 코란도 2010-2019·로디우스II 2012-2019·액티언·티볼리 2015), 3dgroupuk.com(SSR1: 87510-21100 80bit ID8E, 블레이드 KI-7 품번 7105121500 — 티볼리 2016-2022·액티언스포츠·코란도·렉스턴), wikipedia(코란도 투리스모 = 로디우스 2세대 페이스리프트 2013.2), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), autokeymaster.ru(순정 폴딩키 스타빅·액티언·티볼리·렉스턴 2013-2021 4D60x80 433MHz 3버튼), originalkey.ru(렉스턴 2014-·스타빅 2014-·티볼리 2015-·액티언 2013- 키 4D60x80)</t>
         </is>
       </c>
-      <c r="P178" s="11" t="inlineStr"/>
+      <c r="P183" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P178"/>
@@ -12040,7 +12356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -12348,6 +12664,30 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="16" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>※ 행 구분 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -5171,7 +5174,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G70" s="14" t="inlineStr">
         <is>
           <t>ID48</t>
         </is>
@@ -5186,7 +5189,7 @@
       <c r="K70" s="11" t="inlineStr"/>
       <c r="L70" s="11" t="inlineStr"/>
       <c r="M70" s="11" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="N70" s="14" t="inlineStr">
         <is>
           <t>VDO 이모박스</t>
         </is>
@@ -5196,11 +5199,7 @@
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
         </is>
       </c>
-      <c r="P70" s="4" t="inlineStr">
-        <is>
-          <t>이모박스 자료가 2002년부터 — 2000·2001년식 직접 확인 안 됨</t>
-        </is>
-      </c>
+      <c r="P70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -5233,7 +5232,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>ID48</t>
         </is>
@@ -5248,7 +5247,7 @@
       <c r="K71" s="11" t="inlineStr"/>
       <c r="L71" s="11" t="inlineStr"/>
       <c r="M71" s="11" t="inlineStr"/>
-      <c r="N71" s="4" t="inlineStr">
+      <c r="N71" s="14" t="inlineStr">
         <is>
           <t>VDO 이모박스</t>
         </is>
@@ -5258,11 +5257,7 @@
           <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
         </is>
       </c>
-      <c r="P71" s="4" t="inlineStr">
-        <is>
-          <t>이모박스 자료가 2002년부터 — 2000·2001년식 직접 확인 안 됨</t>
-        </is>
-      </c>
+      <c r="P71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -5554,7 +5549,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>직접 자료 없음 — 무쏘 기준 추정</t>
+          <t>무쏘 스포츠 전용 자료 없음 — 같은 차대 무쏘 2001~2005 VDO 이모박스 + ID48(autotronics) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5611,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>직접 자료 없음 — 무쏘 기준 추정</t>
+          <t>무쏘 스포츠 전용 자료 없음 — 같은 차대 무쏘 2001~2005 VDO 이모박스 + ID48(autotronics) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5673,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>직접 자료 없음 — 무쏘 기준 추정</t>
+          <t>무쏘 스포츠 전용 자료 없음 — 같은 차대 무쏘 2001~2005 VDO 이모박스 + ID48(autotronics) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5735,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>직접 자료 없음 — 무쏘 기준 추정</t>
+          <t>무쏘 스포츠 전용 자료 없음 — 같은 차대 무쏘 2001~2005 VDO 이모박스 + ID48(autotronics) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -12356,335 +12351,352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr"/>
+      <c r="A2" s="17" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>- 칼리스타(1993-1997)·코란도 훼미리(1988-1996)는 2000년식 이전에 단종되어 행이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제와 다른 모델은 실제 기준으로 적었습니다(체어맨 H ~2014, 체어맨 W ~2017, 코란도 e-모션 2022~2023, 무쏘 EV 2025~, 렉스턴 스포츠는 2025.2 무쏘 스포츠로 차명 변경).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 구형은 VDO 이모빌라이저 박스(이모박스), 액티언·카이런·렉스턴 계열은 이모빌라이저 컨트롤 유닛(ICU, 87110-08B00/09000), 신형 스마트키 차량은 SKM(스마트키 모듈)입니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>- 폴딩키(리모컨 일체형) 품번은 '폴딩키(부품번호)', 스마트키 트랜스미터 품번은 '스마트키(부품번호)' 칸에 적었습니다. 쌍용은 카드키가 없어 카드키 칸은 비었습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID60(4D60)·ID70/DST80(4D70) → O/O/O, ID48(Megamos Crypto) → △/△/△, ID48·ID60 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr"/>
+      <c r="A15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — 이스타나는 키 칩 자료를 찾지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나 연식 범위 밖인 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr"/>
+      <c r="A19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>- 무쏘·코란도·렉스턴(2002-2006): VDO 이모박스(MCU MC68HC05B16) + 메가모스 크립토(ID48) 트랜스폰더 — TMPro 모듈 85 자료. 코란도 2000-2006 블레이드 HYN10(JMA HY-5.P1).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>- 액티언·카이런·렉스턴 계열: 4D-60 칩 키, 블레이드 SSY3(JMA SSA-2P). 순정 키 87170-32030·32020·08D50은 80bit, 87170-08B21은 40bit — 연식 구분 자료가 없어 키 품번으로 확인해야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>- 이모빌라이저 컨트롤 유닛(87110-08B00/09000) 적용: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언 스포츠 2006.04~2007.03. 2007.4 이후 카이런·액티언 계열의 모듈 명칭은 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>- 순정 3버튼 폴딩키 87510-21100(코란도 C·로디우스 II/코란도 투리스모·티볼리 등): 80bit TI 칩(판매처 표기 ID70 DST80 / ID8E). 블레이드는 TOY48(remkeys)과 KI-7(3D Group, 블레이드 품번 7105121500)로 표기가 다릅니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>- [재조사] 토레스 스마트키 칩은 47칩(ID47, Hitag3) — 국내 열쇠기사 카페 자료. 토레스 EVX·액티언(J120)·무쏘 EV는 같은 플랫폼이라 동일 추정(주황).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>- [재조사] 코란도 C(러시아명 New Actyon) 순정 스마트키 4D60x80·비상키 TOY48, 스타빅·액티언·티볼리·렉스턴 순정 폴딩키(2013-2021) 4D60x80, 렉스턴 W 2버튼 키 4D60x80·TOY40.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>- [재조사] 순정 스마트키 R-C-2CG-SmartKeyMV1(4D60x80, 433MHz): 티볼리 2015.03~2020.01, 렉스턴 스포츠 2018.03~2021.12, G4 렉스턴 2017.07~2020.11, 로디우스/스타빅 II 2015.06~2019.03. 이후 신형 키(G4 2020.11~ 8751036C20 등)는 칩 자료 없음(주황).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>- [재조사] 코란도 C(C200) 이모빌라이저는 SKM(키 슬롯)과 엔진 ECU(EMS)가 P-CAN으로 인증. 액티언 2008~2011도 별도 이모빌라이저 컨트롤 유닛 사용(품번 변경).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>- 코란도 C300 스마트키 DST80·HYN14R, 렉스턴 W 2013 스마트키 4D70 DST80(FCC DEO-MT FOBG02), G4 렉스턴 이모빌라이저 = SKM(87570-36010, 2017.07~).</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n"/>
+      <c r="A30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="n"/>
+      <c r="A38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
+      <c r="A47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>- 무쏘 2000·2001: 무쏘 1998~ ID48(29Fxxx), 2001~2005 VDO 이모박스(MC68HC05B16) + ID48(autotronics·TMPro 모듈 85) — 이모박스 자료가 2002부터라던 이전 기록 정정</t>
         </is>
       </c>
     </row>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -12589,7 +12589,7 @@
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -2241,7 +2241,7 @@
       <c r="I27" s="11" t="inlineStr"/>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>HYN10, JMA HY-5.P1</t>
+          <t>HYN10, HY-5.P1[JMA]</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       <c r="I28" s="11" t="inlineStr"/>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>HYN10, JMA HY-5.P1</t>
+          <t>HYN10, HY-5.P1[JMA]</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -2373,7 +2373,7 @@
       <c r="I29" s="11" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>HYN10, JMA HY-5.P1</t>
+          <t>HYN10, HY-5.P1[JMA]</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -2435,7 +2435,7 @@
       <c r="I30" s="11" t="inlineStr"/>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>HYN10, JMA HY-5.P1</t>
+          <t>HYN10, HY-5.P1[JMA]</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       <c r="I31" s="11" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>HYN10, JMA HY-5.P1</t>
+          <t>HYN10, HY-5.P1[JMA]</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr"/>
@@ -2559,7 +2559,7 @@
       <c r="I32" s="11" t="inlineStr"/>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>HYN10, JMA HY-5.P1</t>
+          <t>HYN10, HY-5.P1[JMA]</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
       <c r="I33" s="11" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>HYN10, JMA HY-5.P1</t>
+          <t>HYN10, HY-5.P1[JMA]</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr"/>
@@ -2683,7 +2683,7 @@
       <c r="I34" s="11" t="inlineStr"/>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>HYN10, JMA HY-5.P1</t>
+          <t>HYN10, HY-5.P1[JMA]</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr"/>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K82" s="11" t="n"/>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K83" s="11" t="n"/>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr"/>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr"/>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr"/>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr"/>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K89" s="11" t="n"/>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K90" s="11" t="n"/>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr"/>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr"/>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr"/>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr"/>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr"/>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K98" s="11" t="n"/>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K99" s="11" t="n"/>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K100" s="11" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr"/>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="J102" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr"/>
@@ -9159,7 +9159,7 @@
       <c r="I132" s="11" t="inlineStr"/>
       <c r="J132" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K132" s="11" t="inlineStr"/>
@@ -9221,7 +9221,7 @@
       <c r="I133" s="11" t="inlineStr"/>
       <c r="J133" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K133" s="11" t="inlineStr"/>
@@ -9283,7 +9283,7 @@
       <c r="I134" s="11" t="inlineStr"/>
       <c r="J134" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K134" s="11" t="inlineStr"/>
@@ -9345,7 +9345,7 @@
       <c r="I135" s="11" t="inlineStr"/>
       <c r="J135" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K135" s="11" t="inlineStr"/>
@@ -9407,7 +9407,7 @@
       <c r="I136" s="11" t="inlineStr"/>
       <c r="J136" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K136" s="11" t="inlineStr"/>
@@ -9469,7 +9469,7 @@
       <c r="I137" s="11" t="n"/>
       <c r="J137" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K137" s="11" t="n"/>
@@ -9531,7 +9531,7 @@
       <c r="I138" s="11" t="n"/>
       <c r="J138" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K138" s="11" t="n"/>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="J139" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K139" s="11" t="inlineStr"/>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="J140" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K140" s="11" t="inlineStr"/>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K141" s="11" t="inlineStr"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="J142" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K142" s="11" t="inlineStr"/>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K143" s="11" t="inlineStr"/>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="J144" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K144" s="11" t="inlineStr"/>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>SSY3, JMA SSA-2P</t>
+          <t>SSY3, SSA-2P[JMA]</t>
         </is>
       </c>
       <c r="K145" s="11" t="inlineStr"/>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -688,7 +691,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr"/>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>7199111050[마스터키], 7199111070[발렛키]</t>
+        </is>
+      </c>
       <c r="J2" s="11" t="inlineStr"/>
       <c r="K2" s="11" t="inlineStr"/>
       <c r="L2" s="11" t="inlineStr"/>
@@ -750,7 +757,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>7199111050[마스터키], 7199111070[발렛키]</t>
+        </is>
+      </c>
       <c r="J3" s="11" t="inlineStr"/>
       <c r="K3" s="11" t="inlineStr"/>
       <c r="L3" s="11" t="inlineStr"/>
@@ -812,7 +823,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr"/>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>7199111050[마스터키], 7199111070[발렛키]</t>
+        </is>
+      </c>
       <c r="J4" s="11" t="inlineStr"/>
       <c r="K4" s="11" t="inlineStr"/>
       <c r="L4" s="11" t="inlineStr"/>
@@ -874,7 +889,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr"/>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>7199111050[마스터키], 7199111070[발렛키]</t>
+        </is>
+      </c>
       <c r="J5" s="11" t="inlineStr"/>
       <c r="K5" s="11" t="inlineStr"/>
       <c r="L5" s="11" t="inlineStr"/>
@@ -936,7 +955,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr"/>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>7199111050[마스터키], 7199111070[발렛키]</t>
+        </is>
+      </c>
       <c r="J6" s="11" t="inlineStr"/>
       <c r="K6" s="11" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr"/>
@@ -998,7 +1021,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>7199111050[마스터키], 7199111070[발렛키]</t>
+        </is>
+      </c>
       <c r="J7" s="11" t="inlineStr"/>
       <c r="K7" s="11" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr"/>
@@ -1060,7 +1087,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr"/>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>7199111050[마스터키], 7199111070[발렛키]</t>
+        </is>
+      </c>
       <c r="J8" s="11" t="inlineStr"/>
       <c r="K8" s="11" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
@@ -1122,7 +1153,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>7199111050[마스터키, ~2007.12], 7199111052[마스터키, 2007.12~], 7199111070[발렛키]</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
       <c r="L9" s="11" t="inlineStr"/>
@@ -1184,7 +1219,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr"/>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>7199111052[마스터키]</t>
+        </is>
+      </c>
       <c r="J10" s="11" t="inlineStr"/>
       <c r="K10" s="11" t="inlineStr"/>
       <c r="L10" s="11" t="inlineStr"/>
@@ -1246,7 +1285,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>7199111052[마스터키]</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr"/>
       <c r="L11" s="11" t="inlineStr"/>
@@ -1308,7 +1351,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>7199111052[마스터키]</t>
+        </is>
+      </c>
       <c r="J12" s="11" t="inlineStr"/>
       <c r="K12" s="11" t="inlineStr"/>
       <c r="L12" s="11" t="inlineStr"/>
@@ -1370,7 +1417,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>7199111052[마스터키]</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
       <c r="L13" s="11" t="inlineStr"/>
@@ -1618,7 +1669,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>7105014000</t>
+        </is>
+      </c>
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr"/>
       <c r="L17" s="11" t="inlineStr"/>
@@ -1680,7 +1735,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr"/>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>7105014000</t>
+        </is>
+      </c>
       <c r="J18" s="11" t="inlineStr"/>
       <c r="K18" s="11" t="inlineStr"/>
       <c r="L18" s="11" t="inlineStr"/>
@@ -1742,7 +1801,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>7105014000</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr"/>
       <c r="L19" s="11" t="inlineStr"/>
@@ -1804,7 +1867,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>7105014000[~2011.6], 7105014300[2011.7~]</t>
+        </is>
+      </c>
       <c r="J20" s="11" t="inlineStr"/>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
@@ -1866,7 +1933,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>7105014300</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr"/>
       <c r="L21" s="11" t="inlineStr"/>
@@ -1928,7 +1999,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr"/>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>7105014300</t>
+        </is>
+      </c>
       <c r="J22" s="11" t="inlineStr"/>
       <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr"/>
@@ -1990,7 +2065,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>7105014300</t>
+        </is>
+      </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr"/>
       <c r="L23" s="11" t="inlineStr"/>
@@ -2052,7 +2131,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr"/>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>7105014300</t>
+        </is>
+      </c>
       <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
@@ -2114,7 +2197,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>7105014300</t>
+        </is>
+      </c>
       <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr"/>
       <c r="L25" s="11" t="inlineStr"/>
@@ -2176,7 +2263,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr"/>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>7105014300</t>
+        </is>
+      </c>
       <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr"/>
       <c r="L26" s="11" t="inlineStr"/>
@@ -2238,7 +2329,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr"/>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>71010062A0</t>
+        </is>
+      </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
           <t>HYN10, HY-5.P1[JMA]</t>
@@ -2304,7 +2399,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>71010062A0</t>
+        </is>
+      </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
           <t>HYN10, HY-5.P1[JMA]</t>
@@ -2370,7 +2469,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr"/>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>71010062A0</t>
+        </is>
+      </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
           <t>HYN10, HY-5.P1[JMA]</t>
@@ -2432,7 +2535,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr"/>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>71010062A0</t>
+        </is>
+      </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
           <t>HYN10, HY-5.P1[JMA]</t>
@@ -2494,7 +2601,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr"/>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>71010062A0</t>
+        </is>
+      </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
           <t>HYN10, HY-5.P1[JMA]</t>
@@ -2556,7 +2667,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr"/>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>71010062A0</t>
+        </is>
+      </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
           <t>HYN10, HY-5.P1[JMA]</t>
@@ -5184,7 +5299,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr"/>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
+        </is>
+      </c>
       <c r="J70" s="11" t="inlineStr"/>
       <c r="K70" s="11" t="inlineStr"/>
       <c r="L70" s="11" t="inlineStr"/>
@@ -5242,7 +5361,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr"/>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
+        </is>
+      </c>
       <c r="J71" s="11" t="inlineStr"/>
       <c r="K71" s="11" t="inlineStr"/>
       <c r="L71" s="11" t="inlineStr"/>
@@ -5300,7 +5423,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr"/>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
+        </is>
+      </c>
       <c r="J72" s="11" t="inlineStr"/>
       <c r="K72" s="11" t="inlineStr"/>
       <c r="L72" s="11" t="inlineStr"/>
@@ -5358,7 +5485,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I73" s="11" t="inlineStr"/>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
+        </is>
+      </c>
       <c r="J73" s="11" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr"/>
       <c r="L73" s="11" t="inlineStr"/>
@@ -5416,7 +5547,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I74" s="11" t="inlineStr"/>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
+        </is>
+      </c>
       <c r="J74" s="11" t="inlineStr"/>
       <c r="K74" s="11" t="inlineStr"/>
       <c r="L74" s="11" t="inlineStr"/>
@@ -5474,7 +5609,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I75" s="11" t="inlineStr"/>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
+        </is>
+      </c>
       <c r="J75" s="11" t="inlineStr"/>
       <c r="K75" s="11" t="inlineStr"/>
       <c r="L75" s="11" t="inlineStr"/>
@@ -5532,7 +5671,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr"/>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>0000000319[칩 없음]</t>
+        </is>
+      </c>
       <c r="J76" s="11" t="inlineStr"/>
       <c r="K76" s="11" t="inlineStr"/>
       <c r="L76" s="11" t="inlineStr"/>
@@ -5594,7 +5737,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr"/>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>0000000319[칩 없음], 71001051A0[이모빌라이저, 2003.12~]</t>
+        </is>
+      </c>
       <c r="J77" s="11" t="inlineStr"/>
       <c r="K77" s="11" t="inlineStr"/>
       <c r="L77" s="11" t="inlineStr"/>
@@ -5656,7 +5803,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I78" s="11" t="inlineStr"/>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
+        </is>
+      </c>
       <c r="J78" s="11" t="inlineStr"/>
       <c r="K78" s="11" t="inlineStr"/>
       <c r="L78" s="11" t="inlineStr"/>
@@ -5718,7 +5869,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr"/>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
+        </is>
+      </c>
       <c r="J79" s="11" t="inlineStr"/>
       <c r="K79" s="11" t="inlineStr"/>
       <c r="L79" s="11" t="inlineStr"/>
@@ -9218,7 +9373,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I133" s="11" t="inlineStr"/>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>71050081A0[~2002.7], 71050081A1[2002.7~]</t>
+        </is>
+      </c>
       <c r="J133" s="11" t="inlineStr">
         <is>
           <t>SSY3, SSA-2P[JMA]</t>
@@ -9280,7 +9439,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I134" s="11" t="inlineStr"/>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>71050081A1[~2003.12], 71050081A2[2003.12~], 71050082A0[디젤, 2003.12~]</t>
+        </is>
+      </c>
       <c r="J134" s="11" t="inlineStr">
         <is>
           <t>SSY3, SSA-2P[JMA]</t>
@@ -9342,7 +9505,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I135" s="11" t="inlineStr"/>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>71050081A2[가솔린], 71050082A0[디젤]</t>
+        </is>
+      </c>
       <c r="J135" s="11" t="inlineStr">
         <is>
           <t>SSY3, SSA-2P[JMA]</t>
@@ -9404,7 +9571,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I136" s="11" t="inlineStr"/>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>71050081A2[가솔린], 71050082A0[디젤]</t>
+        </is>
+      </c>
       <c r="J136" s="11" t="inlineStr">
         <is>
           <t>SSY3, SSA-2P[JMA]</t>
@@ -9466,7 +9637,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I137" s="11" t="n"/>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>71050081A2[가솔린], 71050082A0[디젤]</t>
+        </is>
+      </c>
       <c r="J137" s="11" t="inlineStr">
         <is>
           <t>SSY3, SSA-2P[JMA]</t>
@@ -9528,7 +9703,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I138" s="11" t="n"/>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>71050081A2[가솔린], 71050082A0[디젤]</t>
+        </is>
+      </c>
       <c r="J138" s="11" t="inlineStr">
         <is>
           <t>SSY3, SSA-2P[JMA]</t>
@@ -11046,7 +11225,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I163" s="11" t="inlineStr"/>
+      <c r="I163" s="11" t="inlineStr">
+        <is>
+          <t>0000000418</t>
+        </is>
+      </c>
       <c r="J163" s="11" t="inlineStr"/>
       <c r="K163" s="11" t="inlineStr"/>
       <c r="L163" s="11" t="inlineStr"/>
@@ -11096,7 +11279,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I164" s="11" t="inlineStr"/>
+      <c r="I164" s="11" t="inlineStr">
+        <is>
+          <t>0000000418</t>
+        </is>
+      </c>
       <c r="J164" s="11" t="inlineStr"/>
       <c r="K164" s="11" t="inlineStr"/>
       <c r="L164" s="11" t="inlineStr"/>
@@ -11146,7 +11333,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I165" s="11" t="inlineStr"/>
+      <c r="I165" s="11" t="inlineStr">
+        <is>
+          <t>0000000418</t>
+        </is>
+      </c>
       <c r="J165" s="11" t="inlineStr"/>
       <c r="K165" s="11" t="inlineStr"/>
       <c r="L165" s="11" t="inlineStr"/>
@@ -11196,7 +11387,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I166" s="11" t="inlineStr"/>
+      <c r="I166" s="11" t="inlineStr">
+        <is>
+          <t>0000000418</t>
+        </is>
+      </c>
       <c r="J166" s="11" t="inlineStr"/>
       <c r="K166" s="11" t="inlineStr"/>
       <c r="L166" s="11" t="inlineStr"/>
@@ -11246,7 +11441,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I167" s="11" t="inlineStr"/>
+      <c r="I167" s="11" t="inlineStr">
+        <is>
+          <t>0000000418</t>
+        </is>
+      </c>
       <c r="J167" s="11" t="inlineStr"/>
       <c r="K167" s="11" t="inlineStr"/>
       <c r="L167" s="11" t="inlineStr"/>
@@ -11308,7 +11507,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I168" s="11" t="inlineStr"/>
+      <c r="I168" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤], 7106A21310[가솔린]</t>
+        </is>
+      </c>
       <c r="J168" s="11" t="inlineStr">
         <is>
           <t>SSY3</t>
@@ -11370,7 +11573,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I169" s="11" t="inlineStr"/>
+      <c r="I169" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤], 7106A21310[가솔린]</t>
+        </is>
+      </c>
       <c r="J169" s="11" t="inlineStr">
         <is>
           <t>SSY3</t>
@@ -11432,7 +11639,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I170" s="11" t="inlineStr"/>
+      <c r="I170" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤], 7106A21310[가솔린]</t>
+        </is>
+      </c>
       <c r="J170" s="11" t="inlineStr">
         <is>
           <t>SSY3</t>
@@ -11494,7 +11705,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I171" s="11" t="inlineStr"/>
+      <c r="I171" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤], 7106A21310[가솔린]</t>
+        </is>
+      </c>
       <c r="J171" s="11" t="inlineStr">
         <is>
           <t>SSY3</t>
@@ -11556,7 +11771,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I172" s="11" t="inlineStr"/>
+      <c r="I172" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤], 7106A21310[가솔린]</t>
+        </is>
+      </c>
       <c r="J172" s="11" t="inlineStr">
         <is>
           <t>SSY3</t>
@@ -11618,7 +11837,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I173" s="11" t="inlineStr"/>
+      <c r="I173" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤], 7106A21310[가솔린]</t>
+        </is>
+      </c>
       <c r="J173" s="11" t="inlineStr">
         <is>
           <t>SSY3</t>
@@ -11680,7 +11903,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I174" s="11" t="inlineStr"/>
+      <c r="I174" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤], 7106A21310[가솔린]</t>
+        </is>
+      </c>
       <c r="J174" s="11" t="inlineStr">
         <is>
           <t>SSY3</t>
@@ -11742,7 +11969,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I175" s="11" t="inlineStr"/>
+      <c r="I175" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤], 7106A21310[가솔린]</t>
+        </is>
+      </c>
       <c r="J175" s="11" t="inlineStr">
         <is>
           <t>SSY3</t>
@@ -12351,7 +12582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -12700,6 +12931,13 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>- KGM(쌍용) 순정 키 번호: catcar.info 쌍용 EPC KEY SET 그룹(좌핸들, 이모빌라이저 사양, 생산 기간) — 체어맨 H 7199111050(2000.1~2007.12)·7199111052(2007.12~2011.4)·발렛키 7199111070, 체어맨 W 7105014000(~2011.6)·7105014300(2011.7~), 코란도 71010062A0(이모빌라이저), 무쏘 71001051A0(이모빌라이저)·0000000319(칩 없음), 렉스턴 71050081A0(~2002.7)·A1(~2003.12)·A2(~2006.2)·디젤 71050082A0(2003.12~), 로디우스 7106A21320(디젤)·7106A21310(가솔린), 이스타나 0000000418</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1483,7 +1486,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr"/>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>7199111052[마스터키, 추정]</t>
+        </is>
+      </c>
       <c r="J14" s="11" t="inlineStr"/>
       <c r="K14" s="11" t="inlineStr"/>
       <c r="L14" s="11" t="inlineStr"/>
@@ -1545,7 +1552,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>7199111052[마스터키, 추정]</t>
+        </is>
+      </c>
       <c r="J15" s="11" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr"/>
       <c r="L15" s="11" t="inlineStr"/>
@@ -1607,7 +1618,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr"/>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>7199111052[마스터키, 추정]</t>
+        </is>
+      </c>
       <c r="J16" s="11" t="inlineStr"/>
       <c r="K16" s="11" t="inlineStr"/>
       <c r="L16" s="11" t="inlineStr"/>
@@ -2733,7 +2748,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr"/>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>71010062A0</t>
+        </is>
+      </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
           <t>HYN10, HY-5.P1[JMA]</t>
@@ -2795,7 +2814,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>71010062A0[추정]</t>
+        </is>
+      </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
           <t>HYN10, HY-5.P1[JMA]</t>
@@ -9311,7 +9334,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I132" s="11" t="inlineStr"/>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>71050081A0[추정]</t>
+        </is>
+      </c>
       <c r="J132" s="11" t="inlineStr">
         <is>
           <t>SSY3, SSA-2P[JMA]</t>
@@ -10231,7 +10258,11 @@
           <t>막대키,폴딩키,스마트키</t>
         </is>
       </c>
-      <c r="I146" s="11" t="n"/>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>710A108D00[키 세트, 디젤 2.7], 710A108D20[키 세트, 가솔린 3.2], 710A108D70[키 세트, 디젤 2.0]</t>
+        </is>
+      </c>
       <c r="J146" s="11" t="inlineStr">
         <is>
           <t>TOY40[리모컨키]</t>
@@ -10297,7 +10328,11 @@
           <t>막대키,폴딩키,스마트키</t>
         </is>
       </c>
-      <c r="I147" s="11" t="n"/>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>710A108D00[키 세트, 디젤 2.7], 710A108D20[키 세트, 가솔린 3.2], 710A108D70[키 세트, 디젤 2.0]</t>
+        </is>
+      </c>
       <c r="J147" s="11" t="inlineStr">
         <is>
           <t>TOY40[리모컨키]</t>
@@ -10363,7 +10398,11 @@
           <t>막대키,폴딩키,스마트키</t>
         </is>
       </c>
-      <c r="I148" s="11" t="n"/>
+      <c r="I148" s="11" t="inlineStr">
+        <is>
+          <t>710A108D00[키 세트, 디젤 2.7], 710A108D20[키 세트, 가솔린 3.2], 710A108D70[키 세트, 디젤 2.0]</t>
+        </is>
+      </c>
       <c r="J148" s="11" t="inlineStr">
         <is>
           <t>TOY40[리모컨키]</t>
@@ -10429,7 +10468,11 @@
           <t>막대키,폴딩키,스마트키</t>
         </is>
       </c>
-      <c r="I149" s="11" t="n"/>
+      <c r="I149" s="11" t="inlineStr">
+        <is>
+          <t>710A108D00[키 세트, 디젤 2.7], 710A108D20[키 세트, 가솔린 3.2], 710A108D70[키 세트, 디젤 2.0]</t>
+        </is>
+      </c>
       <c r="J149" s="11" t="inlineStr">
         <is>
           <t>TOY40[리모컨키]</t>
@@ -10495,7 +10538,11 @@
           <t>막대키,폴딩키,스마트키</t>
         </is>
       </c>
-      <c r="I150" s="11" t="n"/>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>710A108D00[키 세트, 디젤 2.7], 710A108D20[키 세트, 가솔린 3.2], 710A108D70[키 세트, 디젤 2.0]</t>
+        </is>
+      </c>
       <c r="J150" s="11" t="inlineStr">
         <is>
           <t>TOY40[리모컨키]</t>
@@ -10561,7 +10608,11 @@
           <t>막대키,폴딩키,스마트키</t>
         </is>
       </c>
-      <c r="I151" s="11" t="n"/>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>710A108D00[키 세트, 디젤 2.7], 710A108D20[키 세트, 가솔린 3.2], 710A108D70[키 세트, 디젤 2.0]</t>
+        </is>
+      </c>
       <c r="J151" s="11" t="inlineStr">
         <is>
           <t>TOY40[리모컨키]</t>
@@ -12035,7 +12086,11 @@
           <t>막대키,폴딩키</t>
         </is>
       </c>
-      <c r="I176" s="11" t="inlineStr"/>
+      <c r="I176" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤, 추정]</t>
+        </is>
+      </c>
       <c r="J176" s="11" t="inlineStr">
         <is>
           <t>SSY3, TOY48, KI-7</t>
@@ -12105,7 +12160,11 @@
           <t>막대키,폴딩키</t>
         </is>
       </c>
-      <c r="I177" s="11" t="inlineStr"/>
+      <c r="I177" s="11" t="inlineStr">
+        <is>
+          <t>7106A21320[디젤, 추정]</t>
+        </is>
+      </c>
       <c r="J177" s="11" t="inlineStr">
         <is>
           <t>SSY3, TOY48, KI-7</t>
@@ -12582,350 +12641,350 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr"/>
+      <c r="A2" s="18" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>- 칼리스타(1993-1997)·코란도 훼미리(1988-1996)는 2000년식 이전에 단종되어 행이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제와 다른 모델은 실제 기준으로 적었습니다(체어맨 H ~2014, 체어맨 W ~2017, 코란도 e-모션 2022~2023, 무쏘 EV 2025~, 렉스턴 스포츠는 2025.2 무쏘 스포츠로 차명 변경).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 구형은 VDO 이모빌라이저 박스(이모박스), 액티언·카이런·렉스턴 계열은 이모빌라이저 컨트롤 유닛(ICU, 87110-08B00/09000), 신형 스마트키 차량은 SKM(스마트키 모듈)입니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>- 폴딩키(리모컨 일체형) 품번은 '폴딩키(부품번호)', 스마트키 트랜스미터 품번은 '스마트키(부품번호)' 칸에 적었습니다. 쌍용은 카드키가 없어 카드키 칸은 비었습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID60(4D60)·ID70/DST80(4D70) → O/O/O, ID48(Megamos Crypto) → △/△/△, ID48·ID60 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr"/>
+      <c r="A15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — 이스타나는 키 칩 자료를 찾지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나 연식 범위 밖인 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr"/>
+      <c r="A19" s="18" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>- 무쏘·코란도·렉스턴(2002-2006): VDO 이모박스(MCU MC68HC05B16) + 메가모스 크립토(ID48) 트랜스폰더 — TMPro 모듈 85 자료. 코란도 2000-2006 블레이드 HYN10(JMA HY-5.P1).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>- 액티언·카이런·렉스턴 계열: 4D-60 칩 키, 블레이드 SSY3(JMA SSA-2P). 순정 키 87170-32030·32020·08D50은 80bit, 87170-08B21은 40bit — 연식 구분 자료가 없어 키 품번으로 확인해야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>- 이모빌라이저 컨트롤 유닛(87110-08B00/09000) 적용: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언 스포츠 2006.04~2007.03. 2007.4 이후 카이런·액티언 계열의 모듈 명칭은 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>- 순정 3버튼 폴딩키 87510-21100(코란도 C·로디우스 II/코란도 투리스모·티볼리 등): 80bit TI 칩(판매처 표기 ID70 DST80 / ID8E). 블레이드는 TOY48(remkeys)과 KI-7(3D Group, 블레이드 품번 7105121500)로 표기가 다릅니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>- [재조사] 토레스 스마트키 칩은 47칩(ID47, Hitag3) — 국내 열쇠기사 카페 자료. 토레스 EVX·액티언(J120)·무쏘 EV는 같은 플랫폼이라 동일 추정(주황).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>- [재조사] 코란도 C(러시아명 New Actyon) 순정 스마트키 4D60x80·비상키 TOY48, 스타빅·액티언·티볼리·렉스턴 순정 폴딩키(2013-2021) 4D60x80, 렉스턴 W 2버튼 키 4D60x80·TOY40.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>- [재조사] 순정 스마트키 R-C-2CG-SmartKeyMV1(4D60x80, 433MHz): 티볼리 2015.03~2020.01, 렉스턴 스포츠 2018.03~2021.12, G4 렉스턴 2017.07~2020.11, 로디우스/스타빅 II 2015.06~2019.03. 이후 신형 키(G4 2020.11~ 8751036C20 등)는 칩 자료 없음(주황).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>- [재조사] 코란도 C(C200) 이모빌라이저는 SKM(키 슬롯)과 엔진 ECU(EMS)가 P-CAN으로 인증. 액티언 2008~2011도 별도 이모빌라이저 컨트롤 유닛 사용(품번 변경).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>- 코란도 C300 스마트키 DST80·HYN14R, 렉스턴 W 2013 스마트키 4D70 DST80(FCC DEO-MT FOBG02), G4 렉스턴 이모빌라이저 = SKM(87570-36010, 2017.07~).</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="n"/>
+      <c r="A30" s="18" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n"/>
+      <c r="A38" s="18" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n"/>
+      <c r="A47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="n"/>
+      <c r="A51" s="18" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>- 무쏘 2000·2001: 무쏘 1998~ ID48(29Fxxx), 2001~2005 VDO 이모박스(MC68HC05B16) + ID48(autotronics·TMPro 모듈 85) — 이모박스 자료가 2002부터라던 이전 기록 정정</t>
         </is>
@@ -12935,6 +12994,13 @@
       <c r="A54" s="18" t="inlineStr">
         <is>
           <t>- KGM(쌍용) 순정 키 번호: catcar.info 쌍용 EPC KEY SET 그룹(좌핸들, 이모빌라이저 사양, 생산 기간) — 체어맨 H 7199111050(2000.1~2007.12)·7199111052(2007.12~2011.4)·발렛키 7199111070, 체어맨 W 7105014000(~2011.6)·7105014300(2011.7~), 코란도 71010062A0(이모빌라이저), 무쏘 71001051A0(이모빌라이저)·0000000319(칩 없음), 렉스턴 71050081A0(~2002.7)·A1(~2003.12)·A2(~2006.2)·디젤 71050082A0(2003.12~), 로디우스 7106A21320(디젤)·7106A21310(가솔린), 이스타나 0000000418</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>- KGM(쌍용) 보완: 뉴 코란도 71010062A0(이모빌라이저 블랭킹 키, ~2005.9.23 생산), 렉스턴 2001년식은 EPC 시작(2002.2) 이전이라 71050081A0 [추정], 렉스턴 W(2012.6~) 키 세트 710A108D00(D27, 디젤 2.7)·710A108D20(E32, 가솔린 3.2)·710A108D70(D20R, 디젤 2.0) — catcar.info 쌍용 EPC(좌핸들), 체어맨 H 2012~2014·로디우스 2012~2013은 EPC 마지막 번호를 [추정]으로 기재</t>
         </is>
       </c>
     </row>

--- a/KG모빌리티(쌍용)_models.xlsx
+++ b/KG모빌리티(쌍용)_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -5327,7 +5330,11 @@
           <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
         </is>
       </c>
-      <c r="J70" s="11" t="inlineStr"/>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K70" s="11" t="inlineStr"/>
       <c r="L70" s="11" t="inlineStr"/>
       <c r="M70" s="11" t="inlineStr"/>
@@ -5338,7 +5345,7 @@
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P70" s="14" t="n"/>
@@ -5389,7 +5396,11 @@
           <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
         </is>
       </c>
-      <c r="J71" s="11" t="inlineStr"/>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K71" s="11" t="inlineStr"/>
       <c r="L71" s="11" t="inlineStr"/>
       <c r="M71" s="11" t="inlineStr"/>
@@ -5400,7 +5411,7 @@
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P71" s="14" t="n"/>
@@ -5451,7 +5462,11 @@
           <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
         </is>
       </c>
-      <c r="J72" s="11" t="inlineStr"/>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K72" s="11" t="inlineStr"/>
       <c r="L72" s="11" t="inlineStr"/>
       <c r="M72" s="11" t="inlineStr"/>
@@ -5462,7 +5477,7 @@
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P72" s="11" t="inlineStr"/>
@@ -5513,7 +5528,11 @@
           <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
         </is>
       </c>
-      <c r="J73" s="11" t="inlineStr"/>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K73" s="11" t="inlineStr"/>
       <c r="L73" s="11" t="inlineStr"/>
       <c r="M73" s="11" t="inlineStr"/>
@@ -5524,7 +5543,7 @@
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P73" s="11" t="inlineStr"/>
@@ -5575,7 +5594,11 @@
           <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
         </is>
       </c>
-      <c r="J74" s="11" t="inlineStr"/>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K74" s="11" t="inlineStr"/>
       <c r="L74" s="11" t="inlineStr"/>
       <c r="M74" s="11" t="inlineStr"/>
@@ -5586,7 +5609,7 @@
       </c>
       <c r="O74" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P74" s="11" t="inlineStr"/>
@@ -5637,7 +5660,11 @@
           <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
         </is>
       </c>
-      <c r="J75" s="11" t="inlineStr"/>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K75" s="11" t="inlineStr"/>
       <c r="L75" s="11" t="inlineStr"/>
       <c r="M75" s="11" t="inlineStr"/>
@@ -5648,7 +5675,7 @@
       </c>
       <c r="O75" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), autotronics.co.uk(무쏘 이모빌라이저 트랜스폰더 리코딩), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P75" s="11" t="inlineStr"/>
@@ -5699,7 +5726,11 @@
           <t>0000000319[칩 없음]</t>
         </is>
       </c>
-      <c r="J76" s="11" t="inlineStr"/>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K76" s="11" t="inlineStr"/>
       <c r="L76" s="11" t="inlineStr"/>
       <c r="M76" s="11" t="inlineStr"/>
@@ -5710,7 +5741,7 @@
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
@@ -5765,7 +5796,11 @@
           <t>0000000319[칩 없음], 71001051A0[이모빌라이저, 2003.12~]</t>
         </is>
       </c>
-      <c r="J77" s="11" t="inlineStr"/>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K77" s="11" t="inlineStr"/>
       <c r="L77" s="11" t="inlineStr"/>
       <c r="M77" s="11" t="inlineStr"/>
@@ -5776,7 +5811,7 @@
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
@@ -5831,7 +5866,11 @@
           <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
         </is>
       </c>
-      <c r="J78" s="11" t="inlineStr"/>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K78" s="11" t="inlineStr"/>
       <c r="L78" s="11" t="inlineStr"/>
       <c r="M78" s="11" t="inlineStr"/>
@@ -5842,7 +5881,7 @@
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
@@ -5897,7 +5936,11 @@
           <t>71001051A0[이모빌라이저], 0000000319[칩 없음]</t>
         </is>
       </c>
-      <c r="J79" s="11" t="inlineStr"/>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>SSY2</t>
+        </is>
+      </c>
       <c r="K79" s="11" t="inlineStr"/>
       <c r="L79" s="11" t="inlineStr"/>
       <c r="M79" s="11" t="inlineStr"/>
@@ -5908,7 +5951,7 @@
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시)</t>
+          <t>tmpro2.com·abkeys.com(TMPro 모듈85 쌍용 VDO 이모박스: 무쏘·코란도·렉스턴 2002-2006, 메가모스 크립토/TS48, MC68HC05B16), wikipedia(무쏘 스포츠 2002 출시), Autokeymaster(SsangYong Musso 1993-2011 ID48 키 블레이드 SSY2)</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
@@ -8069,7 +8112,11 @@
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr"/>
-      <c r="J111" s="11" t="inlineStr"/>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K111" s="11" t="inlineStr"/>
       <c r="L111" s="11" t="inlineStr">
         <is>
@@ -8084,7 +8131,7 @@
       </c>
       <c r="O111" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P111" s="11" t="inlineStr"/>
@@ -8131,7 +8178,11 @@
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr"/>
-      <c r="J112" s="11" t="inlineStr"/>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K112" s="11" t="inlineStr"/>
       <c r="L112" s="11" t="inlineStr">
         <is>
@@ -8146,7 +8197,7 @@
       </c>
       <c r="O112" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P112" s="11" t="inlineStr"/>
@@ -8193,7 +8244,11 @@
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr"/>
-      <c r="J113" s="11" t="inlineStr"/>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K113" s="11" t="inlineStr"/>
       <c r="L113" s="11" t="inlineStr">
         <is>
@@ -8208,7 +8263,7 @@
       </c>
       <c r="O113" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P113" s="11" t="inlineStr"/>
@@ -8255,7 +8310,11 @@
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr"/>
-      <c r="J114" s="11" t="inlineStr"/>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K114" s="11" t="inlineStr"/>
       <c r="L114" s="11" t="inlineStr">
         <is>
@@ -8270,7 +8329,7 @@
       </c>
       <c r="O114" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P114" s="11" t="inlineStr"/>
@@ -8305,7 +8364,11 @@
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr"/>
-      <c r="J115" s="11" t="inlineStr"/>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K115" s="11" t="inlineStr"/>
       <c r="L115" s="11" t="n"/>
       <c r="M115" s="11" t="inlineStr"/>
@@ -8316,7 +8379,7 @@
       </c>
       <c r="O115" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
@@ -8355,7 +8418,11 @@
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr"/>
-      <c r="J116" s="11" t="inlineStr"/>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K116" s="11" t="inlineStr"/>
       <c r="L116" s="11" t="n"/>
       <c r="M116" s="11" t="inlineStr"/>
@@ -8366,7 +8433,7 @@
       </c>
       <c r="O116" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P116" s="4" t="inlineStr">
@@ -8405,7 +8472,11 @@
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr"/>
-      <c r="J117" s="11" t="inlineStr"/>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K117" s="11" t="inlineStr"/>
       <c r="L117" s="11" t="n"/>
       <c r="M117" s="11" t="inlineStr"/>
@@ -8416,7 +8487,7 @@
       </c>
       <c r="O117" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용</t>
+          <t>ebay(2024 렉스턴 스포츠 노블레스 스마트키 모듈 8757038210), autodaily.co.kr(2025.2 무쏘 스포츠·무쏘 칸으로 차명 변경), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), alibaba/ebay(스마트키 8751036B00: 티볼리·렉스턴 스포츠, 무쏘 스포츠 2019-2021), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 렉스턴 스포츠 2018.03~2021.12에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
@@ -8467,7 +8538,11 @@
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr"/>
-      <c r="J118" s="11" t="inlineStr"/>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K118" s="11" t="inlineStr"/>
       <c r="L118" s="11" t="n"/>
       <c r="M118" s="11" t="inlineStr"/>
@@ -8478,7 +8553,7 @@
       </c>
       <c r="O118" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
@@ -8529,7 +8604,11 @@
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr"/>
-      <c r="J119" s="11" t="inlineStr"/>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K119" s="11" t="inlineStr"/>
       <c r="L119" s="11" t="n"/>
       <c r="M119" s="11" t="inlineStr"/>
@@ -8540,7 +8619,7 @@
       </c>
       <c r="O119" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
@@ -8591,7 +8670,11 @@
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr"/>
-      <c r="J120" s="11" t="inlineStr"/>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K120" s="11" t="inlineStr"/>
       <c r="L120" s="11" t="n"/>
       <c r="M120" s="11" t="inlineStr"/>
@@ -8602,7 +8685,7 @@
       </c>
       <c r="O120" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
@@ -8653,7 +8736,11 @@
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr"/>
-      <c r="J121" s="11" t="inlineStr"/>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K121" s="11" t="inlineStr"/>
       <c r="L121" s="11" t="n"/>
       <c r="M121" s="11" t="inlineStr"/>
@@ -8664,7 +8751,7 @@
       </c>
       <c r="O121" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
@@ -8715,7 +8802,11 @@
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr"/>
-      <c r="J122" s="11" t="inlineStr"/>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K122" s="11" t="inlineStr"/>
       <c r="L122" s="11" t="n"/>
       <c r="M122" s="11" t="inlineStr"/>
@@ -8726,7 +8817,7 @@
       </c>
       <c r="O122" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법)</t>
+          <t>wikipedia(토레스 2022.7 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), youtube(토레스 2022년식 스마트키 등록 방법), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P122" s="4" t="inlineStr">
@@ -8777,7 +8868,11 @@
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr"/>
-      <c r="J123" s="11" t="inlineStr"/>
+      <c r="J123" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K123" s="11" t="inlineStr"/>
       <c r="L123" s="11" t="n"/>
       <c r="M123" s="11" t="inlineStr"/>
@@ -8788,7 +8883,7 @@
       </c>
       <c r="O123" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
@@ -8839,7 +8934,11 @@
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr"/>
-      <c r="J124" s="11" t="inlineStr"/>
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K124" s="11" t="inlineStr"/>
       <c r="L124" s="11" t="n"/>
       <c r="M124" s="11" t="inlineStr"/>
@@ -8850,7 +8949,7 @@
       </c>
       <c r="O124" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
@@ -8901,7 +9000,11 @@
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr"/>
-      <c r="J125" s="11" t="inlineStr"/>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K125" s="11" t="inlineStr"/>
       <c r="L125" s="11" t="n"/>
       <c r="M125" s="11" t="inlineStr"/>
@@ -8912,7 +9015,7 @@
       </c>
       <c r="O125" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -8963,7 +9066,11 @@
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr"/>
-      <c r="J126" s="11" t="inlineStr"/>
+      <c r="J126" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K126" s="11" t="inlineStr"/>
       <c r="L126" s="11" t="n"/>
       <c r="M126" s="11" t="inlineStr"/>
@@ -8974,7 +9081,7 @@
       </c>
       <c r="O126" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>ebay(2024 KGM 토레스 EVX 스마트키 트랜스미터), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -9025,7 +9132,11 @@
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr"/>
-      <c r="J127" s="11" t="inlineStr"/>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K127" s="11" t="inlineStr"/>
       <c r="L127" s="11" t="n"/>
       <c r="M127" s="11" t="inlineStr"/>
@@ -9036,7 +9147,7 @@
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
@@ -9087,7 +9198,11 @@
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr"/>
-      <c r="J128" s="11" t="inlineStr"/>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K128" s="11" t="inlineStr"/>
       <c r="L128" s="11" t="n"/>
       <c r="M128" s="11" t="inlineStr"/>
@@ -9098,7 +9213,7 @@
       </c>
       <c r="O128" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -9149,7 +9264,11 @@
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr"/>
-      <c r="J129" s="11" t="inlineStr"/>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K129" s="11" t="inlineStr"/>
       <c r="L129" s="11" t="n"/>
       <c r="M129" s="11" t="inlineStr"/>
@@ -9160,7 +9279,7 @@
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>wikipedia(KGM 액티언 J120 2024.7 공개, 토레스와 플랫폼 공유), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -9211,7 +9330,11 @@
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr"/>
-      <c r="J130" s="11" t="inlineStr"/>
+      <c r="J130" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K130" s="11" t="inlineStr"/>
       <c r="L130" s="11" t="n"/>
       <c r="M130" s="11" t="inlineStr"/>
@@ -9222,7 +9345,7 @@
       </c>
       <c r="O130" s="11" t="inlineStr">
         <is>
-          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
@@ -9273,7 +9396,11 @@
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr"/>
-      <c r="J131" s="11" t="inlineStr"/>
+      <c r="J131" s="11" t="inlineStr">
+        <is>
+          <t>TOY48[추정]</t>
+        </is>
+      </c>
       <c r="K131" s="11" t="inlineStr"/>
       <c r="L131" s="11" t="n"/>
       <c r="M131" s="11" t="inlineStr"/>
@@ -9284,7 +9411,7 @@
       </c>
       <c r="O131" s="11" t="inlineStr">
         <is>
-          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인)</t>
+          <t>jasonryu.net/namu.wiki(무쏘 EV 2025.3 출시), [재조사] cafe.daum.net/soskey 열쇠 기사단 자동차키 자료실(쌍용 신형 토레스 스마트키: 이모빌라이저 칩 47번 칩, 기존과 같은 디자인), Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48) — 같은 회사 스마트키 비상키 기준 추정(신형 전용 자료 없음)</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
@@ -10679,7 +10806,11 @@
         </is>
       </c>
       <c r="I152" s="11" t="inlineStr"/>
-      <c r="J152" s="11" t="inlineStr"/>
+      <c r="J152" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K152" s="11" t="inlineStr"/>
       <c r="L152" s="11" t="inlineStr">
         <is>
@@ -10694,7 +10825,7 @@
       </c>
       <c r="O152" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P152" s="11" t="inlineStr"/>
@@ -10741,7 +10872,11 @@
         </is>
       </c>
       <c r="I153" s="11" t="inlineStr"/>
-      <c r="J153" s="11" t="inlineStr"/>
+      <c r="J153" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K153" s="11" t="inlineStr"/>
       <c r="L153" s="11" t="inlineStr">
         <is>
@@ -10756,7 +10891,7 @@
       </c>
       <c r="O153" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P153" s="11" t="inlineStr"/>
@@ -10803,7 +10938,11 @@
         </is>
       </c>
       <c r="I154" s="11" t="inlineStr"/>
-      <c r="J154" s="11" t="inlineStr"/>
+      <c r="J154" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K154" s="11" t="inlineStr"/>
       <c r="L154" s="11" t="inlineStr">
         <is>
@@ -10818,7 +10957,7 @@
       </c>
       <c r="O154" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P154" s="11" t="inlineStr"/>
@@ -10865,7 +11004,11 @@
         </is>
       </c>
       <c r="I155" s="11" t="n"/>
-      <c r="J155" s="11" t="n"/>
+      <c r="J155" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K155" s="11" t="n"/>
       <c r="L155" s="11" t="inlineStr">
         <is>
@@ -10880,7 +11023,7 @@
       </c>
       <c r="O155" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P155" s="14" t="n"/>
@@ -10915,7 +11058,11 @@
         </is>
       </c>
       <c r="I156" s="11" t="n"/>
-      <c r="J156" s="11" t="n"/>
+      <c r="J156" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K156" s="11" t="n"/>
       <c r="L156" s="11" t="inlineStr">
         <is>
@@ -10930,7 +11077,7 @@
       </c>
       <c r="O156" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
@@ -10969,7 +11116,11 @@
         </is>
       </c>
       <c r="I157" s="11" t="inlineStr"/>
-      <c r="J157" s="11" t="inlineStr"/>
+      <c r="J157" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K157" s="11" t="inlineStr"/>
       <c r="L157" s="11" t="inlineStr">
         <is>
@@ -10984,7 +11135,7 @@
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
@@ -11023,7 +11174,11 @@
         </is>
       </c>
       <c r="I158" s="11" t="inlineStr"/>
-      <c r="J158" s="11" t="inlineStr"/>
+      <c r="J158" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K158" s="11" t="inlineStr"/>
       <c r="L158" s="11" t="inlineStr">
         <is>
@@ -11038,7 +11193,7 @@
       </c>
       <c r="O158" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), kogoos.com(G4 렉스턴 스마트키 8751036C20, 2020.11~2022.04), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P158" s="4" t="inlineStr">
@@ -11077,7 +11232,11 @@
         </is>
       </c>
       <c r="I159" s="11" t="inlineStr"/>
-      <c r="J159" s="11" t="inlineStr"/>
+      <c r="J159" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K159" s="11" t="inlineStr"/>
       <c r="L159" s="11" t="n"/>
       <c r="M159" s="11" t="inlineStr"/>
@@ -11088,7 +11247,7 @@
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P159" s="4" t="inlineStr">
@@ -11127,7 +11286,11 @@
         </is>
       </c>
       <c r="I160" s="11" t="inlineStr"/>
-      <c r="J160" s="11" t="inlineStr"/>
+      <c r="J160" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K160" s="11" t="inlineStr"/>
       <c r="L160" s="11" t="n"/>
       <c r="M160" s="11" t="inlineStr"/>
@@ -11138,7 +11301,7 @@
       </c>
       <c r="O160" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P160" s="4" t="inlineStr">
@@ -11177,7 +11340,11 @@
         </is>
       </c>
       <c r="I161" s="11" t="inlineStr"/>
-      <c r="J161" s="11" t="inlineStr"/>
+      <c r="J161" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K161" s="11" t="inlineStr"/>
       <c r="L161" s="11" t="n"/>
       <c r="M161" s="11" t="inlineStr"/>
@@ -11188,7 +11355,7 @@
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P161" s="4" t="inlineStr">
@@ -11227,7 +11394,11 @@
         </is>
       </c>
       <c r="I162" s="11" t="inlineStr"/>
-      <c r="J162" s="11" t="inlineStr"/>
+      <c r="J162" s="11" t="inlineStr">
+        <is>
+          <t>TOY48</t>
+        </is>
+      </c>
       <c r="K162" s="11" t="inlineStr"/>
       <c r="L162" s="11" t="n"/>
       <c r="M162" s="11" t="inlineStr"/>
@@ -11238,7 +11409,7 @@
       </c>
       <c r="O162" s="11" t="inlineStr">
         <is>
-          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용</t>
+          <t>scandoc.online(렉스턴 G4 Y400 이모빌라이저 = SMART Key Module), ebay.de(렉스턴 Y400 07.17- 스마트키 컨트롤 유닛 87570-36010), [재조사] originalkey.ru(순정 스마트키 R-C-2CG-SmartKeyMV1: 티볼리 2015.03~2020.01·렉스턴 스포츠 2018.03~2021.12·G4 렉스턴 2017.07~2020.11·로디우스/스타빅 II 2015.06~2019.03, 87510-30000/35050/35060/36000/36500/38010/08011 대체, 433MHz), originalkey.ru(G4 렉스턴 2017.05~2020.11 순정 스마트키 SmartKeyMV1), originalkey.ru(티볼리 2015.03~2020.01 순정 스마트키 SmartKeyMV1: 4D60x80 칩, 433MHz) — 같은 SmartKeyMV1 키가 G4 렉스턴 2017.07~2020.11에 적용, Keystation(SsangYong Rexton 2버튼 리모컨 키 케이스 TOY48 블레이드), Autokeymaster(Rexton·Actyon 4D60x80 키 TOY40·TOY48)</t>
         </is>
       </c>
       <c r="P162" s="4" t="inlineStr">
@@ -12641,357 +12812,357 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A55"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr"/>
+      <c r="A2" s="19" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>- 칼리스타(1993-1997)·코란도 훼미리(1988-1996)는 2000년식 이전에 단종되어 행이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제와 다른 모델은 실제 기준으로 적었습니다(체어맨 H ~2014, 체어맨 W ~2017, 코란도 e-모션 2022~2023, 무쏘 EV 2025~, 렉스턴 스포츠는 2025.2 무쏘 스포츠로 차명 변경).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 구형은 VDO 이모빌라이저 박스(이모박스), 액티언·카이런·렉스턴 계열은 이모빌라이저 컨트롤 유닛(ICU, 87110-08B00/09000), 신형 스마트키 차량은 SKM(스마트키 모듈)입니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>- 폴딩키(리모컨 일체형) 품번은 '폴딩키(부품번호)', 스마트키 트랜스미터 품번은 '스마트키(부품번호)' 칸에 적었습니다. 쌍용은 카드키가 없어 카드키 칸은 비었습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID60(4D60)·ID70/DST80(4D70) → O/O/O, ID48(Megamos Crypto) → △/△/△, ID48·ID60 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr"/>
+      <c r="A15" s="19" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — 이스타나는 키 칩 자료를 찾지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나 연식 범위 밖인 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr"/>
+      <c r="A19" s="19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>- 무쏘·코란도·렉스턴(2002-2006): VDO 이모박스(MCU MC68HC05B16) + 메가모스 크립토(ID48) 트랜스폰더 — TMPro 모듈 85 자료. 코란도 2000-2006 블레이드 HYN10(JMA HY-5.P1).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>- 액티언·카이런·렉스턴 계열: 4D-60 칩 키, 블레이드 SSY3(JMA SSA-2P). 순정 키 87170-32030·32020·08D50은 80bit, 87170-08B21은 40bit — 연식 구분 자료가 없어 키 품번으로 확인해야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>- 이모빌라이저 컨트롤 유닛(87110-08B00/09000) 적용: 렉스턴 2006.02~2017.04, 카이런 2005.05~2007.03, 액티언 2005.10~2007.03, 액티언 스포츠 2006.04~2007.03. 2007.4 이후 카이런·액티언 계열의 모듈 명칭은 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>- 순정 3버튼 폴딩키 87510-21100(코란도 C·로디우스 II/코란도 투리스모·티볼리 등): 80bit TI 칩(판매처 표기 ID70 DST80 / ID8E). 블레이드는 TOY48(remkeys)과 KI-7(3D Group, 블레이드 품번 7105121500)로 표기가 다릅니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>- [재조사] 토레스 스마트키 칩은 47칩(ID47, Hitag3) — 국내 열쇠기사 카페 자료. 토레스 EVX·액티언(J120)·무쏘 EV는 같은 플랫폼이라 동일 추정(주황).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>- [재조사] 코란도 C(러시아명 New Actyon) 순정 스마트키 4D60x80·비상키 TOY48, 스타빅·액티언·티볼리·렉스턴 순정 폴딩키(2013-2021) 4D60x80, 렉스턴 W 2버튼 키 4D60x80·TOY40.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>- [재조사] 순정 스마트키 R-C-2CG-SmartKeyMV1(4D60x80, 433MHz): 티볼리 2015.03~2020.01, 렉스턴 스포츠 2018.03~2021.12, G4 렉스턴 2017.07~2020.11, 로디우스/스타빅 II 2015.06~2019.03. 이후 신형 키(G4 2020.11~ 8751036C20 등)는 칩 자료 없음(주황).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>- [재조사] 코란도 C(C200) 이모빌라이저는 SKM(키 슬롯)과 엔진 ECU(EMS)가 P-CAN으로 인증. 액티언 2008~2011도 별도 이모빌라이저 컨트롤 유닛 사용(품번 변경).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>- 코란도 C300 스마트키 DST80·HYN14R, 렉스턴 W 2013 스마트키 4D70 DST80(FCC DEO-MT FOBG02), G4 렉스턴 이모빌라이저 = SKM(87570-36010, 2017.07~).</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n"/>
+      <c r="A30" s="19" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n"/>
+      <c r="A38" s="19" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n"/>
+      <c r="A47" s="19" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n"/>
+      <c r="A51" s="19" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>- 무쏘 2000·2001: 무쏘 1998~ ID48(29Fxxx), 2001~2005 VDO 이모박스(MC68HC05B16) + ID48(autotronics·TMPro 모듈 85) — 이모박스 자료가 2002부터라던 이전 기록 정정</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>- KGM(쌍용) 순정 키 번호: catcar.info 쌍용 EPC KEY SET 그룹(좌핸들, 이모빌라이저 사양, 생산 기간) — 체어맨 H 7199111050(2000.1~2007.12)·7199111052(2007.12~2011.4)·발렛키 7199111070, 체어맨 W 7105014000(~2011.6)·7105014300(2011.7~), 코란도 71010062A0(이모빌라이저), 무쏘 71001051A0(이모빌라이저)·0000000319(칩 없음), 렉스턴 71050081A0(~2002.7)·A1(~2003.12)·A2(~2006.2)·디젤 71050082A0(2003.12~), 로디우스 7106A21320(디젤)·7106A21310(가솔린), 이스타나 0000000418</t>
         </is>
@@ -13001,6 +13172,13 @@
       <c r="A55" s="19" t="inlineStr">
         <is>
           <t>- KGM(쌍용) 보완: 뉴 코란도 71010062A0(이모빌라이저 블랭킹 키, ~2005.9.23 생산), 렉스턴 2001년식은 EPC 시작(2002.2) 이전이라 71050081A0 [추정], 렉스턴 W(2012.6~) 키 세트 710A108D00(D27, 디젤 2.7)·710A108D20(E32, 가솔린 3.2)·710A108D70(D20R, 디젤 2.0) — catcar.info 쌍용 EPC(좌핸들), 체어맨 H 2012~2014·로디우스 2012~2013은 EPC 마지막 번호를 [추정]으로 기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>- 6차 세대별 보완: 무쏘 SSY2(Autokeymaster), G4 렉스턴·렉스턴 스포츠 TOY48(Keystation), 토레스·액티언 2세대·무쏘 EV는 같은 회사 스마트키 기준 TOY48[추정]</t>
         </is>
       </c>
     </row>
